--- a/セリフ編集/その他セリフ/その他.xlsx
+++ b/セリフ編集/その他セリフ/その他.xlsx
@@ -3651,7 +3651,7 @@
       </c>
       <c r="H94" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">旗揚げからここにいるんだぜ、あたし。</t>
+          <t xml:space="preserve">旗揚げからずっと、ここにいるんだぜ。</t>
         </is>
       </c>
     </row>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="H108" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あたしなりに結果は出してきたつもりだ。</t>
+          <t xml:space="preserve">私なりに結果は出してきたつもりだ。</t>
         </is>
       </c>
     </row>

--- a/セリフ編集/その他セリフ/その他.xlsx
+++ b/セリフ編集/その他セリフ/その他.xlsx
@@ -192,7 +192,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J513"/>
+  <dimension ref="A1:J534"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -9540,7 +9540,7 @@
     <row r="256" ht="40" customHeight="1">
       <c r="A256" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreetingGeneric[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.challengeArrival.standard[1]</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
@@ -9560,19 +9560,24 @@
       </c>
       <c r="E256" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreetingGeneric[1]</t>
+          <t xml:space="preserve">challengeArrival.standard[1]</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="H256" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">短い間ですが、よろしくお願いします！</t>
+          <t xml:space="preserve">三人で行きます。お宅の三人、隠さず出してください。</t>
         </is>
       </c>
     </row>
     <row r="257" ht="40" customHeight="1">
       <c r="A257" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreetingGeneric[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.challengeArrival.standard[2]</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
@@ -9592,19 +9597,24 @@
       </c>
       <c r="E257" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreetingGeneric[2]</t>
+          <t xml:space="preserve">challengeArrival.standard[2]</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="H257" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お邪魔します。力になれたら嬉しいです！</t>
+          <t xml:space="preserve">私を切った判断が正しかったか、確かめに来ました。</t>
         </is>
       </c>
     </row>
     <row r="258" ht="40" customHeight="1">
       <c r="A258" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreetingGeneric[3]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.challengeArrival.standard[3]</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
@@ -9624,19 +9634,24 @@
       </c>
       <c r="E258" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreetingGeneric[3]</t>
+          <t xml:space="preserve">challengeArrival.standard[3]</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="H258" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">レンタルでも全力です。よろしくお願いします！</t>
+          <t xml:space="preserve">三つとも取ります。それで話は終わりです。</t>
         </is>
       </c>
     </row>
     <row r="259" ht="40" customHeight="1">
       <c r="A259" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatCoach.fresh[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.challengeArrival.ojousama[1]</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
@@ -9656,19 +9671,24 @@
       </c>
       <c r="E259" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatCoach.fresh[1]</t>
+          <t xml:space="preserve">challengeArrival.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">お嬢様</t>
         </is>
       </c>
       <c r="H259" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}、今日はよく動いてる。仕込むなら今だ</t>
+          <t xml:space="preserve">三人で参りますわ。お宅の精鋭を、お出しになって。</t>
         </is>
       </c>
     </row>
     <row r="260" ht="40" customHeight="1">
       <c r="A260" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatCoach.fresh[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.challengeArrival.ojousama[2]</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
@@ -9688,19 +9708,24 @@
       </c>
       <c r="E260" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatCoach.fresh[2]</t>
+          <t xml:space="preserve">challengeArrival.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">お嬢様</t>
         </is>
       </c>
       <c r="H260" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}の体が、新しい動きを素直に飲み込んでいる</t>
+          <t xml:space="preserve">わたくしを要らないと決めた方に、お会いしたいの。</t>
         </is>
       </c>
     </row>
     <row r="261" ht="40" customHeight="1">
       <c r="A261" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatCoach.fresh[3]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.challengeArrival.ojousama[3]</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
@@ -9720,19 +9745,24 @@
       </c>
       <c r="E261" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatCoach.fresh[3]</t>
+          <t xml:space="preserve">challengeArrival.ojousama[3]</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">お嬢様</t>
         </is>
       </c>
       <c r="H261" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今の{name}なら、多少きつくしても全部持っていく</t>
+          <t xml:space="preserve">三つの勝負で、格の違いをお見せいたします。</t>
         </is>
       </c>
     </row>
     <row r="262" ht="40" customHeight="1">
       <c r="A262" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatCoach.fresh[4]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.challengeArrival.cool[1]</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
@@ -9752,19 +9782,24 @@
       </c>
       <c r="E262" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatCoach.fresh[4]</t>
+          <t xml:space="preserve">challengeArrival.cool[1]</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">クール</t>
         </is>
       </c>
       <c r="H262" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}の足が軽い。こういう週こそ厚く積ませたい</t>
+          <t xml:space="preserve">三人で行く。そちらも三人、出して。</t>
         </is>
       </c>
     </row>
     <row r="263" ht="40" customHeight="1">
       <c r="A263" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatCoach.fresh[5]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.challengeArrival.cool[2]</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
@@ -9784,19 +9819,24 @@
       </c>
       <c r="E263" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatCoach.fresh[5]</t>
+          <t xml:space="preserve">challengeArrival.cool[2]</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">クール</t>
         </is>
       </c>
       <c r="H263" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}、伸びる顔をしている。今日の一本は残るぞ</t>
+          <t xml:space="preserve">切られた理由を、まだ聞いていない。……三つで返す。</t>
         </is>
       </c>
     </row>
     <row r="264" ht="40" customHeight="1">
       <c r="A264" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatCoach.fresh[6]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.challengeArrival.cool[3]</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
@@ -9816,19 +9856,24 @@
       </c>
       <c r="E264" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatCoach.fresh[6]</t>
+          <t xml:space="preserve">challengeArrival.cool[3]</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">クール</t>
         </is>
       </c>
       <c r="H264" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}は休み明けの体だ。一番よく入る時期に来ている</t>
+          <t xml:space="preserve">断ってもいい。逃げたと書かれるだけ。</t>
         </is>
       </c>
     </row>
     <row r="265" ht="40" customHeight="1">
       <c r="A265" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatCoach.fresh[7]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.challengeArrival.delinquent[1]</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
@@ -9848,19 +9893,24 @@
       </c>
       <c r="E265" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatCoach.fresh[7]</t>
+          <t xml:space="preserve">challengeArrival.delinquent[1]</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ヤンキー</t>
         </is>
       </c>
       <c r="H265" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}、今週は当たり週だ。使うなら、ここで使え</t>
+          <t xml:space="preserve">三人で乗り込む。お宅も三人、出しなよ。</t>
         </is>
       </c>
     </row>
     <row r="266" ht="40" customHeight="1">
       <c r="A266" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatCoach.warm[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.challengeArrival.delinquent[2]</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
@@ -9880,19 +9930,24 @@
       </c>
       <c r="E266" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatCoach.warm[1]</t>
+          <t xml:space="preserve">challengeArrival.delinquent[2]</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ヤンキー</t>
         </is>
       </c>
       <c r="H266" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}、悪くはない。ただ、先週ほどは入っていかない</t>
+          <t xml:space="preserve">私を追い出したこと、忘れちゃいねえよ。三人で行く。</t>
         </is>
       </c>
     </row>
     <row r="267" ht="40" customHeight="1">
       <c r="A267" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatCoach.warm[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.challengeArrival.delinquent[3]</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="2">
@@ -9912,19 +9967,24 @@
       </c>
       <c r="E267" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatCoach.warm[2]</t>
+          <t xml:space="preserve">challengeArrival.delinquent[3]</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ヤンキー</t>
         </is>
       </c>
       <c r="H267" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}の伸びが少し鈍ってきた。詰めすぎたか</t>
+          <t xml:space="preserve">あんたたちの一番強いのを出せばいい。潰すから。</t>
         </is>
       </c>
     </row>
     <row r="268" ht="40" customHeight="1">
       <c r="A268" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatCoach.warm[3]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.challengeArrival.polite[1]</t>
         </is>
       </c>
       <c r="B268" t="inlineStr" s="2">
@@ -9944,19 +10004,24 @@
       </c>
       <c r="E268" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatCoach.warm[3]</t>
+          <t xml:space="preserve">challengeArrival.polite[1]</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">丁寧</t>
         </is>
       </c>
       <c r="H268" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}、同じメニューなのに返りが薄い。そろそろ一息か</t>
+          <t xml:space="preserve">三人で伺います。断られては、困りますので。</t>
         </is>
       </c>
     </row>
     <row r="269" ht="40" customHeight="1">
       <c r="A269" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatCoach.warm[4]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.challengeArrival.polite[2]</t>
         </is>
       </c>
       <c r="B269" t="inlineStr" s="2">
@@ -9976,19 +10041,24 @@
       </c>
       <c r="E269" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatCoach.warm[4]</t>
+          <t xml:space="preserve">challengeArrival.polite[2]</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">丁寧</t>
         </is>
       </c>
       <c r="H269" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}、動けてはいる。だが、切れがひとつ落ちている</t>
+          <t xml:space="preserve">私を手放した判断、間違いだったと申し上げます。</t>
         </is>
       </c>
     </row>
     <row r="270" ht="40" customHeight="1">
       <c r="A270" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatCoach.warm[5]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.challengeArrival.polite[3]</t>
         </is>
       </c>
       <c r="B270" t="inlineStr" s="2">
@@ -10008,19 +10078,24 @@
       </c>
       <c r="E270" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatCoach.warm[5]</t>
+          <t xml:space="preserve">challengeArrival.polite[3]</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">丁寧</t>
         </is>
       </c>
       <c r="H270" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}の体が慣れてきた。効きが落ちる頃合いだ</t>
+          <t xml:space="preserve">お宅の三人を、正面から倒させていただきます。</t>
         </is>
       </c>
     </row>
     <row r="271" ht="40" customHeight="1">
       <c r="A271" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatCoach.warm[6]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.challengeArrival.composed[1]</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="2">
@@ -10040,19 +10115,24 @@
       </c>
       <c r="E271" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatCoach.warm[6]</t>
+          <t xml:space="preserve">challengeArrival.composed[1]</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">鷹揚</t>
         </is>
       </c>
       <c r="H271" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}、今週も同じ調子で行くなら、得は薄いぞ</t>
+          <t xml:space="preserve">三人で行かせてもらうよ。そちらも三人、頼むね。</t>
         </is>
       </c>
     </row>
     <row r="272" ht="40" customHeight="1">
       <c r="A272" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatCoach.warm[7]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.challengeArrival.composed[2]</t>
         </is>
       </c>
       <c r="B272" t="inlineStr" s="2">
@@ -10072,19 +10152,24 @@
       </c>
       <c r="E272" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatCoach.warm[7]</t>
+          <t xml:space="preserve">challengeArrival.composed[2]</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">鷹揚</t>
         </is>
       </c>
       <c r="H272" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}にきついのを続けるか。…見極めどきだな</t>
+          <t xml:space="preserve">恨んではいないんだ。ただ、確かめたいことがある。</t>
         </is>
       </c>
     </row>
     <row r="273" ht="40" customHeight="1">
       <c r="A273" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatCoach.heavy[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.challengeArrival.composed[3]</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="2">
@@ -10104,19 +10189,24 @@
       </c>
       <c r="E273" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatCoach.heavy[1]</t>
+          <t xml:space="preserve">challengeArrival.composed[3]</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">鷹揚</t>
         </is>
       </c>
       <c r="H273" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}、今日は体が重い。何をやらせても素通りだ</t>
+          <t xml:space="preserve">断る自由はあるよ。それも、答えのうちだ。</t>
         </is>
       </c>
     </row>
     <row r="274" ht="40" customHeight="1">
       <c r="A274" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatCoach.heavy[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.challengeArrival.seductive[1]</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="2">
@@ -10136,19 +10226,24 @@
       </c>
       <c r="E274" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatCoach.heavy[2]</t>
+          <t xml:space="preserve">challengeArrival.seductive[1]</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">蠱惑</t>
         </is>
       </c>
       <c r="H274" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今の{name}に課しても、削るだけで何も積まれない</t>
+          <t xml:space="preserve">三人で伺うわ。お宅の自慢の三人、見せて。</t>
         </is>
       </c>
     </row>
     <row r="275" ht="40" customHeight="1">
       <c r="A275" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatCoach.heavy[3]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.challengeArrival.seductive[2]</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
@@ -10168,19 +10263,24 @@
       </c>
       <c r="E275" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatCoach.heavy[3]</t>
+          <t xml:space="preserve">challengeArrival.seductive[2]</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">蠱惑</t>
         </is>
       </c>
       <c r="H275" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}は追い込みすぎだ。一度、外してやってくれ</t>
+          <t xml:space="preserve">私を手放したこと、後悔させてあげる。……ふふ。</t>
         </is>
       </c>
     </row>
     <row r="276" ht="40" customHeight="1">
       <c r="A276" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatCoach.heavy[4]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.challengeArrival.seductive[3]</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
@@ -10200,19 +10300,24 @@
       </c>
       <c r="E276" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatCoach.heavy[4]</t>
+          <t xml:space="preserve">challengeArrival.seductive[3]</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">蠱惑</t>
         </is>
       </c>
       <c r="H276" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}、汗はかいている。だが、身についてはいない</t>
+          <t xml:space="preserve">三つとも、いただくわ。断る理由、あるかしら？</t>
         </is>
       </c>
     </row>
     <row r="277" ht="40" customHeight="1">
       <c r="A277" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatCoach.heavy[5]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreetingGeneric[1]</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
@@ -10232,19 +10337,19 @@
       </c>
       <c r="E277" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatCoach.heavy[5]</t>
+          <t xml:space="preserve">rentalGreetingGeneric[1]</t>
         </is>
       </c>
       <c r="H277" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}の体はもう受け付けていない。休ませれば戻る</t>
+          <t xml:space="preserve">短い間ですが、よろしくお願いします！</t>
         </is>
       </c>
     </row>
     <row r="278" ht="40" customHeight="1">
       <c r="A278" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatCoach.heavy[6]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreetingGeneric[2]</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
@@ -10264,19 +10369,19 @@
       </c>
       <c r="E278" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatCoach.heavy[6]</t>
+          <t xml:space="preserve">rentalGreetingGeneric[2]</t>
         </is>
       </c>
       <c r="H278" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今の{name}にやらせるのは、怪我を買うようなものだ</t>
+          <t xml:space="preserve">お邪魔します。力になれたら嬉しいです！</t>
         </is>
       </c>
     </row>
     <row r="279" ht="40" customHeight="1">
       <c r="A279" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatCoach.heavy[7]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreetingGeneric[3]</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
@@ -10296,19 +10401,19 @@
       </c>
       <c r="E279" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatCoach.heavy[7]</t>
+          <t xml:space="preserve">rentalGreetingGeneric[3]</t>
         </is>
       </c>
       <c r="H279" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}、一週抜けばまた入るようになる。それだけの話だ</t>
+          <t xml:space="preserve">レンタルでも全力です。よろしくお願いします！</t>
         </is>
       </c>
     </row>
     <row r="280" ht="40" customHeight="1">
       <c r="A280" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreetingGeneric[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatCoach.fresh[1]</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="2">
@@ -10328,19 +10433,19 @@
       </c>
       <c r="E280" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreetingGeneric[1]</t>
+          <t xml:space="preserve">heatCoach.fresh[1]</t>
         </is>
       </c>
       <c r="H280" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">声をかけてもらえて嬉しいです。頑張ります！</t>
+          <t xml:space="preserve">{name}、今日はよく動いてる。仕込むなら今だ</t>
         </is>
       </c>
     </row>
     <row r="281" ht="40" customHeight="1">
       <c r="A281" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreetingGeneric[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatCoach.fresh[2]</t>
         </is>
       </c>
       <c r="B281" t="inlineStr" s="2">
@@ -10360,19 +10465,19 @@
       </c>
       <c r="E281" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreetingGeneric[2]</t>
+          <t xml:space="preserve">heatCoach.fresh[2]</t>
         </is>
       </c>
       <c r="H281" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">期待に応えられるよう、全力でやります！</t>
+          <t xml:space="preserve">{name}の体が、新しい動きを素直に飲み込んでいる</t>
         </is>
       </c>
     </row>
     <row r="282" ht="40" customHeight="1">
       <c r="A282" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreetingGeneric[3]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatCoach.fresh[3]</t>
         </is>
       </c>
       <c r="B282" t="inlineStr" s="2">
@@ -10392,19 +10497,19 @@
       </c>
       <c r="E282" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreetingGeneric[3]</t>
+          <t xml:space="preserve">heatCoach.fresh[3]</t>
         </is>
       </c>
       <c r="H282" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここで腕を磨かせてもらいます。よろしくお願いします！</t>
+          <t xml:space="preserve">今の{name}なら、多少きつくしても全部持っていく</t>
         </is>
       </c>
     </row>
     <row r="283" ht="40" customHeight="1">
       <c r="A283" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreetingGeneric[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatCoach.fresh[4]</t>
         </is>
       </c>
       <c r="B283" t="inlineStr" s="2">
@@ -10424,19 +10529,19 @@
       </c>
       <c r="E283" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreetingGeneric[1]</t>
+          <t xml:space="preserve">heatCoach.fresh[4]</t>
         </is>
       </c>
       <c r="H283" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう一度リングに立てます。無駄にしません！</t>
+          <t xml:space="preserve">{name}の足が軽い。こういう週こそ厚く積ませたい</t>
         </is>
       </c>
     </row>
     <row r="284" ht="40" customHeight="1">
       <c r="A284" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreetingGeneric[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatCoach.fresh[5]</t>
         </is>
       </c>
       <c r="B284" t="inlineStr" s="2">
@@ -10456,19 +10561,19 @@
       </c>
       <c r="E284" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreetingGeneric[2]</t>
+          <t xml:space="preserve">heatCoach.fresh[5]</t>
         </is>
       </c>
       <c r="H284" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">拾っていただいた恩、必ず返します！</t>
+          <t xml:space="preserve">{name}、伸びる顔をしている。今日の一本は残るぞ</t>
         </is>
       </c>
     </row>
     <row r="285" ht="40" customHeight="1">
       <c r="A285" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreetingGeneric[3]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatCoach.fresh[6]</t>
         </is>
       </c>
       <c r="B285" t="inlineStr" s="2">
@@ -10488,24 +10593,24 @@
       </c>
       <c r="E285" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreetingGeneric[3]</t>
+          <t xml:space="preserve">heatCoach.fresh[6]</t>
         </is>
       </c>
       <c r="H285" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">所属を失っていました。ここで、やり直します！</t>
+          <t xml:space="preserve">{name}は休み明けの体だ。一番よく入る時期に来ている</t>
         </is>
       </c>
     </row>
     <row r="286" ht="40" customHeight="1">
       <c r="A286" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-12._narration[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatCoach.fresh[7]</t>
         </is>
       </c>
       <c r="B286" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13-Glimpse Cascade</t>
+          <t xml:space="preserve">12-選手経歴イベント</t>
         </is>
       </c>
       <c r="C286" t="inlineStr" s="2">
@@ -10515,29 +10620,29 @@
       </c>
       <c r="D286" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="E286" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-12._narration[1]</t>
+          <t xml:space="preserve">heatCoach.fresh[7]</t>
         </is>
       </c>
       <c r="H286" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{nameA}と{nameB}は、控え室で一度も目を合わせなかったという</t>
+          <t xml:space="preserve">{name}、今週は当たり週だ。使うなら、ここで使え</t>
         </is>
       </c>
     </row>
     <row r="287" ht="40" customHeight="1">
       <c r="A287" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-12._narration[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatCoach.warm[1]</t>
         </is>
       </c>
       <c r="B287" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13-Glimpse Cascade</t>
+          <t xml:space="preserve">12-選手経歴イベント</t>
         </is>
       </c>
       <c r="C287" t="inlineStr" s="2">
@@ -10547,29 +10652,29 @@
       </c>
       <c r="D287" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="E287" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-12._narration[2]</t>
+          <t xml:space="preserve">heatCoach.warm[1]</t>
         </is>
       </c>
       <c r="H287" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">インタビュー後、{nameA}は{nameB}の名前を口にしなかった</t>
+          <t xml:space="preserve">{name}、悪くはない。ただ、先週ほどは入っていかない</t>
         </is>
       </c>
     </row>
     <row r="288" ht="40" customHeight="1">
       <c r="A288" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-12._narration[3]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatCoach.warm[2]</t>
         </is>
       </c>
       <c r="B288" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13-Glimpse Cascade</t>
+          <t xml:space="preserve">12-選手経歴イベント</t>
         </is>
       </c>
       <c r="C288" t="inlineStr" s="2">
@@ -10579,29 +10684,29 @@
       </c>
       <c r="D288" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="E288" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-12._narration[3]</t>
+          <t xml:space="preserve">heatCoach.warm[2]</t>
         </is>
       </c>
       <c r="H288" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">リング上ですれ違った瞬間、空気が凍ったように見えた</t>
+          <t xml:space="preserve">{name}の伸びが少し鈍ってきた。詰めすぎたか</t>
         </is>
       </c>
     </row>
     <row r="289" ht="40" customHeight="1">
       <c r="A289" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-12._narration[4]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatCoach.warm[3]</t>
         </is>
       </c>
       <c r="B289" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13-Glimpse Cascade</t>
+          <t xml:space="preserve">12-選手経歴イベント</t>
         </is>
       </c>
       <c r="C289" t="inlineStr" s="2">
@@ -10611,29 +10716,29 @@
       </c>
       <c r="D289" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="E289" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-12._narration[4]</t>
+          <t xml:space="preserve">heatCoach.warm[3]</t>
         </is>
       </c>
       <c r="H289" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{nameA}と{nameB}が同じ廊下に居合わせたとき、誰もが息を潜めたという</t>
+          <t xml:space="preserve">{name}、同じメニューなのに返りが薄い。そろそろ一息か</t>
         </is>
       </c>
     </row>
     <row r="290" ht="40" customHeight="1">
       <c r="A290" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-12._narration[5]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatCoach.warm[4]</t>
         </is>
       </c>
       <c r="B290" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13-Glimpse Cascade</t>
+          <t xml:space="preserve">12-選手経歴イベント</t>
         </is>
       </c>
       <c r="C290" t="inlineStr" s="2">
@@ -10643,29 +10748,29 @@
       </c>
       <c r="D290" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="E290" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-12._narration[5]</t>
+          <t xml:space="preserve">heatCoach.warm[4]</t>
         </is>
       </c>
       <c r="H290" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{nameB}の話題が出ても、{nameA}は表情ひとつ変えなかった</t>
+          <t xml:space="preserve">{name}、動けてはいる。だが、切れがひとつ落ちている</t>
         </is>
       </c>
     </row>
     <row r="291" ht="40" customHeight="1">
       <c r="A291" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.A.standard[1].text</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatCoach.warm[5]</t>
         </is>
       </c>
       <c r="B291" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14-PPV・対抗戦・トーナメント</t>
+          <t xml:space="preserve">12-選手経歴イベント</t>
         </is>
       </c>
       <c r="C291" t="inlineStr" s="2">
@@ -10675,34 +10780,29 @@
       </c>
       <c r="D291" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="E291" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A.standard[1].text</t>
-        </is>
-      </c>
-      <c r="F291" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">標準</t>
+          <t xml:space="preserve">heatCoach.warm[5]</t>
         </is>
       </c>
       <c r="H291" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">膝が笑ってる。…でも不思議と、清々しいんです。あなたに負けたなら</t>
+          <t xml:space="preserve">{name}の体が慣れてきた。効きが落ちる頃合いだ</t>
         </is>
       </c>
     </row>
     <row r="292" ht="40" customHeight="1">
       <c r="A292" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.A.standard[2].text</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatCoach.warm[6]</t>
         </is>
       </c>
       <c r="B292" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14-PPV・対抗戦・トーナメント</t>
+          <t xml:space="preserve">12-選手経歴イベント</t>
         </is>
       </c>
       <c r="C292" t="inlineStr" s="2">
@@ -10712,34 +10812,29 @@
       </c>
       <c r="D292" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="E292" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A.standard[2].text</t>
-        </is>
-      </c>
-      <c r="F292" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">標準</t>
+          <t xml:space="preserve">heatCoach.warm[6]</t>
         </is>
       </c>
       <c r="H292" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最後の技、返せなかった。…認めます。今日はあなたが上でした</t>
+          <t xml:space="preserve">{name}、今週も同じ調子で行くなら、得は薄いぞ</t>
         </is>
       </c>
     </row>
     <row r="293" ht="40" customHeight="1">
       <c r="A293" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.A.standard[3].text</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatCoach.warm[7]</t>
         </is>
       </c>
       <c r="B293" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14-PPV・対抗戦・トーナメント</t>
+          <t xml:space="preserve">12-選手経歴イベント</t>
         </is>
       </c>
       <c r="C293" t="inlineStr" s="2">
@@ -10749,34 +10844,29 @@
       </c>
       <c r="D293" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="E293" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A.standard[3].text</t>
-        </is>
-      </c>
-      <c r="F293" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">標準</t>
+          <t xml:space="preserve">heatCoach.warm[7]</t>
         </is>
       </c>
       <c r="H293" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">4年後、同じ舞台でまた。…その時は、こんな顔で終わらせません</t>
+          <t xml:space="preserve">{name}にきついのを続けるか。…見極めどきだな</t>
         </is>
       </c>
     </row>
     <row r="294" ht="40" customHeight="1">
       <c r="A294" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.A.composed[1].text</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatCoach.heavy[1]</t>
         </is>
       </c>
       <c r="B294" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14-PPV・対抗戦・トーナメント</t>
+          <t xml:space="preserve">12-選手経歴イベント</t>
         </is>
       </c>
       <c r="C294" t="inlineStr" s="2">
@@ -10786,34 +10876,29 @@
       </c>
       <c r="D294" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="E294" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A.composed[1].text</t>
-        </is>
-      </c>
-      <c r="F294" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">鷹揚</t>
+          <t xml:space="preserve">heatCoach.heavy[1]</t>
         </is>
       </c>
       <c r="H294" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…参った。あんたのほうが、一枚上だったね</t>
+          <t xml:space="preserve">{name}、今日は体が重い。何をやらせても素通りだ</t>
         </is>
       </c>
     </row>
     <row r="295" ht="40" customHeight="1">
       <c r="A295" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.A.composed[2].text</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatCoach.heavy[2]</t>
         </is>
       </c>
       <c r="B295" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14-PPV・対抗戦・トーナメント</t>
+          <t xml:space="preserve">12-選手経歴イベント</t>
         </is>
       </c>
       <c r="C295" t="inlineStr" s="2">
@@ -10823,34 +10908,29 @@
       </c>
       <c r="D295" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="E295" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A.composed[2].text</t>
-        </is>
-      </c>
-      <c r="F295" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">鷹揚</t>
+          <t xml:space="preserve">heatCoach.heavy[2]</t>
         </is>
       </c>
       <c r="H295" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">効いたよ、最後のあれ。…次は、そう簡単にはいかない</t>
+          <t xml:space="preserve">今の{name}に課しても、削るだけで何も積まれない</t>
         </is>
       </c>
     </row>
     <row r="296" ht="40" customHeight="1">
       <c r="A296" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.A.composed[3].text</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatCoach.heavy[3]</t>
         </is>
       </c>
       <c r="B296" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14-PPV・対抗戦・トーナメント</t>
+          <t xml:space="preserve">12-選手経歴イベント</t>
         </is>
       </c>
       <c r="C296" t="inlineStr" s="2">
@@ -10860,34 +10940,29 @@
       </c>
       <c r="D296" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="E296" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A.composed[3].text</t>
-        </is>
-      </c>
-      <c r="F296" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">鷹揚</t>
+          <t xml:space="preserve">heatCoach.heavy[3]</t>
         </is>
       </c>
       <c r="H296" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">4年か。…長いようで、すぐだ。…その時まで、覚えてて</t>
+          <t xml:space="preserve">{name}は追い込みすぎだ。一度、外してやってくれ</t>
         </is>
       </c>
     </row>
     <row r="297" ht="40" customHeight="1">
       <c r="A297" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.A.ojousama[1].text</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatCoach.heavy[4]</t>
         </is>
       </c>
       <c r="B297" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14-PPV・対抗戦・トーナメント</t>
+          <t xml:space="preserve">12-選手経歴イベント</t>
         </is>
       </c>
       <c r="C297" t="inlineStr" s="2">
@@ -10897,34 +10972,29 @@
       </c>
       <c r="D297" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="E297" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A.ojousama[1].text</t>
-        </is>
-      </c>
-      <c r="F297" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">お嬢様</t>
+          <t xml:space="preserve">heatCoach.heavy[4]</t>
         </is>
       </c>
       <c r="H297" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お見事ですわ。…このわたくしを、ここまで追い込むなんて</t>
+          <t xml:space="preserve">{name}、汗はかいている。だが、身についてはいない</t>
         </is>
       </c>
     </row>
     <row r="298" ht="40" customHeight="1">
       <c r="A298" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.A.ojousama[2].text</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatCoach.heavy[5]</t>
         </is>
       </c>
       <c r="B298" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14-PPV・対抗戦・トーナメント</t>
+          <t xml:space="preserve">12-選手経歴イベント</t>
         </is>
       </c>
       <c r="C298" t="inlineStr" s="2">
@@ -10934,34 +11004,29 @@
       </c>
       <c r="D298" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="E298" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A.ojousama[2].text</t>
-        </is>
-      </c>
-      <c r="F298" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">お嬢様</t>
+          <t xml:space="preserve">heatCoach.heavy[5]</t>
         </is>
       </c>
       <c r="H298" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しさより、感謝が勝ちますの。…あなたと踊れて、幸せでしたわ</t>
+          <t xml:space="preserve">{name}の体はもう受け付けていない。休ませれば戻る</t>
         </is>
       </c>
     </row>
     <row r="299" ht="40" customHeight="1">
       <c r="A299" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.A.ojousama[3].text</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatCoach.heavy[6]</t>
         </is>
       </c>
       <c r="B299" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14-PPV・対抗戦・トーナメント</t>
+          <t xml:space="preserve">12-選手経歴イベント</t>
         </is>
       </c>
       <c r="C299" t="inlineStr" s="2">
@@ -10971,34 +11036,29 @@
       </c>
       <c r="D299" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="E299" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A.ojousama[3].text</t>
-        </is>
-      </c>
-      <c r="F299" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">お嬢様</t>
+          <t xml:space="preserve">heatCoach.heavy[6]</t>
         </is>
       </c>
       <c r="H299" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次の四年後、きっとお迎えに上がりますわ。…覚悟なさって</t>
+          <t xml:space="preserve">今の{name}にやらせるのは、怪我を買うようなものだ</t>
         </is>
       </c>
     </row>
     <row r="300" ht="40" customHeight="1">
       <c r="A300" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.A.delinquent[1].text</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatCoach.heavy[7]</t>
         </is>
       </c>
       <c r="B300" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14-PPV・対抗戦・トーナメント</t>
+          <t xml:space="preserve">12-選手経歴イベント</t>
         </is>
       </c>
       <c r="C300" t="inlineStr" s="2">
@@ -11008,34 +11068,29 @@
       </c>
       <c r="D300" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="E300" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A.delinquent[1].text</t>
-        </is>
-      </c>
-      <c r="F300" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">ヤンキー</t>
+          <t xml:space="preserve">heatCoach.heavy[7]</t>
         </is>
       </c>
       <c r="H300" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ちくしょう…強ぇな、あんた。参ったって言うしかねぇわ</t>
+          <t xml:space="preserve">{name}、一週抜けばまた入るようになる。それだけの話だ</t>
         </is>
       </c>
     </row>
     <row r="301" ht="40" customHeight="1">
       <c r="A301" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.A.delinquent[2].text</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreetingGeneric[1]</t>
         </is>
       </c>
       <c r="B301" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14-PPV・対抗戦・トーナメント</t>
+          <t xml:space="preserve">12-選手経歴イベント</t>
         </is>
       </c>
       <c r="C301" t="inlineStr" s="2">
@@ -11045,34 +11100,29 @@
       </c>
       <c r="D301" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="E301" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A.delinquent[2].text</t>
-        </is>
-      </c>
-      <c r="F301" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">ヤンキー</t>
+          <t xml:space="preserve">scoutGreetingGeneric[1]</t>
         </is>
       </c>
       <c r="H301" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">体、ボロボロだけど…笑っちまうな。いい試合だったろ?</t>
+          <t xml:space="preserve">声をかけてもらえて嬉しいです。頑張ります！</t>
         </is>
       </c>
     </row>
     <row r="302" ht="40" customHeight="1">
       <c r="A302" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.A.delinquent[3].text</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreetingGeneric[2]</t>
         </is>
       </c>
       <c r="B302" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14-PPV・対抗戦・トーナメント</t>
+          <t xml:space="preserve">12-選手経歴イベント</t>
         </is>
       </c>
       <c r="C302" t="inlineStr" s="2">
@@ -11082,34 +11132,29 @@
       </c>
       <c r="D302" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="E302" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A.delinquent[3].text</t>
-        </is>
-      </c>
-      <c r="F302" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">ヤンキー</t>
+          <t xml:space="preserve">scoutGreetingGeneric[2]</t>
         </is>
       </c>
       <c r="H302" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次は絶対ぶっ倒す。…って、負けたヤツが言うのもダセぇけどよ</t>
+          <t xml:space="preserve">期待に応えられるよう、全力でやります！</t>
         </is>
       </c>
     </row>
     <row r="303" ht="40" customHeight="1">
       <c r="A303" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.A.cool[1].text</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreetingGeneric[3]</t>
         </is>
       </c>
       <c r="B303" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14-PPV・対抗戦・トーナメント</t>
+          <t xml:space="preserve">12-選手経歴イベント</t>
         </is>
       </c>
       <c r="C303" t="inlineStr" s="2">
@@ -11119,34 +11164,29 @@
       </c>
       <c r="D303" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="E303" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A.cool[1].text</t>
-        </is>
-      </c>
-      <c r="F303" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">クール</t>
+          <t xml:space="preserve">scoutGreetingGeneric[3]</t>
         </is>
       </c>
       <c r="H303" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……強い。それだけだ</t>
+          <t xml:space="preserve">ここで腕を磨かせてもらいます。よろしくお願いします！</t>
         </is>
       </c>
     </row>
     <row r="304" ht="40" customHeight="1">
       <c r="A304" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.A.cool[2].text</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreetingGeneric[1]</t>
         </is>
       </c>
       <c r="B304" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14-PPV・対抗戦・トーナメント</t>
+          <t xml:space="preserve">12-選手経歴イベント</t>
         </is>
       </c>
       <c r="C304" t="inlineStr" s="2">
@@ -11156,34 +11196,29 @@
       </c>
       <c r="D304" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="E304" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A.cool[2].text</t>
-        </is>
-      </c>
-      <c r="F304" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">クール</t>
+          <t xml:space="preserve">faGreetingGeneric[1]</t>
         </is>
       </c>
       <c r="H304" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……あの一撃、忘れない。次に返す</t>
+          <t xml:space="preserve">もう一度リングに立てます。無駄にしません！</t>
         </is>
       </c>
     </row>
     <row r="305" ht="40" customHeight="1">
       <c r="A305" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.A.cool[3].text</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreetingGeneric[2]</t>
         </is>
       </c>
       <c r="B305" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14-PPV・対抗戦・トーナメント</t>
+          <t xml:space="preserve">12-選手経歴イベント</t>
         </is>
       </c>
       <c r="C305" t="inlineStr" s="2">
@@ -11193,34 +11228,29 @@
       </c>
       <c r="D305" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="E305" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A.cool[3].text</t>
-        </is>
-      </c>
-      <c r="F305" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">クール</t>
+          <t xml:space="preserve">faGreetingGeneric[2]</t>
         </is>
       </c>
       <c r="H305" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……4年。…短い。すぐ、また会う</t>
+          <t xml:space="preserve">拾っていただいた恩、必ず返します！</t>
         </is>
       </c>
     </row>
     <row r="306" ht="40" customHeight="1">
       <c r="A306" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.A.seductive[1].text</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreetingGeneric[3]</t>
         </is>
       </c>
       <c r="B306" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14-PPV・対抗戦・トーナメント</t>
+          <t xml:space="preserve">12-選手経歴イベント</t>
         </is>
       </c>
       <c r="C306" t="inlineStr" s="2">
@@ -11230,34 +11260,29 @@
       </c>
       <c r="D306" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="E306" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A.seductive[1].text</t>
-        </is>
-      </c>
-      <c r="F306" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">蠱惑</t>
+          <t xml:space="preserve">faGreetingGeneric[3]</t>
         </is>
       </c>
       <c r="H306" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、負けちゃった。…でも、悪くない負け方だったわ、ふふ</t>
+          <t xml:space="preserve">所属を失っていました。ここで、やり直します！</t>
         </is>
       </c>
     </row>
     <row r="307" ht="40" customHeight="1">
       <c r="A307" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.A.seductive[2].text</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-12._narration[1]</t>
         </is>
       </c>
       <c r="B307" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14-PPV・対抗戦・トーナメント</t>
+          <t xml:space="preserve">13-Glimpse Cascade</t>
         </is>
       </c>
       <c r="C307" t="inlineStr" s="2">
@@ -11267,34 +11292,29 @@
       </c>
       <c r="D307" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="E307" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A.seductive[2].text</t>
-        </is>
-      </c>
-      <c r="F307" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">蠱惑</t>
+          <t xml:space="preserve">GL-12._narration[1]</t>
         </is>
       </c>
       <c r="H307" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あなたのあの目…ゾクッとしたわ。認めてあげる、今日は上手</t>
+          <t xml:space="preserve">{nameA}と{nameB}は、控え室で一度も目を合わせなかったという</t>
         </is>
       </c>
     </row>
     <row r="308" ht="40" customHeight="1">
       <c r="A308" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.A.seductive[3].text</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-12._narration[2]</t>
         </is>
       </c>
       <c r="B308" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14-PPV・対抗戦・トーナメント</t>
+          <t xml:space="preserve">13-Glimpse Cascade</t>
         </is>
       </c>
       <c r="C308" t="inlineStr" s="2">
@@ -11304,34 +11324,29 @@
       </c>
       <c r="D308" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="E308" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A.seductive[3].text</t>
-        </is>
-      </c>
-      <c r="F308" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">蠱惑</t>
+          <t xml:space="preserve">GL-12._narration[2]</t>
         </is>
       </c>
       <c r="H308" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">4年後、今度は私が上に立つ。…楽しみにしてなさい?</t>
+          <t xml:space="preserve">インタビュー後、{nameA}は{nameB}の名前を口にしなかった</t>
         </is>
       </c>
     </row>
     <row r="309" ht="40" customHeight="1">
       <c r="A309" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.A.polite[1].text</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-12._narration[3]</t>
         </is>
       </c>
       <c r="B309" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14-PPV・対抗戦・トーナメント</t>
+          <t xml:space="preserve">13-Glimpse Cascade</t>
         </is>
       </c>
       <c r="C309" t="inlineStr" s="2">
@@ -11341,34 +11356,29 @@
       </c>
       <c r="D309" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="E309" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A.polite[1].text</t>
-        </is>
-      </c>
-      <c r="F309" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">丁寧</t>
+          <t xml:space="preserve">GL-12._narration[3]</t>
         </is>
       </c>
       <c r="H309" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">完敗です。…あなたの強さ、この体でしっかり教わりました</t>
+          <t xml:space="preserve">リング上ですれ違った瞬間、空気が凍ったように見えた</t>
         </is>
       </c>
     </row>
     <row r="310" ht="40" customHeight="1">
       <c r="A310" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.A.polite[2].text</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-12._narration[4]</t>
         </is>
       </c>
       <c r="B310" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14-PPV・対抗戦・トーナメント</t>
+          <t xml:space="preserve">13-Glimpse Cascade</t>
         </is>
       </c>
       <c r="C310" t="inlineStr" s="2">
@@ -11378,34 +11388,29 @@
       </c>
       <c r="D310" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="E310" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A.polite[2].text</t>
-        </is>
-      </c>
-      <c r="F310" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">丁寧</t>
+          <t xml:space="preserve">GL-12._narration[4]</t>
         </is>
       </c>
       <c r="H310" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しさはあります。でも、それ以上に…あなたに感謝しています</t>
+          <t xml:space="preserve">{nameA}と{nameB}が同じ廊下に居合わせたとき、誰もが息を潜めたという</t>
         </is>
       </c>
     </row>
     <row r="311" ht="40" customHeight="1">
       <c r="A311" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.A.polite[3].text</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-12._narration[5]</t>
         </is>
       </c>
       <c r="B311" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14-PPV・対抗戦・トーナメント</t>
+          <t xml:space="preserve">13-Glimpse Cascade</t>
         </is>
       </c>
       <c r="C311" t="inlineStr" s="2">
@@ -11415,29 +11420,24 @@
       </c>
       <c r="D311" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="E311" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A.polite[3].text</t>
-        </is>
-      </c>
-      <c r="F311" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">丁寧</t>
+          <t xml:space="preserve">GL-12._narration[5]</t>
         </is>
       </c>
       <c r="H311" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次にこの舞台が巡る時、必ずもう一度。…お願いします</t>
+          <t xml:space="preserve">{nameB}の話題が出ても、{nameA}は表情ひとつ変えなかった</t>
         </is>
       </c>
     </row>
     <row r="312" ht="40" customHeight="1">
       <c r="A312" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.B.standard[1].text</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.A.standard[1].text</t>
         </is>
       </c>
       <c r="B312" t="inlineStr" s="2">
@@ -11457,7 +11457,7 @@
       </c>
       <c r="E312" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B.standard[1].text</t>
+          <t xml:space="preserve">A.standard[1].text</t>
         </is>
       </c>
       <c r="F312" t="inlineStr" s="2">
@@ -11467,14 +11467,14 @@
       </c>
       <c r="H312" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ったけど…紙一重でした。あなたがいたから、ここまで来れた</t>
+          <t xml:space="preserve">膝が笑ってる。…でも不思議と、清々しいんです。あなたに負けたなら</t>
         </is>
       </c>
     </row>
     <row r="313" ht="40" customHeight="1">
       <c r="A313" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.B.standard[2].text</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.A.standard[2].text</t>
         </is>
       </c>
       <c r="B313" t="inlineStr" s="2">
@@ -11494,7 +11494,7 @@
       </c>
       <c r="E313" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B.standard[2].text</t>
+          <t xml:space="preserve">A.standard[2].text</t>
         </is>
       </c>
       <c r="F313" t="inlineStr" s="2">
@@ -11504,14 +11504,14 @@
       </c>
       <c r="H313" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">その拳、まだ痺れが残ってます。…また、こうやって闘いたい</t>
+          <t xml:space="preserve">最後の技、返せなかった。…認めます。今日はあなたが上でした</t>
         </is>
       </c>
     </row>
     <row r="314" ht="40" customHeight="1">
       <c r="A314" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.B.standard[3].text</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.A.standard[3].text</t>
         </is>
       </c>
       <c r="B314" t="inlineStr" s="2">
@@ -11531,7 +11531,7 @@
       </c>
       <c r="E314" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B.standard[3].text</t>
+          <t xml:space="preserve">A.standard[3].text</t>
         </is>
       </c>
       <c r="F314" t="inlineStr" s="2">
@@ -11541,14 +11541,14 @@
       </c>
       <c r="H314" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">4年後も、あなたが立ってる場所まで登ります。待っててください</t>
+          <t xml:space="preserve">4年後、同じ舞台でまた。…その時は、こんな顔で終わらせません</t>
         </is>
       </c>
     </row>
     <row r="315" ht="40" customHeight="1">
       <c r="A315" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.B.composed[1].text</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.A.composed[1].text</t>
         </is>
       </c>
       <c r="B315" t="inlineStr" s="2">
@@ -11568,7 +11568,7 @@
       </c>
       <c r="E315" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B.composed[1].text</t>
+          <t xml:space="preserve">A.composed[1].text</t>
         </is>
       </c>
       <c r="F315" t="inlineStr" s="2">
@@ -11578,14 +11578,14 @@
       </c>
       <c r="H315" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…いい試合だった。あんたのおかげだよ、正直</t>
+          <t xml:space="preserve">…参った。あんたのほうが、一枚上だったね</t>
         </is>
       </c>
     </row>
     <row r="316" ht="40" customHeight="1">
       <c r="A316" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.B.composed[2].text</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.A.composed[2].text</t>
         </is>
       </c>
       <c r="B316" t="inlineStr" s="2">
@@ -11605,7 +11605,7 @@
       </c>
       <c r="E316" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B.composed[2].text</t>
+          <t xml:space="preserve">A.composed[2].text</t>
         </is>
       </c>
       <c r="F316" t="inlineStr" s="2">
@@ -11615,14 +11615,14 @@
       </c>
       <c r="H316" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ったのに、負けた気もする。…変な感じだね</t>
+          <t xml:space="preserve">効いたよ、最後のあれ。…次は、そう簡単にはいかない</t>
         </is>
       </c>
     </row>
     <row r="317" ht="40" customHeight="1">
       <c r="A317" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.B.composed[3].text</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.A.composed[3].text</t>
         </is>
       </c>
       <c r="B317" t="inlineStr" s="2">
@@ -11642,7 +11642,7 @@
       </c>
       <c r="E317" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B.composed[3].text</t>
+          <t xml:space="preserve">A.composed[3].text</t>
         </is>
       </c>
       <c r="F317" t="inlineStr" s="2">
@@ -11652,14 +11652,14 @@
       </c>
       <c r="H317" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">また、やろう。…四年も待たせないかもしれないよ</t>
+          <t xml:space="preserve">4年か。…長いようで、すぐだ。…その時まで、覚えてて</t>
         </is>
       </c>
     </row>
     <row r="318" ht="40" customHeight="1">
       <c r="A318" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.B.ojousama[1].text</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.A.ojousama[1].text</t>
         </is>
       </c>
       <c r="B318" t="inlineStr" s="2">
@@ -11679,7 +11679,7 @@
       </c>
       <c r="E318" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B.ojousama[1].text</t>
+          <t xml:space="preserve">A.ojousama[1].text</t>
         </is>
       </c>
       <c r="F318" t="inlineStr" s="2">
@@ -11689,14 +11689,14 @@
       </c>
       <c r="H318" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝たせていただきましたわ。…あなたという好敵手あってこそ</t>
+          <t xml:space="preserve">お見事ですわ。…このわたくしを、ここまで追い込むなんて</t>
         </is>
       </c>
     </row>
     <row r="319" ht="40" customHeight="1">
       <c r="A319" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.B.ojousama[2].text</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.A.ojousama[2].text</t>
         </is>
       </c>
       <c r="B319" t="inlineStr" s="2">
@@ -11716,7 +11716,7 @@
       </c>
       <c r="E319" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B.ojousama[2].text</t>
+          <t xml:space="preserve">A.ojousama[2].text</t>
         </is>
       </c>
       <c r="F319" t="inlineStr" s="2">
@@ -11726,14 +11726,14 @@
       </c>
       <c r="H319" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、まだ膝が震えておりますの。…素敵な時間でしたわ</t>
+          <t xml:space="preserve">悔しさより、感謝が勝ちますの。…あなたと踊れて、幸せでしたわ</t>
         </is>
       </c>
     </row>
     <row r="320" ht="40" customHeight="1">
       <c r="A320" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.B.ojousama[3].text</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.A.ojousama[3].text</t>
         </is>
       </c>
       <c r="B320" t="inlineStr" s="2">
@@ -11753,7 +11753,7 @@
       </c>
       <c r="E320" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B.ojousama[3].text</t>
+          <t xml:space="preserve">A.ojousama[3].text</t>
         </is>
       </c>
       <c r="F320" t="inlineStr" s="2">
@@ -11763,14 +11763,14 @@
       </c>
       <c r="H320" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次はもっと磨いて参りますわ。あなたに、恥じないように</t>
+          <t xml:space="preserve">次の四年後、きっとお迎えに上がりますわ。…覚悟なさって</t>
         </is>
       </c>
     </row>
     <row r="321" ht="40" customHeight="1">
       <c r="A321" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.B.delinquent[1].text</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.A.delinquent[1].text</t>
         </is>
       </c>
       <c r="B321" t="inlineStr" s="2">
@@ -11790,7 +11790,7 @@
       </c>
       <c r="E321" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B.delinquent[1].text</t>
+          <t xml:space="preserve">A.delinquent[1].text</t>
         </is>
       </c>
       <c r="F321" t="inlineStr" s="2">
@@ -11800,14 +11800,14 @@
       </c>
       <c r="H321" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うっしゃあ、勝ったぜ…! あんたみてぇな強いのに勝てたんだ、今日は祝わせろよ</t>
+          <t xml:space="preserve">ちくしょう…強ぇな、あんた。参ったって言うしかねぇわ</t>
         </is>
       </c>
     </row>
     <row r="322" ht="40" customHeight="1">
       <c r="A322" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.B.delinquent[2].text</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.A.delinquent[2].text</t>
         </is>
       </c>
       <c r="B322" t="inlineStr" s="2">
@@ -11827,7 +11827,7 @@
       </c>
       <c r="E322" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B.delinquent[2].text</t>
+          <t xml:space="preserve">A.delinquent[2].text</t>
         </is>
       </c>
       <c r="F322" t="inlineStr" s="2">
@@ -11837,14 +11837,14 @@
       </c>
       <c r="H322" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">息、まだ整わねぇ。…けど、こんな相手と戦えて最高だったぜ</t>
+          <t xml:space="preserve">体、ボロボロだけど…笑っちまうな。いい試合だったろ?</t>
         </is>
       </c>
     </row>
     <row r="323" ht="40" customHeight="1">
       <c r="A323" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.B.delinquent[3].text</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.A.delinquent[3].text</t>
         </is>
       </c>
       <c r="B323" t="inlineStr" s="2">
@@ -11864,7 +11864,7 @@
       </c>
       <c r="E323" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B.delinquent[3].text</t>
+          <t xml:space="preserve">A.delinquent[3].text</t>
         </is>
       </c>
       <c r="F323" t="inlineStr" s="2">
@@ -11874,14 +11874,14 @@
       </c>
       <c r="H323" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次も来いよ。あんた相手なら、何回でも燃えるからよ</t>
+          <t xml:space="preserve">次は絶対ぶっ倒す。…って、負けたヤツが言うのもダセぇけどよ</t>
         </is>
       </c>
     </row>
     <row r="324" ht="40" customHeight="1">
       <c r="A324" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.B.cool[1].text</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.A.cool[1].text</t>
         </is>
       </c>
       <c r="B324" t="inlineStr" s="2">
@@ -11901,7 +11901,7 @@
       </c>
       <c r="E324" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B.cool[1].text</t>
+          <t xml:space="preserve">A.cool[1].text</t>
         </is>
       </c>
       <c r="F324" t="inlineStr" s="2">
@@ -11911,14 +11911,14 @@
       </c>
       <c r="H324" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……手強かった。認める</t>
+          <t xml:space="preserve">……強い。それだけだ</t>
         </is>
       </c>
     </row>
     <row r="325" ht="40" customHeight="1">
       <c r="A325" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.B.cool[2].text</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.A.cool[2].text</t>
         </is>
       </c>
       <c r="B325" t="inlineStr" s="2">
@@ -11938,7 +11938,7 @@
       </c>
       <c r="E325" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B.cool[2].text</t>
+          <t xml:space="preserve">A.cool[2].text</t>
         </is>
       </c>
       <c r="F325" t="inlineStr" s="2">
@@ -11948,14 +11948,14 @@
       </c>
       <c r="H325" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……いい目をしてた。次も、よろしく</t>
+          <t xml:space="preserve">……あの一撃、忘れない。次に返す</t>
         </is>
       </c>
     </row>
     <row r="326" ht="40" customHeight="1">
       <c r="A326" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.B.cool[3].text</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.A.cool[3].text</t>
         </is>
       </c>
       <c r="B326" t="inlineStr" s="2">
@@ -11975,7 +11975,7 @@
       </c>
       <c r="E326" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B.cool[3].text</t>
+          <t xml:space="preserve">A.cool[3].text</t>
         </is>
       </c>
       <c r="F326" t="inlineStr" s="2">
@@ -11985,14 +11985,14 @@
       </c>
       <c r="H326" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……また来い。…待ってる</t>
+          <t xml:space="preserve">……4年。…短い。すぐ、また会う</t>
         </is>
       </c>
     </row>
     <row r="327" ht="40" customHeight="1">
       <c r="A327" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.B.seductive[1].text</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.A.seductive[1].text</t>
         </is>
       </c>
       <c r="B327" t="inlineStr" s="2">
@@ -12012,7 +12012,7 @@
       </c>
       <c r="E327" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B.seductive[1].text</t>
+          <t xml:space="preserve">A.seductive[1].text</t>
         </is>
       </c>
       <c r="F327" t="inlineStr" s="2">
@@ -12022,14 +12022,14 @@
       </c>
       <c r="H327" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝っちゃったけど…惜しいわ。あなた、もっと味わいたかった</t>
+          <t xml:space="preserve">あら、負けちゃった。…でも、悪くない負け方だったわ、ふふ</t>
         </is>
       </c>
     </row>
     <row r="328" ht="40" customHeight="1">
       <c r="A328" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.B.seductive[2].text</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.A.seductive[2].text</t>
         </is>
       </c>
       <c r="B328" t="inlineStr" s="2">
@@ -12049,7 +12049,7 @@
       </c>
       <c r="E328" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B.seductive[2].text</t>
+          <t xml:space="preserve">A.seductive[2].text</t>
         </is>
       </c>
       <c r="F328" t="inlineStr" s="2">
@@ -12059,14 +12059,14 @@
       </c>
       <c r="H328" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、いい汗かかせてくれたわね。…嫌いじゃないわよ、あなた</t>
+          <t xml:space="preserve">あなたのあの目…ゾクッとしたわ。認めてあげる、今日は上手</t>
         </is>
       </c>
     </row>
     <row r="329" ht="40" customHeight="1">
       <c r="A329" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.B.seductive[3].text</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.A.seductive[3].text</t>
         </is>
       </c>
       <c r="B329" t="inlineStr" s="2">
@@ -12086,7 +12086,7 @@
       </c>
       <c r="E329" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B.seductive[3].text</t>
+          <t xml:space="preserve">A.seductive[3].text</t>
         </is>
       </c>
       <c r="F329" t="inlineStr" s="2">
@@ -12096,14 +12096,14 @@
       </c>
       <c r="H329" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次はもっと私を楽しませて。…4年後も、期待しているわ</t>
+          <t xml:space="preserve">4年後、今度は私が上に立つ。…楽しみにしてなさい?</t>
         </is>
       </c>
     </row>
     <row r="330" ht="40" customHeight="1">
       <c r="A330" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.B.polite[1].text</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.A.polite[1].text</t>
         </is>
       </c>
       <c r="B330" t="inlineStr" s="2">
@@ -12123,7 +12123,7 @@
       </c>
       <c r="E330" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B.polite[1].text</t>
+          <t xml:space="preserve">A.polite[1].text</t>
         </is>
       </c>
       <c r="F330" t="inlineStr" s="2">
@@ -12133,14 +12133,14 @@
       </c>
       <c r="H330" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝てたのは、あなたが全力でぶつかってくれたからです</t>
+          <t xml:space="preserve">完敗です。…あなたの強さ、この体でしっかり教わりました</t>
         </is>
       </c>
     </row>
     <row r="331" ht="40" customHeight="1">
       <c r="A331" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.B.polite[2].text</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.A.polite[2].text</t>
         </is>
       </c>
       <c r="B331" t="inlineStr" s="2">
@@ -12160,7 +12160,7 @@
       </c>
       <c r="E331" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B.polite[2].text</t>
+          <t xml:space="preserve">A.polite[2].text</t>
         </is>
       </c>
       <c r="F331" t="inlineStr" s="2">
@@ -12170,14 +12170,14 @@
       </c>
       <c r="H331" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ手が震えています。…それだけの相手だった、ということです</t>
+          <t xml:space="preserve">悔しさはあります。でも、それ以上に…あなたに感謝しています</t>
         </is>
       </c>
     </row>
     <row r="332" ht="40" customHeight="1">
       <c r="A332" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.B.polite[3].text</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.A.polite[3].text</t>
         </is>
       </c>
       <c r="B332" t="inlineStr" s="2">
@@ -12197,7 +12197,7 @@
       </c>
       <c r="E332" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B.polite[3].text</t>
+          <t xml:space="preserve">A.polite[3].text</t>
         </is>
       </c>
       <c r="F332" t="inlineStr" s="2">
@@ -12207,14 +12207,14 @@
       </c>
       <c r="H332" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次にお相手する時まで、もっと強くなっておきます。約束します</t>
+          <t xml:space="preserve">次にこの舞台が巡る時、必ずもう一度。…お願いします</t>
         </is>
       </c>
     </row>
     <row r="333" ht="40" customHeight="1">
       <c r="A333" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.C.standard[1].text</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.B.standard[1].text</t>
         </is>
       </c>
       <c r="B333" t="inlineStr" s="2">
@@ -12234,7 +12234,7 @@
       </c>
       <c r="E333" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">C.standard[1].text</t>
+          <t xml:space="preserve">B.standard[1].text</t>
         </is>
       </c>
       <c r="F333" t="inlineStr" s="2">
@@ -12244,14 +12244,14 @@
       </c>
       <c r="H333" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…こんな終わり方、認めない。この借りは、必ず返します</t>
+          <t xml:space="preserve">勝ったけど…紙一重でした。あなたがいたから、ここまで来れた</t>
         </is>
       </c>
     </row>
     <row r="334" ht="40" customHeight="1">
       <c r="A334" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.C.standard[2].text</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.B.standard[2].text</t>
         </is>
       </c>
       <c r="B334" t="inlineStr" s="2">
@@ -12271,7 +12271,7 @@
       </c>
       <c r="E334" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">C.standard[2].text</t>
+          <t xml:space="preserve">B.standard[2].text</t>
         </is>
       </c>
       <c r="F334" t="inlineStr" s="2">
@@ -12281,14 +12281,14 @@
       </c>
       <c r="H334" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">笑ってればいい。…今の顔、忘れませんから。次で塗り替える</t>
+          <t xml:space="preserve">その拳、まだ痺れが残ってます。…また、こうやって闘いたい</t>
         </is>
       </c>
     </row>
     <row r="335" ht="40" customHeight="1">
       <c r="A335" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.C.standard[3].text</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.B.standard[3].text</t>
         </is>
       </c>
       <c r="B335" t="inlineStr" s="2">
@@ -12308,7 +12308,7 @@
       </c>
       <c r="E335" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">C.standard[3].text</t>
+          <t xml:space="preserve">B.standard[3].text</t>
         </is>
       </c>
       <c r="F335" t="inlineStr" s="2">
@@ -12318,14 +12318,14 @@
       </c>
       <c r="H335" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">4年、待てばいい。…あなたを引きずり下ろすためだけに、鍛え直す</t>
+          <t xml:space="preserve">4年後も、あなたが立ってる場所まで登ります。待っててください</t>
         </is>
       </c>
     </row>
     <row r="336" ht="40" customHeight="1">
       <c r="A336" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.C.composed[1].text</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.B.composed[1].text</t>
         </is>
       </c>
       <c r="B336" t="inlineStr" s="2">
@@ -12345,7 +12345,7 @@
       </c>
       <c r="E336" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">C.composed[1].text</t>
+          <t xml:space="preserve">B.composed[1].text</t>
         </is>
       </c>
       <c r="F336" t="inlineStr" s="2">
@@ -12355,14 +12355,14 @@
       </c>
       <c r="H336" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…へえ。…あんたが、ね。…いいよ、覚えておく</t>
+          <t xml:space="preserve">…いい試合だった。あんたのおかげだよ、正直</t>
         </is>
       </c>
     </row>
     <row r="337" ht="40" customHeight="1">
       <c r="A337" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.C.composed[2].text</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.B.composed[2].text</t>
         </is>
       </c>
       <c r="B337" t="inlineStr" s="2">
@@ -12382,7 +12382,7 @@
       </c>
       <c r="E337" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">C.composed[2].text</t>
+          <t xml:space="preserve">B.composed[2].text</t>
         </is>
       </c>
       <c r="F337" t="inlineStr" s="2">
@@ -12392,14 +12392,14 @@
       </c>
       <c r="H337" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今は何も言わない。…次に会った時、分かるから</t>
+          <t xml:space="preserve">勝ったのに、負けた気もする。…変な感じだね</t>
         </is>
       </c>
     </row>
     <row r="338" ht="40" customHeight="1">
       <c r="A338" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.C.composed[3].text</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.B.composed[3].text</t>
         </is>
       </c>
       <c r="B338" t="inlineStr" s="2">
@@ -12419,7 +12419,7 @@
       </c>
       <c r="E338" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">C.composed[3].text</t>
+          <t xml:space="preserve">B.composed[3].text</t>
         </is>
       </c>
       <c r="F338" t="inlineStr" s="2">
@@ -12429,14 +12429,14 @@
       </c>
       <c r="H338" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">4年後。…その澄ました顔、崩してあげる。…楽しみにしてて</t>
+          <t xml:space="preserve">また、やろう。…四年も待たせないかもしれないよ</t>
         </is>
       </c>
     </row>
     <row r="339" ht="40" customHeight="1">
       <c r="A339" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.C.ojousama[1].text</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.B.ojousama[1].text</t>
         </is>
       </c>
       <c r="B339" t="inlineStr" s="2">
@@ -12456,7 +12456,7 @@
       </c>
       <c r="E339" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">C.ojousama[1].text</t>
+          <t xml:space="preserve">B.ojousama[1].text</t>
         </is>
       </c>
       <c r="F339" t="inlineStr" s="2">
@@ -12466,14 +12466,14 @@
       </c>
       <c r="H339" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら…このわたくしに恥をかかせて。…その罪、高くつきましてよ</t>
+          <t xml:space="preserve">勝たせていただきましたわ。…あなたという好敵手あってこそ</t>
         </is>
       </c>
     </row>
     <row r="340" ht="40" customHeight="1">
       <c r="A340" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.C.ojousama[2].text</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.B.ojousama[2].text</t>
         </is>
       </c>
       <c r="B340" t="inlineStr" s="2">
@@ -12493,7 +12493,7 @@
       </c>
       <c r="E340" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">C.ojousama[2].text</t>
+          <t xml:space="preserve">B.ojousama[2].text</t>
         </is>
       </c>
       <c r="F340" t="inlineStr" s="2">
@@ -12503,14 +12503,14 @@
       </c>
       <c r="H340" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日は差し上げますわ。…でも次は、あなたの全てを頂きますの</t>
+          <t xml:space="preserve">ふふ、まだ膝が震えておりますの。…素敵な時間でしたわ</t>
         </is>
       </c>
     </row>
     <row r="341" ht="40" customHeight="1">
       <c r="A341" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.C.ojousama[3].text</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.B.ojousama[3].text</t>
         </is>
       </c>
       <c r="B341" t="inlineStr" s="2">
@@ -12530,7 +12530,7 @@
       </c>
       <c r="E341" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">C.ojousama[3].text</t>
+          <t xml:space="preserve">B.ojousama[3].text</t>
         </is>
       </c>
       <c r="F341" t="inlineStr" s="2">
@@ -12540,14 +12540,14 @@
       </c>
       <c r="H341" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ…笑っていられるのも今のうち。…わたくし、執念深いのですわ</t>
+          <t xml:space="preserve">次はもっと磨いて参りますわ。あなたに、恥じないように</t>
         </is>
       </c>
     </row>
     <row r="342" ht="40" customHeight="1">
       <c r="A342" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.C.delinquent[1].text</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.B.delinquent[1].text</t>
         </is>
       </c>
       <c r="B342" t="inlineStr" s="2">
@@ -12567,7 +12567,7 @@
       </c>
       <c r="E342" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">C.delinquent[1].text</t>
+          <t xml:space="preserve">B.delinquent[1].text</t>
         </is>
       </c>
       <c r="F342" t="inlineStr" s="2">
@@ -12577,14 +12577,14 @@
       </c>
       <c r="H342" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…上等だよ。よくもやってくれたな。この落とし前、必ずつけさせる</t>
+          <t xml:space="preserve">うっしゃあ、勝ったぜ…! あんたみてぇな強いのに勝てたんだ、今日は祝わせろよ</t>
         </is>
       </c>
     </row>
     <row r="343" ht="40" customHeight="1">
       <c r="A343" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.C.delinquent[2].text</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.B.delinquent[2].text</t>
         </is>
       </c>
       <c r="B343" t="inlineStr" s="2">
@@ -12604,7 +12604,7 @@
       </c>
       <c r="E343" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">C.delinquent[2].text</t>
+          <t xml:space="preserve">B.delinquent[2].text</t>
         </is>
       </c>
       <c r="F343" t="inlineStr" s="2">
@@ -12614,14 +12614,14 @@
       </c>
       <c r="H343" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日のこと、一生忘れねぇからな。…次はテメェが地面舐める番だ</t>
+          <t xml:space="preserve">息、まだ整わねぇ。…けど、こんな相手と戦えて最高だったぜ</t>
         </is>
       </c>
     </row>
     <row r="344" ht="40" customHeight="1">
       <c r="A344" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.C.delinquent[3].text</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.B.delinquent[3].text</t>
         </is>
       </c>
       <c r="B344" t="inlineStr" s="2">
@@ -12641,7 +12641,7 @@
       </c>
       <c r="E344" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">C.delinquent[3].text</t>
+          <t xml:space="preserve">B.delinquent[3].text</t>
         </is>
       </c>
       <c r="F344" t="inlineStr" s="2">
@@ -12651,14 +12651,14 @@
       </c>
       <c r="H344" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">4年? 上等だ。それまで、あんたをぶっ潰すことだけ考えてやるよ</t>
+          <t xml:space="preserve">次も来いよ。あんた相手なら、何回でも燃えるからよ</t>
         </is>
       </c>
     </row>
     <row r="345" ht="40" customHeight="1">
       <c r="A345" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.C.cool[1].text</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.B.cool[1].text</t>
         </is>
       </c>
       <c r="B345" t="inlineStr" s="2">
@@ -12678,7 +12678,7 @@
       </c>
       <c r="E345" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">C.cool[1].text</t>
+          <t xml:space="preserve">B.cool[1].text</t>
         </is>
       </c>
       <c r="F345" t="inlineStr" s="2">
@@ -12688,14 +12688,14 @@
       </c>
       <c r="H345" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……忘れない。この屈辱は</t>
+          <t xml:space="preserve">……手強かった。認める</t>
         </is>
       </c>
     </row>
     <row r="346" ht="40" customHeight="1">
       <c r="A346" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.C.cool[2].text</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.B.cool[2].text</t>
         </is>
       </c>
       <c r="B346" t="inlineStr" s="2">
@@ -12715,7 +12715,7 @@
       </c>
       <c r="E346" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">C.cool[2].text</t>
+          <t xml:space="preserve">B.cool[2].text</t>
         </is>
       </c>
       <c r="F346" t="inlineStr" s="2">
@@ -12725,14 +12725,14 @@
       </c>
       <c r="H346" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……次は、無い。お前が落ちる番だ</t>
+          <t xml:space="preserve">……いい目をしてた。次も、よろしく</t>
         </is>
       </c>
     </row>
     <row r="347" ht="40" customHeight="1">
       <c r="A347" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.C.cool[3].text</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.B.cool[3].text</t>
         </is>
       </c>
       <c r="B347" t="inlineStr" s="2">
@@ -12752,7 +12752,7 @@
       </c>
       <c r="E347" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">C.cool[3].text</t>
+          <t xml:space="preserve">B.cool[3].text</t>
         </is>
       </c>
       <c r="F347" t="inlineStr" s="2">
@@ -12762,14 +12762,14 @@
       </c>
       <c r="H347" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……4年。…お前を壊すには、十分すぎる</t>
+          <t xml:space="preserve">……また来い。…待ってる</t>
         </is>
       </c>
     </row>
     <row r="348" ht="40" customHeight="1">
       <c r="A348" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.C.seductive[1].text</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.B.seductive[1].text</t>
         </is>
       </c>
       <c r="B348" t="inlineStr" s="2">
@@ -12789,7 +12789,7 @@
       </c>
       <c r="E348" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">C.seductive[1].text</t>
+          <t xml:space="preserve">B.seductive[1].text</t>
         </is>
       </c>
       <c r="F348" t="inlineStr" s="2">
@@ -12799,14 +12799,14 @@
       </c>
       <c r="H348" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら…ずいぶん派手にやってくれたわね。…その借り、体で払ってもらう</t>
+          <t xml:space="preserve">勝っちゃったけど…惜しいわ。あなた、もっと味わいたかった</t>
         </is>
       </c>
     </row>
     <row r="349" ht="40" customHeight="1">
       <c r="A349" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.C.seductive[2].text</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.B.seductive[2].text</t>
         </is>
       </c>
       <c r="B349" t="inlineStr" s="2">
@@ -12826,7 +12826,7 @@
       </c>
       <c r="E349" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">C.seductive[2].text</t>
+          <t xml:space="preserve">B.seductive[2].text</t>
         </is>
       </c>
       <c r="F349" t="inlineStr" s="2">
@@ -12836,14 +12836,14 @@
       </c>
       <c r="H349" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ…今夜は眠れそうにないわ。あなたを堕とす方法、考えてて</t>
+          <t xml:space="preserve">ふふ、いい汗かかせてくれたわね。…嫌いじゃないわよ、あなた</t>
         </is>
       </c>
     </row>
     <row r="350" ht="40" customHeight="1">
       <c r="A350" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.C.seductive[3].text</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.B.seductive[3].text</t>
         </is>
       </c>
       <c r="B350" t="inlineStr" s="2">
@@ -12863,7 +12863,7 @@
       </c>
       <c r="E350" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">C.seductive[3].text</t>
+          <t xml:space="preserve">B.seductive[3].text</t>
         </is>
       </c>
       <c r="F350" t="inlineStr" s="2">
@@ -12873,14 +12873,14 @@
       </c>
       <c r="H350" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">逃がさないわよ。…4年でも、その先でも。…私、諦めが悪いの</t>
+          <t xml:space="preserve">次はもっと私を楽しませて。…4年後も、期待しているわ</t>
         </is>
       </c>
     </row>
     <row r="351" ht="40" customHeight="1">
       <c r="A351" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.C.polite[1].text</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.B.polite[1].text</t>
         </is>
       </c>
       <c r="B351" t="inlineStr" s="2">
@@ -12900,7 +12900,7 @@
       </c>
       <c r="E351" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">C.polite[1].text</t>
+          <t xml:space="preserve">B.polite[1].text</t>
         </is>
       </c>
       <c r="F351" t="inlineStr" s="2">
@@ -12910,14 +12910,14 @@
       </c>
       <c r="H351" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…結構なお手前でした。この屈辱、丁寧にお返しいたします</t>
+          <t xml:space="preserve">勝てたのは、あなたが全力でぶつかってくれたからです</t>
         </is>
       </c>
     </row>
     <row r="352" ht="40" customHeight="1">
       <c r="A352" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.C.polite[2].text</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.B.polite[2].text</t>
         </is>
       </c>
       <c r="B352" t="inlineStr" s="2">
@@ -12937,7 +12937,7 @@
       </c>
       <c r="E352" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">C.polite[2].text</t>
+          <t xml:space="preserve">B.polite[2].text</t>
         </is>
       </c>
       <c r="F352" t="inlineStr" s="2">
@@ -12947,14 +12947,14 @@
       </c>
       <c r="H352" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日のこと、感謝します。…あなたを倒す理由を、いただきました</t>
+          <t xml:space="preserve">まだ手が震えています。…それだけの相手だった、ということです</t>
         </is>
       </c>
     </row>
     <row r="353" ht="40" customHeight="1">
       <c r="A353" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.C.polite[3].text</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.B.polite[3].text</t>
         </is>
       </c>
       <c r="B353" t="inlineStr" s="2">
@@ -12974,7 +12974,7 @@
       </c>
       <c r="E353" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">C.polite[3].text</t>
+          <t xml:space="preserve">B.polite[3].text</t>
         </is>
       </c>
       <c r="F353" t="inlineStr" s="2">
@@ -12984,14 +12984,14 @@
       </c>
       <c r="H353" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次にお会いする時を、心待ちにしています。…覚悟しておいてください</t>
+          <t xml:space="preserve">次にお相手する時まで、もっと強くなっておきます。約束します</t>
         </is>
       </c>
     </row>
     <row r="354" ht="40" customHeight="1">
       <c r="A354" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.D.standard[1].text</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.C.standard[1].text</t>
         </is>
       </c>
       <c r="B354" t="inlineStr" s="2">
@@ -13011,7 +13011,7 @@
       </c>
       <c r="E354" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">D.standard[1].text</t>
+          <t xml:space="preserve">C.standard[1].text</t>
         </is>
       </c>
       <c r="F354" t="inlineStr" s="2">
@@ -13021,14 +13021,14 @@
       </c>
       <c r="H354" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…おめでとう。…ごめん、今はうまく笑えそうにないです</t>
+          <t xml:space="preserve">…こんな終わり方、認めない。この借りは、必ず返します</t>
         </is>
       </c>
     </row>
     <row r="355" ht="40" customHeight="1">
       <c r="A355" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.D.standard[2].text</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.C.standard[2].text</t>
         </is>
       </c>
       <c r="B355" t="inlineStr" s="2">
@@ -13048,7 +13048,7 @@
       </c>
       <c r="E355" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">D.standard[2].text</t>
+          <t xml:space="preserve">C.standard[2].text</t>
         </is>
       </c>
       <c r="F355" t="inlineStr" s="2">
@@ -13058,14 +13058,14 @@
       </c>
       <c r="H355" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">おめでとうって、ちゃんと言えたかな。…自分の声じゃないみたいだった</t>
+          <t xml:space="preserve">笑ってればいい。…今の顔、忘れませんから。次で塗り替える</t>
         </is>
       </c>
     </row>
     <row r="356" ht="40" customHeight="1">
       <c r="A356" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.D.composed[1].text</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.C.standard[3].text</t>
         </is>
       </c>
       <c r="B356" t="inlineStr" s="2">
@@ -13085,24 +13085,24 @@
       </c>
       <c r="E356" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">D.composed[1].text</t>
+          <t xml:space="preserve">C.standard[3].text</t>
         </is>
       </c>
       <c r="F356" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">鷹揚</t>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="H356" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…おめでとう。…ちょっと、今は顔を見たくないかな</t>
+          <t xml:space="preserve">4年、待てばいい。…あなたを引きずり下ろすためだけに、鍛え直す</t>
         </is>
       </c>
     </row>
     <row r="357" ht="40" customHeight="1">
       <c r="A357" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.D.composed[2].text</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.C.composed[1].text</t>
         </is>
       </c>
       <c r="B357" t="inlineStr" s="2">
@@ -13122,7 +13122,7 @@
       </c>
       <c r="E357" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">D.composed[2].text</t>
+          <t xml:space="preserve">C.composed[1].text</t>
         </is>
       </c>
       <c r="F357" t="inlineStr" s="2">
@@ -13132,14 +13132,14 @@
       </c>
       <c r="H357" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…いい試合だった。…それ以上は、今日は勘弁して</t>
+          <t xml:space="preserve">…へえ。…あんたが、ね。…いいよ、覚えておく</t>
         </is>
       </c>
     </row>
     <row r="358" ht="40" customHeight="1">
       <c r="A358" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.D.ojousama[1].text</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.C.composed[2].text</t>
         </is>
       </c>
       <c r="B358" t="inlineStr" s="2">
@@ -13159,24 +13159,24 @@
       </c>
       <c r="E358" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">D.ojousama[1].text</t>
+          <t xml:space="preserve">C.composed[2].text</t>
         </is>
       </c>
       <c r="F358" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">お嬢様</t>
+          <t xml:space="preserve">鷹揚</t>
         </is>
       </c>
       <c r="H358" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">おめでとうございますわ。…少し、距離を置かせてくださいまし</t>
+          <t xml:space="preserve">今は何も言わない。…次に会った時、分かるから</t>
         </is>
       </c>
     </row>
     <row r="359" ht="40" customHeight="1">
       <c r="A359" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.D.ojousama[2].text</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.C.composed[3].text</t>
         </is>
       </c>
       <c r="B359" t="inlineStr" s="2">
@@ -13196,24 +13196,24 @@
       </c>
       <c r="E359" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">D.ojousama[2].text</t>
+          <t xml:space="preserve">C.composed[3].text</t>
         </is>
       </c>
       <c r="F359" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">お嬢様</t>
+          <t xml:space="preserve">鷹揚</t>
         </is>
       </c>
       <c r="H359" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">祝福は、いたしましたわ。…それ以上を求めるのは、酷というものですわ</t>
+          <t xml:space="preserve">4年後。…その澄ました顔、崩してあげる。…楽しみにしてて</t>
         </is>
       </c>
     </row>
     <row r="360" ht="40" customHeight="1">
       <c r="A360" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.D.delinquent[1].text</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.C.ojousama[1].text</t>
         </is>
       </c>
       <c r="B360" t="inlineStr" s="2">
@@ -13233,24 +13233,24 @@
       </c>
       <c r="E360" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">D.delinquent[1].text</t>
+          <t xml:space="preserve">C.ojousama[1].text</t>
         </is>
       </c>
       <c r="F360" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ヤンキー</t>
+          <t xml:space="preserve">お嬢様</t>
         </is>
       </c>
       <c r="H360" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…おう、勝ったな。おめでとよ。…悪ぃ、今は一人にしてくれ</t>
+          <t xml:space="preserve">あら…このわたくしに恥をかかせて。…その罪、高くつきましてよ</t>
         </is>
       </c>
     </row>
     <row r="361" ht="40" customHeight="1">
       <c r="A361" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.D.delinquent[2].text</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.C.ojousama[2].text</t>
         </is>
       </c>
       <c r="B361" t="inlineStr" s="2">
@@ -13270,24 +13270,24 @@
       </c>
       <c r="E361" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">D.delinquent[2].text</t>
+          <t xml:space="preserve">C.ojousama[2].text</t>
         </is>
       </c>
       <c r="F361" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ヤンキー</t>
+          <t xml:space="preserve">お嬢様</t>
         </is>
       </c>
       <c r="H361" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ちゃんと祝ってやりてぇのによ。喉の奥に、何かつっかえてんだわ</t>
+          <t xml:space="preserve">今日は差し上げますわ。…でも次は、あなたの全てを頂きますの</t>
         </is>
       </c>
     </row>
     <row r="362" ht="40" customHeight="1">
       <c r="A362" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.D.cool[1].text</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.C.ojousama[3].text</t>
         </is>
       </c>
       <c r="B362" t="inlineStr" s="2">
@@ -13307,24 +13307,24 @@
       </c>
       <c r="E362" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">D.cool[1].text</t>
+          <t xml:space="preserve">C.ojousama[3].text</t>
         </is>
       </c>
       <c r="F362" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">クール</t>
+          <t xml:space="preserve">お嬢様</t>
         </is>
       </c>
       <c r="H362" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……おめでとう。…今は、話しかけないで</t>
+          <t xml:space="preserve">ふふ…笑っていられるのも今のうち。…わたくし、執念深いのですわ</t>
         </is>
       </c>
     </row>
     <row r="363" ht="40" customHeight="1">
       <c r="A363" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.D.cool[2].text</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.C.delinquent[1].text</t>
         </is>
       </c>
       <c r="B363" t="inlineStr" s="2">
@@ -13344,24 +13344,24 @@
       </c>
       <c r="E363" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">D.cool[2].text</t>
+          <t xml:space="preserve">C.delinquent[1].text</t>
         </is>
       </c>
       <c r="F363" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">クール</t>
+          <t xml:space="preserve">ヤンキー</t>
         </is>
       </c>
       <c r="H363" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……祝った。…それで、十分だろう</t>
+          <t xml:space="preserve">…上等だよ。よくもやってくれたな。この落とし前、必ずつけさせる</t>
         </is>
       </c>
     </row>
     <row r="364" ht="40" customHeight="1">
       <c r="A364" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.D.seductive[1].text</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.C.delinquent[2].text</t>
         </is>
       </c>
       <c r="B364" t="inlineStr" s="2">
@@ -13381,24 +13381,24 @@
       </c>
       <c r="E364" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">D.seductive[1].text</t>
+          <t xml:space="preserve">C.delinquent[2].text</t>
         </is>
       </c>
       <c r="F364" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">蠱惑</t>
+          <t xml:space="preserve">ヤンキー</t>
         </is>
       </c>
       <c r="H364" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">おめでとう。…ふふ、笑ってるでしょ? …無理してるの、バレバレよ</t>
+          <t xml:space="preserve">今日のこと、一生忘れねぇからな。…次はテメェが地面舐める番だ</t>
         </is>
       </c>
     </row>
     <row r="365" ht="40" customHeight="1">
       <c r="A365" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.D.seductive[2].text</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.C.delinquent[3].text</t>
         </is>
       </c>
       <c r="B365" t="inlineStr" s="2">
@@ -13418,24 +13418,24 @@
       </c>
       <c r="E365" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">D.seductive[2].text</t>
+          <t xml:space="preserve">C.delinquent[3].text</t>
         </is>
       </c>
       <c r="F365" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">蠱惑</t>
+          <t xml:space="preserve">ヤンキー</t>
         </is>
       </c>
       <c r="H365" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、おめでとう。…あら。私、ちゃんと笑えてるかしら</t>
+          <t xml:space="preserve">4年? 上等だ。それまで、あんたをぶっ潰すことだけ考えてやるよ</t>
         </is>
       </c>
     </row>
     <row r="366" ht="40" customHeight="1">
       <c r="A366" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.D.polite[1].text</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.C.cool[1].text</t>
         </is>
       </c>
       <c r="B366" t="inlineStr" s="2">
@@ -13455,24 +13455,24 @@
       </c>
       <c r="E366" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">D.polite[1].text</t>
+          <t xml:space="preserve">C.cool[1].text</t>
         </is>
       </c>
       <c r="F366" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">丁寧</t>
+          <t xml:space="preserve">クール</t>
         </is>
       </c>
       <c r="H366" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">おめでとうございます。…すみません、今日は先に上がらせてください</t>
+          <t xml:space="preserve">……忘れない。この屈辱は</t>
         </is>
       </c>
     </row>
     <row r="367" ht="40" customHeight="1">
       <c r="A367" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.D.polite[2].text</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.C.cool[2].text</t>
         </is>
       </c>
       <c r="B367" t="inlineStr" s="2">
@@ -13492,24 +13492,24 @@
       </c>
       <c r="E367" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">D.polite[2].text</t>
+          <t xml:space="preserve">C.cool[2].text</t>
         </is>
       </c>
       <c r="F367" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">丁寧</t>
+          <t xml:space="preserve">クール</t>
         </is>
       </c>
       <c r="H367" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">おめでとうございます、心からそう思っています。…思って、いるんです</t>
+          <t xml:space="preserve">……次は、無い。お前が落ちる番だ</t>
         </is>
       </c>
     </row>
     <row r="368" ht="40" customHeight="1">
       <c r="A368" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.E.standard[1].text</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.C.cool[3].text</t>
         </is>
       </c>
       <c r="B368" t="inlineStr" s="2">
@@ -13529,24 +13529,24 @@
       </c>
       <c r="E368" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E.standard[1].text</t>
+          <t xml:space="preserve">C.cool[3].text</t>
         </is>
       </c>
       <c r="F368" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">標準</t>
+          <t xml:space="preserve">クール</t>
         </is>
       </c>
       <c r="H368" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けたけど…同じ団体に、こんな強い人がいて嬉しいです</t>
+          <t xml:space="preserve">……4年。…お前を壊すには、十分すぎる</t>
         </is>
       </c>
     </row>
     <row r="369" ht="40" customHeight="1">
       <c r="A369" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.E.standard[2].text</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.C.seductive[1].text</t>
         </is>
       </c>
       <c r="B369" t="inlineStr" s="2">
@@ -13566,24 +13566,24 @@
       </c>
       <c r="E369" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E.standard[2].text</t>
+          <t xml:space="preserve">C.seductive[1].text</t>
         </is>
       </c>
       <c r="F369" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">標準</t>
+          <t xml:space="preserve">蠱惑</t>
         </is>
       </c>
       <c r="H369" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しい。…でも、あなたが上に行くなら、背中は私が守ります</t>
+          <t xml:space="preserve">あら…ずいぶん派手にやってくれたわね。…その借り、体で払ってもらう</t>
         </is>
       </c>
     </row>
     <row r="370" ht="40" customHeight="1">
       <c r="A370" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.E.composed[1].text</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.C.seductive[2].text</t>
         </is>
       </c>
       <c r="B370" t="inlineStr" s="2">
@@ -13603,24 +13603,24 @@
       </c>
       <c r="E370" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E.composed[1].text</t>
+          <t xml:space="preserve">C.seductive[2].text</t>
         </is>
       </c>
       <c r="F370" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">鷹揚</t>
+          <t xml:space="preserve">蠱惑</t>
         </is>
       </c>
       <c r="H370" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…参ったよ。…けど、あんたが仲間で良かった。本気でそう思う</t>
+          <t xml:space="preserve">ふふ…今夜は眠れそうにないわ。あなたを堕とす方法、考えてて</t>
         </is>
       </c>
     </row>
     <row r="371" ht="40" customHeight="1">
       <c r="A371" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.E.composed[2].text</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.C.seductive[3].text</t>
         </is>
       </c>
       <c r="B371" t="inlineStr" s="2">
@@ -13640,24 +13640,24 @@
       </c>
       <c r="E371" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E.composed[2].text</t>
+          <t xml:space="preserve">C.seductive[3].text</t>
         </is>
       </c>
       <c r="F371" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">鷹揚</t>
+          <t xml:space="preserve">蠱惑</t>
         </is>
       </c>
       <c r="H371" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">同じ看板を背負う相手が強い。…悪くない、むしろ誇らしいね</t>
+          <t xml:space="preserve">逃がさないわよ。…4年でも、その先でも。…私、諦めが悪いの</t>
         </is>
       </c>
     </row>
     <row r="372" ht="40" customHeight="1">
       <c r="A372" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.E.ojousama[1].text</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.C.polite[1].text</t>
         </is>
       </c>
       <c r="B372" t="inlineStr" s="2">
@@ -13677,24 +13677,24 @@
       </c>
       <c r="E372" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E.ojousama[1].text</t>
+          <t xml:space="preserve">C.polite[1].text</t>
         </is>
       </c>
       <c r="F372" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">お嬢様</t>
+          <t xml:space="preserve">丁寧</t>
         </is>
       </c>
       <c r="H372" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">見事でしたわ。…同じ団体に、あなたがいる幸せを噛みしめておりますの</t>
+          <t xml:space="preserve">…結構なお手前でした。この屈辱、丁寧にお返しいたします</t>
         </is>
       </c>
     </row>
     <row r="373" ht="40" customHeight="1">
       <c r="A373" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.E.ojousama[2].text</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.C.polite[2].text</t>
         </is>
       </c>
       <c r="B373" t="inlineStr" s="2">
@@ -13714,24 +13714,24 @@
       </c>
       <c r="E373" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E.ojousama[2].text</t>
+          <t xml:space="preserve">C.polite[2].text</t>
         </is>
       </c>
       <c r="F373" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">お嬢様</t>
+          <t xml:space="preserve">丁寧</t>
         </is>
       </c>
       <c r="H373" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しさの奥に、誇りがありますわ。…あなたと同じ旗の下で、良かった</t>
+          <t xml:space="preserve">今日のこと、感謝します。…あなたを倒す理由を、いただきました</t>
         </is>
       </c>
     </row>
     <row r="374" ht="40" customHeight="1">
       <c r="A374" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.E.delinquent[1].text</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.C.polite[3].text</t>
         </is>
       </c>
       <c r="B374" t="inlineStr" s="2">
@@ -13751,24 +13751,24 @@
       </c>
       <c r="E374" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E.delinquent[1].text</t>
+          <t xml:space="preserve">C.polite[3].text</t>
         </is>
       </c>
       <c r="F374" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ヤンキー</t>
+          <t xml:space="preserve">丁寧</t>
         </is>
       </c>
       <c r="H374" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">クソ、負けた…けど、あんたが身内で良かったって心底思うわ</t>
+          <t xml:space="preserve">次にお会いする時を、心待ちにしています。…覚悟しておいてください</t>
         </is>
       </c>
     </row>
     <row r="375" ht="40" customHeight="1">
       <c r="A375" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.E.delinquent[2].text</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.D.standard[1].text</t>
         </is>
       </c>
       <c r="B375" t="inlineStr" s="2">
@@ -13788,24 +13788,24 @@
       </c>
       <c r="E375" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E.delinquent[2].text</t>
+          <t xml:space="preserve">D.standard[1].text</t>
         </is>
       </c>
       <c r="F375" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ヤンキー</t>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="H375" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">同じチームにこんな怪物がいるとか、最高じゃねぇか。…惚れ直したぜ</t>
+          <t xml:space="preserve">…おめでとう。…ごめん、今はうまく笑えそうにないです</t>
         </is>
       </c>
     </row>
     <row r="376" ht="40" customHeight="1">
       <c r="A376" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.E.cool[1].text</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.D.standard[2].text</t>
         </is>
       </c>
       <c r="B376" t="inlineStr" s="2">
@@ -13825,24 +13825,24 @@
       </c>
       <c r="E376" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E.cool[1].text</t>
+          <t xml:space="preserve">D.standard[2].text</t>
         </is>
       </c>
       <c r="F376" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">クール</t>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="H376" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……強い。仲間として、誇らしい</t>
+          <t xml:space="preserve">おめでとうって、ちゃんと言えたかな。…自分の声じゃないみたいだった</t>
         </is>
       </c>
     </row>
     <row r="377" ht="40" customHeight="1">
       <c r="A377" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.E.cool[2].text</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.D.composed[1].text</t>
         </is>
       </c>
       <c r="B377" t="inlineStr" s="2">
@@ -13862,24 +13862,24 @@
       </c>
       <c r="E377" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E.cool[2].text</t>
+          <t xml:space="preserve">D.composed[1].text</t>
         </is>
       </c>
       <c r="F377" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">クール</t>
+          <t xml:space="preserve">鷹揚</t>
         </is>
       </c>
       <c r="H377" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……負けた。…でも、お前が同じ旗の下でよかった</t>
+          <t xml:space="preserve">…おめでとう。…ちょっと、今は顔を見たくないかな</t>
         </is>
       </c>
     </row>
     <row r="378" ht="40" customHeight="1">
       <c r="A378" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.E.seductive[1].text</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.D.composed[2].text</t>
         </is>
       </c>
       <c r="B378" t="inlineStr" s="2">
@@ -13899,24 +13899,24 @@
       </c>
       <c r="E378" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E.seductive[1].text</t>
+          <t xml:space="preserve">D.composed[2].text</t>
         </is>
       </c>
       <c r="F378" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">蠱惑</t>
+          <t xml:space="preserve">鷹揚</t>
         </is>
       </c>
       <c r="H378" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けちゃったけど…同じ団体にあなたがいるの、悪くないわ、ふふ</t>
+          <t xml:space="preserve">…いい試合だった。…それ以上は、今日は勘弁して</t>
         </is>
       </c>
     </row>
     <row r="379" ht="40" customHeight="1">
       <c r="A379" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.E.seductive[2].text</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.D.ojousama[1].text</t>
         </is>
       </c>
       <c r="B379" t="inlineStr" s="2">
@@ -13936,24 +13936,24 @@
       </c>
       <c r="E379" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E.seductive[2].text</t>
+          <t xml:space="preserve">D.ojousama[1].text</t>
         </is>
       </c>
       <c r="F379" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">蠱惑</t>
+          <t xml:space="preserve">お嬢様</t>
         </is>
       </c>
       <c r="H379" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しいのに、なぜかドキドキしてる。…同志にしておくには、惜しい人</t>
+          <t xml:space="preserve">おめでとうございますわ。…少し、距離を置かせてくださいまし</t>
         </is>
       </c>
     </row>
     <row r="380" ht="40" customHeight="1">
       <c r="A380" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.E.polite[1].text</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.D.ojousama[2].text</t>
         </is>
       </c>
       <c r="B380" t="inlineStr" s="2">
@@ -13973,24 +13973,24 @@
       </c>
       <c r="E380" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E.polite[1].text</t>
+          <t xml:space="preserve">D.ojousama[2].text</t>
         </is>
       </c>
       <c r="F380" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">丁寧</t>
+          <t xml:space="preserve">お嬢様</t>
         </is>
       </c>
       <c r="H380" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">完敗です。…でも、あなたと同じ団体でいられることを、誇りに思います</t>
+          <t xml:space="preserve">祝福は、いたしましたわ。…それ以上を求めるのは、酷というものですわ</t>
         </is>
       </c>
     </row>
     <row r="381" ht="40" customHeight="1">
       <c r="A381" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.E.polite[2].text</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.D.delinquent[1].text</t>
         </is>
       </c>
       <c r="B381" t="inlineStr" s="2">
@@ -14010,24 +14010,24 @@
       </c>
       <c r="E381" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E.polite[2].text</t>
+          <t xml:space="preserve">D.delinquent[1].text</t>
         </is>
       </c>
       <c r="F381" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">丁寧</t>
+          <t xml:space="preserve">ヤンキー</t>
         </is>
       </c>
       <c r="H381" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けて、むしろ嬉しいんです。…あなたの背中を追える意味が、わかった</t>
+          <t xml:space="preserve">…おう、勝ったな。おめでとよ。…悪ぃ、今は一人にしてくれ</t>
         </is>
       </c>
     </row>
     <row r="382" ht="40" customHeight="1">
       <c r="A382" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES.coach.sparta[1]</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.D.delinquent[2].text</t>
         </is>
       </c>
       <c r="B382" t="inlineStr" s="2">
@@ -14042,24 +14042,29 @@
       </c>
       <c r="D382" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES</t>
         </is>
       </c>
       <c r="E382" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">coach.sparta[1]</t>
+          <t xml:space="preserve">D.delinquent[2].text</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ヤンキー</t>
         </is>
       </c>
       <c r="H382" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、いよいよですな。四年に一度のあの舞台——うちの子らを鍛え上げてきた、その成果を全部ぶつけさせてもらう</t>
+          <t xml:space="preserve">…ちゃんと祝ってやりてぇのによ。喉の奥に、何かつっかえてんだわ</t>
         </is>
       </c>
     </row>
     <row r="383" ht="40" customHeight="1">
       <c r="A383" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES.coach.sparta[2]</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.D.cool[1].text</t>
         </is>
       </c>
       <c r="B383" t="inlineStr" s="2">
@@ -14074,24 +14079,29 @@
       </c>
       <c r="D383" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES</t>
         </is>
       </c>
       <c r="E383" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">coach.sparta[2]</t>
+          <t xml:space="preserve">D.cool[1].text</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">クール</t>
         </is>
       </c>
       <c r="H383" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この日のために汗を絞ってきたんだ。逃げも隠れもできん、剥き出しの真剣勝負の場。社長、存分に暴れさせてやってくれ</t>
+          <t xml:space="preserve">……おめでとう。…今は、話しかけないで</t>
         </is>
       </c>
     </row>
     <row r="384" ht="40" customHeight="1">
       <c r="A384" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES.coach.theorist[1]</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.D.cool[2].text</t>
         </is>
       </c>
       <c r="B384" t="inlineStr" s="2">
@@ -14106,24 +14116,29 @@
       </c>
       <c r="D384" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES</t>
         </is>
       </c>
       <c r="E384" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">coach.theorist[1]</t>
+          <t xml:space="preserve">D.cool[2].text</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">クール</t>
         </is>
       </c>
       <c r="H384" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、エントリーの顔ぶれが読めてきました。他団体の主力データ、粗方は揃っています。…付け入る隙は、必ずありますよ</t>
+          <t xml:space="preserve">……祝った。…それで、十分だろう</t>
         </is>
       </c>
     </row>
     <row r="385" ht="40" customHeight="1">
       <c r="A385" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES.coach.theorist[2]</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.D.seductive[1].text</t>
         </is>
       </c>
       <c r="B385" t="inlineStr" s="2">
@@ -14138,24 +14153,29 @@
       </c>
       <c r="D385" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES</t>
         </is>
       </c>
       <c r="E385" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">coach.theorist[2]</t>
+          <t xml:space="preserve">D.seductive[1].text</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">蠱惑</t>
         </is>
       </c>
       <c r="H385" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">四年に一度、最強を決める舞台です。各団体の戦力を並べて見ると、社長、うちにも勝ち筋は描ける。数字がそう言っています</t>
+          <t xml:space="preserve">おめでとう。…ふふ、笑ってるでしょ? …無理してるの、バレバレよ</t>
         </is>
       </c>
     </row>
     <row r="386" ht="40" customHeight="1">
       <c r="A386" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES.coach.artisan[1]</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.D.seductive[2].text</t>
         </is>
       </c>
       <c r="B386" t="inlineStr" s="2">
@@ -14170,24 +14190,29 @@
       </c>
       <c r="D386" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES</t>
         </is>
       </c>
       <c r="E386" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">coach.artisan[1]</t>
+          <t xml:space="preserve">D.seductive[2].text</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">蠱惑</t>
         </is>
       </c>
       <c r="H386" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長……来ましたな、四年に一度が。あそこは小手先の通じん舞台だ。磨き上げてきた技が本物かどうか——問われるのは、それだけです</t>
+          <t xml:space="preserve">ふふ、おめでとう。…あら。私、ちゃんと笑えてるかしら</t>
         </is>
       </c>
     </row>
     <row r="387" ht="40" customHeight="1">
       <c r="A387" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES.coach.artisan[2]</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.D.polite[1].text</t>
         </is>
       </c>
       <c r="B387" t="inlineStr" s="2">
@@ -14202,24 +14227,29 @@
       </c>
       <c r="D387" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES</t>
         </is>
       </c>
       <c r="E387" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">coach.artisan[2]</t>
+          <t xml:space="preserve">D.polite[1].text</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">丁寧</t>
         </is>
       </c>
       <c r="H387" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">四年に一度、あの大舞台で技を晒す。社長、うちの子らが仕上げてきた形、そろそろ世に問うていい頃合いだと思います</t>
+          <t xml:space="preserve">おめでとうございます。…すみません、今日は先に上がらせてください</t>
         </is>
       </c>
     </row>
     <row r="388" ht="40" customHeight="1">
       <c r="A388" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES.coach.mentor[1]</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.D.polite[2].text</t>
         </is>
       </c>
       <c r="B388" t="inlineStr" s="2">
@@ -14234,24 +14264,29 @@
       </c>
       <c r="D388" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES</t>
         </is>
       </c>
       <c r="E388" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">coach.mentor[1]</t>
+          <t xml:space="preserve">D.polite[2].text</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">丁寧</t>
         </is>
       </c>
       <c r="H388" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、あれはただの大会じゃありません。あの子たちのキャリアに四年に一度きり刻まれる節目です。…見届けてやりましょう</t>
+          <t xml:space="preserve">おめでとうございます、心からそう思っています。…思って、いるんです</t>
         </is>
       </c>
     </row>
     <row r="389" ht="40" customHeight="1">
       <c r="A389" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES.coach.mentor[2]</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.E.standard[1].text</t>
         </is>
       </c>
       <c r="B389" t="inlineStr" s="2">
@@ -14266,24 +14301,29 @@
       </c>
       <c r="D389" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES</t>
         </is>
       </c>
       <c r="E389" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">coach.mentor[2]</t>
+          <t xml:space="preserve">E.standard[1].text</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="H389" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ち負けの前に、あの子たちが自分の到達点を知る舞台になります。社長、四年に一度の大切な一度、丁寧に送り出したいですね</t>
+          <t xml:space="preserve">負けたけど…同じ団体に、こんな強い人がいて嬉しいです</t>
         </is>
       </c>
     </row>
     <row r="390" ht="40" customHeight="1">
       <c r="A390" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES.coach.bigheart[1]</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.E.standard[2].text</t>
         </is>
       </c>
       <c r="B390" t="inlineStr" s="2">
@@ -14298,24 +14338,29 @@
       </c>
       <c r="D390" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES</t>
         </is>
       </c>
       <c r="E390" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">coach.bigheart[1]</t>
+          <t xml:space="preserve">E.standard[2].text</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="H390" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、聞きましたか! 四年に一度ですよ。こういう祭りはどうにも血が騒ぐ。うちの子らも、もうそわそわし始めてますわ</t>
+          <t xml:space="preserve">悔しい。…でも、あなたが上に行くなら、背中は私が守ります</t>
         </is>
       </c>
     </row>
     <row r="391" ht="40" customHeight="1">
       <c r="A391" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES.coach.bigheart[2]</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.E.composed[1].text</t>
         </is>
       </c>
       <c r="B391" t="inlineStr" s="2">
@@ -14330,24 +14375,29 @@
       </c>
       <c r="D391" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES</t>
         </is>
       </c>
       <c r="E391" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">coach.bigheart[2]</t>
+          <t xml:space="preserve">E.composed[1].text</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">鷹揚</t>
         </is>
       </c>
       <c r="H391" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いやあ社長、また天頂戦の季節が巡ってきましたな。四年ぶりのお祭り騒ぎだ。難しい顔してないで、一緒に楽しみましょうや</t>
+          <t xml:space="preserve">…参ったよ。…けど、あんたが仲間で良かった。本気でそう思う</t>
         </is>
       </c>
     </row>
     <row r="392" ht="40" customHeight="1">
       <c r="A392" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES.fighter.standard[1].text</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.E.composed[2].text</t>
         </is>
       </c>
       <c r="B392" t="inlineStr" s="2">
@@ -14362,29 +14412,29 @@
       </c>
       <c r="D392" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES</t>
         </is>
       </c>
       <c r="E392" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.standard[1].text</t>
+          <t xml:space="preserve">E.composed[2].text</t>
         </is>
       </c>
       <c r="F392" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">標準</t>
+          <t xml:space="preserve">鷹揚</t>
         </is>
       </c>
       <c r="H392" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">四年に一度、なんですよね。前回はただ見てるだけだった。今度は、あの輪の中に立ちたいんです</t>
+          <t xml:space="preserve">同じ看板を背負う相手が強い。…悪くない、むしろ誇らしいね</t>
         </is>
       </c>
     </row>
     <row r="393" ht="40" customHeight="1">
       <c r="A393" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES.fighter.standard[2].text</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.E.ojousama[1].text</t>
         </is>
       </c>
       <c r="B393" t="inlineStr" s="2">
@@ -14399,29 +14449,29 @@
       </c>
       <c r="D393" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES</t>
         </is>
       </c>
       <c r="E393" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.standard[2].text</t>
+          <t xml:space="preserve">E.ojousama[1].text</t>
         </is>
       </c>
       <c r="F393" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">標準</t>
+          <t xml:space="preserve">お嬢様</t>
         </is>
       </c>
       <c r="H393" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">エントリー発表、もうすぐですね。あの狭き門をくぐれるかどうか。…そう思うと、練習の一本が重くなります</t>
+          <t xml:space="preserve">見事でしたわ。…同じ団体に、あなたがいる幸せを噛みしめておりますの</t>
         </is>
       </c>
     </row>
     <row r="394" ht="40" customHeight="1">
       <c r="A394" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES.fighter.standard[3].text</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.E.ojousama[2].text</t>
         </is>
       </c>
       <c r="B394" t="inlineStr" s="2">
@@ -14436,29 +14486,29 @@
       </c>
       <c r="D394" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES</t>
         </is>
       </c>
       <c r="E394" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.standard[3].text</t>
+          <t xml:space="preserve">E.ojousama[2].text</t>
         </is>
       </c>
       <c r="F394" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">標準</t>
+          <t xml:space="preserve">お嬢様</t>
         </is>
       </c>
       <c r="H394" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">四年に一度。…次があるかは、わかりません。だからこそ、この一回に全部を置いていきたいんです</t>
+          <t xml:space="preserve">悔しさの奥に、誇りがありますわ。…あなたと同じ旗の下で、良かった</t>
         </is>
       </c>
     </row>
     <row r="395" ht="40" customHeight="1">
       <c r="A395" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES.fighter.composed[1].text</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.E.delinquent[1].text</t>
         </is>
       </c>
       <c r="B395" t="inlineStr" s="2">
@@ -14473,29 +14523,29 @@
       </c>
       <c r="D395" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES</t>
         </is>
       </c>
       <c r="E395" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.composed[1].text</t>
+          <t xml:space="preserve">E.delinquent[1].text</t>
         </is>
       </c>
       <c r="F395" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">鷹揚</t>
+          <t xml:space="preserve">ヤンキー</t>
         </is>
       </c>
       <c r="H395" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…天頂戦、か。四年ぶりだね。…ま、こういう舞台のために続けてきたんだ。悪くない</t>
+          <t xml:space="preserve">クソ、負けた…けど、あんたが身内で良かったって心底思うわ</t>
         </is>
       </c>
     </row>
     <row r="396" ht="40" customHeight="1">
       <c r="A396" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES.fighter.composed[2].text</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.E.delinquent[2].text</t>
         </is>
       </c>
       <c r="B396" t="inlineStr" s="2">
@@ -14510,29 +14560,29 @@
       </c>
       <c r="D396" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES</t>
         </is>
       </c>
       <c r="E396" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.composed[2].text</t>
+          <t xml:space="preserve">E.delinquent[2].text</t>
         </is>
       </c>
       <c r="F396" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">鷹揚</t>
+          <t xml:space="preserve">ヤンキー</t>
         </is>
       </c>
       <c r="H396" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">近づいてきたね。…狭き門だってことは、分かってる。…焦らず、体を仕上げるよ</t>
+          <t xml:space="preserve">同じチームにこんな怪物がいるとか、最高じゃねぇか。…惚れ直したぜ</t>
         </is>
       </c>
     </row>
     <row r="397" ht="40" customHeight="1">
       <c r="A397" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES.fighter.composed[3].text</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.E.cool[1].text</t>
         </is>
       </c>
       <c r="B397" t="inlineStr" s="2">
@@ -14547,29 +14597,29 @@
       </c>
       <c r="D397" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES</t>
         </is>
       </c>
       <c r="E397" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.composed[3].text</t>
+          <t xml:space="preserve">E.cool[1].text</t>
         </is>
       </c>
       <c r="F397" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">鷹揚</t>
+          <t xml:space="preserve">クール</t>
         </is>
       </c>
       <c r="H397" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">四年後、ここに立ってる保証はないよ。…だからこそ、今回は…ちゃんとやる</t>
+          <t xml:space="preserve">……強い。仲間として、誇らしい</t>
         </is>
       </c>
     </row>
     <row r="398" ht="40" customHeight="1">
       <c r="A398" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES.fighter.ojousama[1].text</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.E.cool[2].text</t>
         </is>
       </c>
       <c r="B398" t="inlineStr" s="2">
@@ -14584,29 +14634,29 @@
       </c>
       <c r="D398" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES</t>
         </is>
       </c>
       <c r="E398" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.ojousama[1].text</t>
+          <t xml:space="preserve">E.cool[2].text</t>
         </is>
       </c>
       <c r="F398" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">お嬢様</t>
+          <t xml:space="preserve">クール</t>
         </is>
       </c>
       <c r="H398" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">四年に一度の大舞台ですわね。前回のあの熱気…今も胸に残っておりますの</t>
+          <t xml:space="preserve">……負けた。…でも、お前が同じ旗の下でよかった</t>
         </is>
       </c>
     </row>
     <row r="399" ht="40" customHeight="1">
       <c r="A399" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES.fighter.ojousama[2].text</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.E.seductive[1].text</t>
         </is>
       </c>
       <c r="B399" t="inlineStr" s="2">
@@ -14621,29 +14671,29 @@
       </c>
       <c r="D399" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES</t>
         </is>
       </c>
       <c r="E399" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.ojousama[2].text</t>
+          <t xml:space="preserve">E.seductive[1].text</t>
         </is>
       </c>
       <c r="F399" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">お嬢様</t>
+          <t xml:space="preserve">蠱惑</t>
         </is>
       </c>
       <c r="H399" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">エントリーが近づいて参りましたわ。選ばれし者だけが立てる場所…わたくし、静かに燃えておりますの</t>
+          <t xml:space="preserve">負けちゃったけど…同じ団体にあなたがいるの、悪くないわ、ふふ</t>
         </is>
       </c>
     </row>
     <row r="400" ht="40" customHeight="1">
       <c r="A400" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES.fighter.ojousama[3].text</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.E.seductive[2].text</t>
         </is>
       </c>
       <c r="B400" t="inlineStr" s="2">
@@ -14658,29 +14708,29 @@
       </c>
       <c r="D400" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES</t>
         </is>
       </c>
       <c r="E400" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.ojousama[3].text</t>
+          <t xml:space="preserve">E.seductive[2].text</t>
         </is>
       </c>
       <c r="F400" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">お嬢様</t>
+          <t xml:space="preserve">蠱惑</t>
         </is>
       </c>
       <c r="H400" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">四年後、この体で戦えているかは…わかりませんわ。ですから、今回こそ悔いのないように</t>
+          <t xml:space="preserve">悔しいのに、なぜかドキドキしてる。…同志にしておくには、惜しい人</t>
         </is>
       </c>
     </row>
     <row r="401" ht="40" customHeight="1">
       <c r="A401" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES.fighter.delinquent[1].text</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.E.polite[1].text</t>
         </is>
       </c>
       <c r="B401" t="inlineStr" s="2">
@@ -14695,29 +14745,29 @@
       </c>
       <c r="D401" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES</t>
         </is>
       </c>
       <c r="E401" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.delinquent[1].text</t>
+          <t xml:space="preserve">E.polite[1].text</t>
         </is>
       </c>
       <c r="F401" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ヤンキー</t>
+          <t xml:space="preserve">丁寧</t>
         </is>
       </c>
       <c r="H401" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">四年ぶりかよ、あの大会。前は指くわえて見てただけ。今度はテメェの足で、あの中に立ってやる</t>
+          <t xml:space="preserve">完敗です。…でも、あなたと同じ団体でいられることを、誇りに思います</t>
         </is>
       </c>
     </row>
     <row r="402" ht="40" customHeight="1">
       <c r="A402" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES.fighter.delinquent[2].text</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES.E.polite[2].text</t>
         </is>
       </c>
       <c r="B402" t="inlineStr" s="2">
@@ -14732,29 +14782,29 @@
       </c>
       <c r="D402" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES</t>
+          <t xml:space="preserve">TENCHOSEN_DRAMA_LINES</t>
         </is>
       </c>
       <c r="E402" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.delinquent[2].text</t>
+          <t xml:space="preserve">E.polite[2].text</t>
         </is>
       </c>
       <c r="F402" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ヤンキー</t>
+          <t xml:space="preserve">丁寧</t>
         </is>
       </c>
       <c r="H402" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もうすぐエントリーだろ? あんな狭き門、こじ開けてやるっての。腕が鳴って鳴って、しゃあねぇわ</t>
+          <t xml:space="preserve">負けて、むしろ嬉しいんです。…あなたの背中を追える意味が、わかった</t>
         </is>
       </c>
     </row>
     <row r="403" ht="40" customHeight="1">
       <c r="A403" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES.fighter.delinquent[3].text</t>
+          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES.coach.sparta[1]</t>
         </is>
       </c>
       <c r="B403" t="inlineStr" s="2">
@@ -14774,24 +14824,19 @@
       </c>
       <c r="E403" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.delinquent[3].text</t>
-        </is>
-      </c>
-      <c r="F403" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">ヤンキー</t>
+          <t xml:space="preserve">coach.sparta[1]</t>
         </is>
       </c>
       <c r="H403" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">四年後? …そんな先のこと、あるかどうかも分かんねぇ。だから今回で全部出しきる。それだけだ</t>
+          <t xml:space="preserve">社長、いよいよですな。四年に一度のあの舞台——うちの子らを鍛え上げてきた、その成果を全部ぶつけさせてもらう</t>
         </is>
       </c>
     </row>
     <row r="404" ht="40" customHeight="1">
       <c r="A404" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES.fighter.cool[1].text</t>
+          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES.coach.sparta[2]</t>
         </is>
       </c>
       <c r="B404" t="inlineStr" s="2">
@@ -14811,24 +14856,19 @@
       </c>
       <c r="E404" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.cool[1].text</t>
-        </is>
-      </c>
-      <c r="F404" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">クール</t>
+          <t xml:space="preserve">coach.sparta[2]</t>
         </is>
       </c>
       <c r="H404" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……四年に一度の、頂だ</t>
+          <t xml:space="preserve">この日のために汗を絞ってきたんだ。逃げも隠れもできん、剥き出しの真剣勝負の場。社長、存分に暴れさせてやってくれ</t>
         </is>
       </c>
     </row>
     <row r="405" ht="40" customHeight="1">
       <c r="A405" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES.fighter.cool[2].text</t>
+          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES.coach.theorist[1]</t>
         </is>
       </c>
       <c r="B405" t="inlineStr" s="2">
@@ -14848,24 +14888,19 @@
       </c>
       <c r="E405" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.cool[2].text</t>
-        </is>
-      </c>
-      <c r="F405" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">クール</t>
+          <t xml:space="preserve">coach.theorist[1]</t>
         </is>
       </c>
       <c r="H405" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……エントリーは、もうすぐ。狭き門を、くぐるだけ</t>
+          <t xml:space="preserve">社長、エントリーの顔ぶれが読めてきました。他団体の主力データ、粗方は揃っています。…付け入る隙は、必ずありますよ</t>
         </is>
       </c>
     </row>
     <row r="406" ht="40" customHeight="1">
       <c r="A406" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES.fighter.cool[3].text</t>
+          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES.coach.theorist[2]</t>
         </is>
       </c>
       <c r="B406" t="inlineStr" s="2">
@@ -14885,24 +14920,19 @@
       </c>
       <c r="E406" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.cool[3].text</t>
-        </is>
-      </c>
-      <c r="F406" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">クール</t>
+          <t xml:space="preserve">coach.theorist[2]</t>
         </is>
       </c>
       <c r="H406" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……四年後は、もう無いかもしれない。だから、今</t>
+          <t xml:space="preserve">四年に一度、最強を決める舞台です。各団体の戦力を並べて見ると、社長、うちにも勝ち筋は描ける。数字がそう言っています</t>
         </is>
       </c>
     </row>
     <row r="407" ht="40" customHeight="1">
       <c r="A407" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES.fighter.seductive[1].text</t>
+          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES.coach.artisan[1]</t>
         </is>
       </c>
       <c r="B407" t="inlineStr" s="2">
@@ -14922,24 +14952,19 @@
       </c>
       <c r="E407" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.seductive[1].text</t>
-        </is>
-      </c>
-      <c r="F407" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">蠱惑</t>
+          <t xml:space="preserve">coach.artisan[1]</t>
         </is>
       </c>
       <c r="H407" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">四年に一度しか味わえない空気ね。ふふ、今からもう肌がざわついているわ</t>
+          <t xml:space="preserve">社長……来ましたな、四年に一度が。あそこは小手先の通じん舞台だ。磨き上げてきた技が本物かどうか——問われるのは、それだけです</t>
         </is>
       </c>
     </row>
     <row r="408" ht="40" customHeight="1">
       <c r="A408" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES.fighter.seductive[2].text</t>
+          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES.coach.artisan[2]</t>
         </is>
       </c>
       <c r="B408" t="inlineStr" s="2">
@@ -14959,24 +14984,19 @@
       </c>
       <c r="E408" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.seductive[2].text</t>
-        </is>
-      </c>
-      <c r="F408" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">蠱惑</t>
+          <t xml:space="preserve">coach.artisan[2]</t>
         </is>
       </c>
       <c r="H408" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もうすぐエントリーね。あの狭き門…選ばれる女は、そう多くないの。私、その一人でいたいわ</t>
+          <t xml:space="preserve">四年に一度、あの大舞台で技を晒す。社長、うちの子らが仕上げてきた形、そろそろ世に問うていい頃合いだと思います</t>
         </is>
       </c>
     </row>
     <row r="409" ht="40" customHeight="1">
       <c r="A409" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES.fighter.seductive[3].text</t>
+          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES.coach.mentor[1]</t>
         </is>
       </c>
       <c r="B409" t="inlineStr" s="2">
@@ -14996,24 +15016,19 @@
       </c>
       <c r="E409" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.seductive[3].text</t>
-        </is>
-      </c>
-      <c r="F409" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">蠱惑</t>
+          <t xml:space="preserve">coach.mentor[1]</t>
         </is>
       </c>
       <c r="H409" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">四年後、まだこの舞台に立てているかしら。…だから今回は、しっかり目に焼き付けておくの</t>
+          <t xml:space="preserve">社長、あれはただの大会じゃありません。あの子たちのキャリアに四年に一度きり刻まれる節目です。…見届けてやりましょう</t>
         </is>
       </c>
     </row>
     <row r="410" ht="40" customHeight="1">
       <c r="A410" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES.fighter.polite[1].text</t>
+          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES.coach.mentor[2]</t>
         </is>
       </c>
       <c r="B410" t="inlineStr" s="2">
@@ -15033,24 +15048,19 @@
       </c>
       <c r="E410" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.polite[1].text</t>
-        </is>
-      </c>
-      <c r="F410" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">丁寧</t>
+          <t xml:space="preserve">coach.mentor[2]</t>
         </is>
       </c>
       <c r="H410" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">四年に一度の大舞台です。前回、遠くから見上げていた景色に…今度は近づきたいんです</t>
+          <t xml:space="preserve">勝ち負けの前に、あの子たちが自分の到達点を知る舞台になります。社長、四年に一度の大切な一度、丁寧に送り出したいですね</t>
         </is>
       </c>
     </row>
     <row r="411" ht="40" customHeight="1">
       <c r="A411" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES.fighter.polite[2].text</t>
+          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES.coach.bigheart[1]</t>
         </is>
       </c>
       <c r="B411" t="inlineStr" s="2">
@@ -15070,24 +15080,19 @@
       </c>
       <c r="E411" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.polite[2].text</t>
-        </is>
-      </c>
-      <c r="F411" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">丁寧</t>
+          <t xml:space="preserve">coach.bigheart[1]</t>
         </is>
       </c>
       <c r="H411" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もうすぐエントリー発表ですね。あの狭き門をくぐる資格が自分にあるのか。…試させてください</t>
+          <t xml:space="preserve">社長、聞きましたか! 四年に一度ですよ。こういう祭りはどうにも血が騒ぐ。うちの子らも、もうそわそわし始めてますわ</t>
         </is>
       </c>
     </row>
     <row r="412" ht="40" customHeight="1">
       <c r="A412" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES.fighter.polite[3].text</t>
+          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES.coach.bigheart[2]</t>
         </is>
       </c>
       <c r="B412" t="inlineStr" s="2">
@@ -15107,29 +15112,24 @@
       </c>
       <c r="E412" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.polite[3].text</t>
-        </is>
-      </c>
-      <c r="F412" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">丁寧</t>
+          <t xml:space="preserve">coach.bigheart[2]</t>
         </is>
       </c>
       <c r="H412" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">四年後も同じ舞台に立てるとは、限りません。…だからこそ、今回を大切に戦わせてください</t>
+          <t xml:space="preserve">いやあ社長、また天頂戦の季節が巡ってきましたな。四年ぶりのお祭り騒ぎだ。難しい顔してないで、一緒に楽しみましょうや</t>
         </is>
       </c>
     </row>
     <row r="413" ht="40" customHeight="1">
       <c r="A413" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_COACH_LINES.fresh[1]</t>
+          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES.fighter.standard[1].text</t>
         </is>
       </c>
       <c r="B413" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">15-その他</t>
+          <t xml:space="preserve">14-PPV・対抗戦・トーナメント</t>
         </is>
       </c>
       <c r="C413" t="inlineStr" s="2">
@@ -15139,29 +15139,34 @@
       </c>
       <c r="D413" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">HEAT_STATE_COACH_LINES</t>
+          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES</t>
         </is>
       </c>
       <c r="E413" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fresh[1]</t>
+          <t xml:space="preserve">fighter.standard[1].text</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="H413" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}、今日はよく動いてる。仕込むなら今だ</t>
+          <t xml:space="preserve">四年に一度、なんですよね。前回はただ見てるだけだった。今度は、あの輪の中に立ちたいんです</t>
         </is>
       </c>
     </row>
     <row r="414" ht="40" customHeight="1">
       <c r="A414" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_COACH_LINES.fresh[2]</t>
+          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES.fighter.standard[2].text</t>
         </is>
       </c>
       <c r="B414" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">15-その他</t>
+          <t xml:space="preserve">14-PPV・対抗戦・トーナメント</t>
         </is>
       </c>
       <c r="C414" t="inlineStr" s="2">
@@ -15171,29 +15176,34 @@
       </c>
       <c r="D414" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">HEAT_STATE_COACH_LINES</t>
+          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES</t>
         </is>
       </c>
       <c r="E414" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fresh[2]</t>
+          <t xml:space="preserve">fighter.standard[2].text</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="H414" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}の体が、新しい動きを素直に飲み込んでいる</t>
+          <t xml:space="preserve">エントリー発表、もうすぐですね。あの狭き門をくぐれるかどうか。…そう思うと、練習の一本が重くなります</t>
         </is>
       </c>
     </row>
     <row r="415" ht="40" customHeight="1">
       <c r="A415" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_COACH_LINES.fresh[3]</t>
+          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES.fighter.standard[3].text</t>
         </is>
       </c>
       <c r="B415" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">15-その他</t>
+          <t xml:space="preserve">14-PPV・対抗戦・トーナメント</t>
         </is>
       </c>
       <c r="C415" t="inlineStr" s="2">
@@ -15203,29 +15213,34 @@
       </c>
       <c r="D415" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">HEAT_STATE_COACH_LINES</t>
+          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES</t>
         </is>
       </c>
       <c r="E415" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fresh[3]</t>
+          <t xml:space="preserve">fighter.standard[3].text</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="H415" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今の{name}なら、多少きつくしても全部持っていく</t>
+          <t xml:space="preserve">四年に一度。…次があるかは、わかりません。だからこそ、この一回に全部を置いていきたいんです</t>
         </is>
       </c>
     </row>
     <row r="416" ht="40" customHeight="1">
       <c r="A416" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_COACH_LINES.fresh[4]</t>
+          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES.fighter.composed[1].text</t>
         </is>
       </c>
       <c r="B416" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">15-その他</t>
+          <t xml:space="preserve">14-PPV・対抗戦・トーナメント</t>
         </is>
       </c>
       <c r="C416" t="inlineStr" s="2">
@@ -15235,29 +15250,34 @@
       </c>
       <c r="D416" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">HEAT_STATE_COACH_LINES</t>
+          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES</t>
         </is>
       </c>
       <c r="E416" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fresh[4]</t>
+          <t xml:space="preserve">fighter.composed[1].text</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">鷹揚</t>
         </is>
       </c>
       <c r="H416" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}の足が軽い。こういう週こそ厚く積ませたい</t>
+          <t xml:space="preserve">…天頂戦、か。四年ぶりだね。…ま、こういう舞台のために続けてきたんだ。悪くない</t>
         </is>
       </c>
     </row>
     <row r="417" ht="40" customHeight="1">
       <c r="A417" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_COACH_LINES.fresh[5]</t>
+          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES.fighter.composed[2].text</t>
         </is>
       </c>
       <c r="B417" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">15-その他</t>
+          <t xml:space="preserve">14-PPV・対抗戦・トーナメント</t>
         </is>
       </c>
       <c r="C417" t="inlineStr" s="2">
@@ -15267,29 +15287,34 @@
       </c>
       <c r="D417" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">HEAT_STATE_COACH_LINES</t>
+          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES</t>
         </is>
       </c>
       <c r="E417" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fresh[5]</t>
+          <t xml:space="preserve">fighter.composed[2].text</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">鷹揚</t>
         </is>
       </c>
       <c r="H417" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}、伸びる顔をしている。今日の一本は残るぞ</t>
+          <t xml:space="preserve">近づいてきたね。…狭き門だってことは、分かってる。…焦らず、体を仕上げるよ</t>
         </is>
       </c>
     </row>
     <row r="418" ht="40" customHeight="1">
       <c r="A418" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_COACH_LINES.fresh[6]</t>
+          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES.fighter.composed[3].text</t>
         </is>
       </c>
       <c r="B418" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">15-その他</t>
+          <t xml:space="preserve">14-PPV・対抗戦・トーナメント</t>
         </is>
       </c>
       <c r="C418" t="inlineStr" s="2">
@@ -15299,29 +15324,34 @@
       </c>
       <c r="D418" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">HEAT_STATE_COACH_LINES</t>
+          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES</t>
         </is>
       </c>
       <c r="E418" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fresh[6]</t>
+          <t xml:space="preserve">fighter.composed[3].text</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">鷹揚</t>
         </is>
       </c>
       <c r="H418" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}は休み明けの体だ。一番よく入る時期に来ている</t>
+          <t xml:space="preserve">四年後、ここに立ってる保証はないよ。…だからこそ、今回は…ちゃんとやる</t>
         </is>
       </c>
     </row>
     <row r="419" ht="40" customHeight="1">
       <c r="A419" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_COACH_LINES.fresh[7]</t>
+          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES.fighter.ojousama[1].text</t>
         </is>
       </c>
       <c r="B419" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">15-その他</t>
+          <t xml:space="preserve">14-PPV・対抗戦・トーナメント</t>
         </is>
       </c>
       <c r="C419" t="inlineStr" s="2">
@@ -15331,29 +15361,34 @@
       </c>
       <c r="D419" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">HEAT_STATE_COACH_LINES</t>
+          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES</t>
         </is>
       </c>
       <c r="E419" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fresh[7]</t>
+          <t xml:space="preserve">fighter.ojousama[1].text</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">お嬢様</t>
         </is>
       </c>
       <c r="H419" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}、今週は当たり週だ。使うなら、ここで使え</t>
+          <t xml:space="preserve">四年に一度の大舞台ですわね。前回のあの熱気…今も胸に残っておりますの</t>
         </is>
       </c>
     </row>
     <row r="420" ht="40" customHeight="1">
       <c r="A420" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_COACH_LINES.warm[1]</t>
+          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES.fighter.ojousama[2].text</t>
         </is>
       </c>
       <c r="B420" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">15-その他</t>
+          <t xml:space="preserve">14-PPV・対抗戦・トーナメント</t>
         </is>
       </c>
       <c r="C420" t="inlineStr" s="2">
@@ -15363,29 +15398,34 @@
       </c>
       <c r="D420" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">HEAT_STATE_COACH_LINES</t>
+          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES</t>
         </is>
       </c>
       <c r="E420" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">warm[1]</t>
+          <t xml:space="preserve">fighter.ojousama[2].text</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">お嬢様</t>
         </is>
       </c>
       <c r="H420" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}、悪くはない。ただ、先週ほどは入っていかない</t>
+          <t xml:space="preserve">エントリーが近づいて参りましたわ。選ばれし者だけが立てる場所…わたくし、静かに燃えておりますの</t>
         </is>
       </c>
     </row>
     <row r="421" ht="40" customHeight="1">
       <c r="A421" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_COACH_LINES.warm[2]</t>
+          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES.fighter.ojousama[3].text</t>
         </is>
       </c>
       <c r="B421" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">15-その他</t>
+          <t xml:space="preserve">14-PPV・対抗戦・トーナメント</t>
         </is>
       </c>
       <c r="C421" t="inlineStr" s="2">
@@ -15395,29 +15435,34 @@
       </c>
       <c r="D421" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">HEAT_STATE_COACH_LINES</t>
+          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES</t>
         </is>
       </c>
       <c r="E421" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">warm[2]</t>
+          <t xml:space="preserve">fighter.ojousama[3].text</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">お嬢様</t>
         </is>
       </c>
       <c r="H421" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}の伸びが少し鈍ってきた。詰めすぎたか</t>
+          <t xml:space="preserve">四年後、この体で戦えているかは…わかりませんわ。ですから、今回こそ悔いのないように</t>
         </is>
       </c>
     </row>
     <row r="422" ht="40" customHeight="1">
       <c r="A422" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_COACH_LINES.warm[3]</t>
+          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES.fighter.delinquent[1].text</t>
         </is>
       </c>
       <c r="B422" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">15-その他</t>
+          <t xml:space="preserve">14-PPV・対抗戦・トーナメント</t>
         </is>
       </c>
       <c r="C422" t="inlineStr" s="2">
@@ -15427,29 +15472,34 @@
       </c>
       <c r="D422" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">HEAT_STATE_COACH_LINES</t>
+          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES</t>
         </is>
       </c>
       <c r="E422" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">warm[3]</t>
+          <t xml:space="preserve">fighter.delinquent[1].text</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ヤンキー</t>
         </is>
       </c>
       <c r="H422" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}、同じメニューなのに返りが薄い。そろそろ一息か</t>
+          <t xml:space="preserve">四年ぶりかよ、あの大会。前は指くわえて見てただけ。今度はテメェの足で、あの中に立ってやる</t>
         </is>
       </c>
     </row>
     <row r="423" ht="40" customHeight="1">
       <c r="A423" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_COACH_LINES.warm[4]</t>
+          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES.fighter.delinquent[2].text</t>
         </is>
       </c>
       <c r="B423" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">15-その他</t>
+          <t xml:space="preserve">14-PPV・対抗戦・トーナメント</t>
         </is>
       </c>
       <c r="C423" t="inlineStr" s="2">
@@ -15459,29 +15509,34 @@
       </c>
       <c r="D423" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">HEAT_STATE_COACH_LINES</t>
+          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES</t>
         </is>
       </c>
       <c r="E423" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">warm[4]</t>
+          <t xml:space="preserve">fighter.delinquent[2].text</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ヤンキー</t>
         </is>
       </c>
       <c r="H423" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}、動けてはいる。だが、切れがひとつ落ちている</t>
+          <t xml:space="preserve">もうすぐエントリーだろ? あんな狭き門、こじ開けてやるっての。腕が鳴って鳴って、しゃあねぇわ</t>
         </is>
       </c>
     </row>
     <row r="424" ht="40" customHeight="1">
       <c r="A424" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_COACH_LINES.warm[5]</t>
+          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES.fighter.delinquent[3].text</t>
         </is>
       </c>
       <c r="B424" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">15-その他</t>
+          <t xml:space="preserve">14-PPV・対抗戦・トーナメント</t>
         </is>
       </c>
       <c r="C424" t="inlineStr" s="2">
@@ -15491,29 +15546,34 @@
       </c>
       <c r="D424" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">HEAT_STATE_COACH_LINES</t>
+          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES</t>
         </is>
       </c>
       <c r="E424" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">warm[5]</t>
+          <t xml:space="preserve">fighter.delinquent[3].text</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ヤンキー</t>
         </is>
       </c>
       <c r="H424" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}の体が慣れてきた。効きが落ちる頃合いだ</t>
+          <t xml:space="preserve">四年後? …そんな先のこと、あるかどうかも分かんねぇ。だから今回で全部出しきる。それだけだ</t>
         </is>
       </c>
     </row>
     <row r="425" ht="40" customHeight="1">
       <c r="A425" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_COACH_LINES.warm[6]</t>
+          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES.fighter.cool[1].text</t>
         </is>
       </c>
       <c r="B425" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">15-その他</t>
+          <t xml:space="preserve">14-PPV・対抗戦・トーナメント</t>
         </is>
       </c>
       <c r="C425" t="inlineStr" s="2">
@@ -15523,29 +15583,34 @@
       </c>
       <c r="D425" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">HEAT_STATE_COACH_LINES</t>
+          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES</t>
         </is>
       </c>
       <c r="E425" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">warm[6]</t>
+          <t xml:space="preserve">fighter.cool[1].text</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">クール</t>
         </is>
       </c>
       <c r="H425" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}、今週も同じ調子で行くなら、得は薄いぞ</t>
+          <t xml:space="preserve">……四年に一度の、頂だ</t>
         </is>
       </c>
     </row>
     <row r="426" ht="40" customHeight="1">
       <c r="A426" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_COACH_LINES.warm[7]</t>
+          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES.fighter.cool[2].text</t>
         </is>
       </c>
       <c r="B426" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">15-その他</t>
+          <t xml:space="preserve">14-PPV・対抗戦・トーナメント</t>
         </is>
       </c>
       <c r="C426" t="inlineStr" s="2">
@@ -15555,29 +15620,34 @@
       </c>
       <c r="D426" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">HEAT_STATE_COACH_LINES</t>
+          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES</t>
         </is>
       </c>
       <c r="E426" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">warm[7]</t>
+          <t xml:space="preserve">fighter.cool[2].text</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">クール</t>
         </is>
       </c>
       <c r="H426" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}にきついのを続けるか。…見極めどきだな</t>
+          <t xml:space="preserve">……エントリーは、もうすぐ。狭き門を、くぐるだけ</t>
         </is>
       </c>
     </row>
     <row r="427" ht="40" customHeight="1">
       <c r="A427" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_COACH_LINES.heavy[1]</t>
+          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES.fighter.cool[3].text</t>
         </is>
       </c>
       <c r="B427" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">15-その他</t>
+          <t xml:space="preserve">14-PPV・対抗戦・トーナメント</t>
         </is>
       </c>
       <c r="C427" t="inlineStr" s="2">
@@ -15587,29 +15657,34 @@
       </c>
       <c r="D427" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">HEAT_STATE_COACH_LINES</t>
+          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES</t>
         </is>
       </c>
       <c r="E427" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heavy[1]</t>
+          <t xml:space="preserve">fighter.cool[3].text</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">クール</t>
         </is>
       </c>
       <c r="H427" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}、今日は体が重い。何をやらせても素通りだ</t>
+          <t xml:space="preserve">……四年後は、もう無いかもしれない。だから、今</t>
         </is>
       </c>
     </row>
     <row r="428" ht="40" customHeight="1">
       <c r="A428" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_COACH_LINES.heavy[2]</t>
+          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES.fighter.seductive[1].text</t>
         </is>
       </c>
       <c r="B428" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">15-その他</t>
+          <t xml:space="preserve">14-PPV・対抗戦・トーナメント</t>
         </is>
       </c>
       <c r="C428" t="inlineStr" s="2">
@@ -15619,29 +15694,34 @@
       </c>
       <c r="D428" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">HEAT_STATE_COACH_LINES</t>
+          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES</t>
         </is>
       </c>
       <c r="E428" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heavy[2]</t>
+          <t xml:space="preserve">fighter.seductive[1].text</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">蠱惑</t>
         </is>
       </c>
       <c r="H428" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今の{name}に課しても、削るだけで何も積まれない</t>
+          <t xml:space="preserve">四年に一度しか味わえない空気ね。ふふ、今からもう肌がざわついているわ</t>
         </is>
       </c>
     </row>
     <row r="429" ht="40" customHeight="1">
       <c r="A429" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_COACH_LINES.heavy[3]</t>
+          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES.fighter.seductive[2].text</t>
         </is>
       </c>
       <c r="B429" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">15-その他</t>
+          <t xml:space="preserve">14-PPV・対抗戦・トーナメント</t>
         </is>
       </c>
       <c r="C429" t="inlineStr" s="2">
@@ -15651,29 +15731,34 @@
       </c>
       <c r="D429" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">HEAT_STATE_COACH_LINES</t>
+          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES</t>
         </is>
       </c>
       <c r="E429" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heavy[3]</t>
+          <t xml:space="preserve">fighter.seductive[2].text</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">蠱惑</t>
         </is>
       </c>
       <c r="H429" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}は追い込みすぎだ。一度、外してやってくれ</t>
+          <t xml:space="preserve">もうすぐエントリーね。あの狭き門…選ばれる女は、そう多くないの。私、その一人でいたいわ</t>
         </is>
       </c>
     </row>
     <row r="430" ht="40" customHeight="1">
       <c r="A430" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_COACH_LINES.heavy[4]</t>
+          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES.fighter.seductive[3].text</t>
         </is>
       </c>
       <c r="B430" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">15-その他</t>
+          <t xml:space="preserve">14-PPV・対抗戦・トーナメント</t>
         </is>
       </c>
       <c r="C430" t="inlineStr" s="2">
@@ -15683,29 +15768,34 @@
       </c>
       <c r="D430" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">HEAT_STATE_COACH_LINES</t>
+          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES</t>
         </is>
       </c>
       <c r="E430" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heavy[4]</t>
+          <t xml:space="preserve">fighter.seductive[3].text</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">蠱惑</t>
         </is>
       </c>
       <c r="H430" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}、汗はかいている。だが、身についてはいない</t>
+          <t xml:space="preserve">四年後、まだこの舞台に立てているかしら。…だから今回は、しっかり目に焼き付けておくの</t>
         </is>
       </c>
     </row>
     <row r="431" ht="40" customHeight="1">
       <c r="A431" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_COACH_LINES.heavy[5]</t>
+          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES.fighter.polite[1].text</t>
         </is>
       </c>
       <c r="B431" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">15-その他</t>
+          <t xml:space="preserve">14-PPV・対抗戦・トーナメント</t>
         </is>
       </c>
       <c r="C431" t="inlineStr" s="2">
@@ -15715,29 +15805,34 @@
       </c>
       <c r="D431" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">HEAT_STATE_COACH_LINES</t>
+          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES</t>
         </is>
       </c>
       <c r="E431" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heavy[5]</t>
+          <t xml:space="preserve">fighter.polite[1].text</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">丁寧</t>
         </is>
       </c>
       <c r="H431" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}の体はもう受け付けていない。休ませれば戻る</t>
+          <t xml:space="preserve">四年に一度の大舞台です。前回、遠くから見上げていた景色に…今度は近づきたいんです</t>
         </is>
       </c>
     </row>
     <row r="432" ht="40" customHeight="1">
       <c r="A432" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_COACH_LINES.heavy[6]</t>
+          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES.fighter.polite[2].text</t>
         </is>
       </c>
       <c r="B432" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">15-その他</t>
+          <t xml:space="preserve">14-PPV・対抗戦・トーナメント</t>
         </is>
       </c>
       <c r="C432" t="inlineStr" s="2">
@@ -15747,29 +15842,34 @@
       </c>
       <c r="D432" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">HEAT_STATE_COACH_LINES</t>
+          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES</t>
         </is>
       </c>
       <c r="E432" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heavy[6]</t>
+          <t xml:space="preserve">fighter.polite[2].text</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">丁寧</t>
         </is>
       </c>
       <c r="H432" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今の{name}にやらせるのは、怪我を買うようなものだ</t>
+          <t xml:space="preserve">もうすぐエントリー発表ですね。あの狭き門をくぐる資格が自分にあるのか。…試させてください</t>
         </is>
       </c>
     </row>
     <row r="433" ht="40" customHeight="1">
       <c r="A433" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_COACH_LINES.heavy[7]</t>
+          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES.fighter.polite[3].text</t>
         </is>
       </c>
       <c r="B433" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">15-その他</t>
+          <t xml:space="preserve">14-PPV・対抗戦・トーナメント</t>
         </is>
       </c>
       <c r="C433" t="inlineStr" s="2">
@@ -15779,29 +15879,34 @@
       </c>
       <c r="D433" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">HEAT_STATE_COACH_LINES</t>
+          <t xml:space="preserve">TENCHOSEN_PREEVENT_LINES</t>
         </is>
       </c>
       <c r="E433" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heavy[7]</t>
+          <t xml:space="preserve">fighter.polite[3].text</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">丁寧</t>
         </is>
       </c>
       <c r="H433" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}、一週抜けばまた入るようになる。それだけの話だ</t>
+          <t xml:space="preserve">四年後も同じ舞台に立てるとは、限りません。…だからこそ、今回を大切に戦わせてください</t>
         </is>
       </c>
     </row>
     <row r="434" ht="40" customHeight="1">
       <c r="A434" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CRISIS_DIALOGUE.enter.ojousama[1]</t>
+          <t xml:space="preserve">HEAT_STATE_COACH_LINES.fresh[1]</t>
         </is>
       </c>
       <c r="B434" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18-経営危機・エンディング</t>
+          <t xml:space="preserve">15-その他</t>
         </is>
       </c>
       <c r="C434" t="inlineStr" s="2">
@@ -15811,34 +15916,29 @@
       </c>
       <c r="D434" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CRISIS_DIALOGUE</t>
+          <t xml:space="preserve">HEAT_STATE_COACH_LINES</t>
         </is>
       </c>
       <c r="E434" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">enter.ojousama[1]</t>
-        </is>
-      </c>
-      <c r="F434" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">お嬢様</t>
+          <t xml:space="preserve">fresh[1]</t>
         </is>
       </c>
       <c r="H434" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">資金繰りが、そのような状況に……? わたくしに何かできることはございまして?</t>
+          <t xml:space="preserve">{name}、今日はよく動いてる。仕込むなら今だ</t>
         </is>
       </c>
     </row>
     <row r="435" ht="40" customHeight="1">
       <c r="A435" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CRISIS_DIALOGUE.enter.ojousama[2]</t>
+          <t xml:space="preserve">HEAT_STATE_COACH_LINES.fresh[2]</t>
         </is>
       </c>
       <c r="B435" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18-経営危機・エンディング</t>
+          <t xml:space="preserve">15-その他</t>
         </is>
       </c>
       <c r="C435" t="inlineStr" s="2">
@@ -15848,34 +15948,29 @@
       </c>
       <c r="D435" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CRISIS_DIALOGUE</t>
+          <t xml:space="preserve">HEAT_STATE_COACH_LINES</t>
         </is>
       </c>
       <c r="E435" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">enter.ojousama[2]</t>
-        </is>
-      </c>
-      <c r="F435" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">お嬢様</t>
+          <t xml:space="preserve">fresh[2]</t>
         </is>
       </c>
       <c r="H435" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">動揺していると思われるのは癪ですけれど……正直、不安ですわ</t>
+          <t xml:space="preserve">{name}の体が、新しい動きを素直に飲み込んでいる</t>
         </is>
       </c>
     </row>
     <row r="436" ht="40" customHeight="1">
       <c r="A436" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CRISIS_DIALOGUE.enter.delinquent[1]</t>
+          <t xml:space="preserve">HEAT_STATE_COACH_LINES.fresh[3]</t>
         </is>
       </c>
       <c r="B436" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18-経営危機・エンディング</t>
+          <t xml:space="preserve">15-その他</t>
         </is>
       </c>
       <c r="C436" t="inlineStr" s="2">
@@ -15885,34 +15980,29 @@
       </c>
       <c r="D436" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CRISIS_DIALOGUE</t>
+          <t xml:space="preserve">HEAT_STATE_COACH_LINES</t>
         </is>
       </c>
       <c r="E436" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">enter.delinquent[1]</t>
-        </is>
-      </c>
-      <c r="F436" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">ヤンキー</t>
+          <t xml:space="preserve">fresh[3]</t>
         </is>
       </c>
       <c r="H436" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">マジかよ。社長、立て直せんのか? まあ、やるしかねぇんだろうな</t>
+          <t xml:space="preserve">今の{name}なら、多少きつくしても全部持っていく</t>
         </is>
       </c>
     </row>
     <row r="437" ht="40" customHeight="1">
       <c r="A437" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CRISIS_DIALOGUE.enter.delinquent[2]</t>
+          <t xml:space="preserve">HEAT_STATE_COACH_LINES.fresh[4]</t>
         </is>
       </c>
       <c r="B437" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18-経営危機・エンディング</t>
+          <t xml:space="preserve">15-その他</t>
         </is>
       </c>
       <c r="C437" t="inlineStr" s="2">
@@ -15922,34 +16012,29 @@
       </c>
       <c r="D437" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CRISIS_DIALOGUE</t>
+          <t xml:space="preserve">HEAT_STATE_COACH_LINES</t>
         </is>
       </c>
       <c r="E437" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">enter.delinquent[2]</t>
-        </is>
-      </c>
-      <c r="F437" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">ヤンキー</t>
+          <t xml:space="preserve">fresh[4]</t>
         </is>
       </c>
       <c r="H437" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ったく、潰れんの勘弁してくれよ。私のリングを取り上げるな</t>
+          <t xml:space="preserve">{name}の足が軽い。こういう週こそ厚く積ませたい</t>
         </is>
       </c>
     </row>
     <row r="438" ht="40" customHeight="1">
       <c r="A438" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CRISIS_DIALOGUE.enter.cool[1]</t>
+          <t xml:space="preserve">HEAT_STATE_COACH_LINES.fresh[5]</t>
         </is>
       </c>
       <c r="B438" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18-経営危機・エンディング</t>
+          <t xml:space="preserve">15-その他</t>
         </is>
       </c>
       <c r="C438" t="inlineStr" s="2">
@@ -15959,34 +16044,29 @@
       </c>
       <c r="D438" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CRISIS_DIALOGUE</t>
+          <t xml:space="preserve">HEAT_STATE_COACH_LINES</t>
         </is>
       </c>
       <c r="E438" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">enter.cool[1]</t>
-        </is>
-      </c>
-      <c r="F438" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">クール</t>
+          <t xml:space="preserve">fresh[5]</t>
         </is>
       </c>
       <c r="H438" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……そうか。残された時間は、限られているということだな</t>
+          <t xml:space="preserve">{name}、伸びる顔をしている。今日の一本は残るぞ</t>
         </is>
       </c>
     </row>
     <row r="439" ht="40" customHeight="1">
       <c r="A439" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CRISIS_DIALOGUE.enter.cool[2]</t>
+          <t xml:space="preserve">HEAT_STATE_COACH_LINES.fresh[6]</t>
         </is>
       </c>
       <c r="B439" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18-経営危機・エンディング</t>
+          <t xml:space="preserve">15-その他</t>
         </is>
       </c>
       <c r="C439" t="inlineStr" s="2">
@@ -15996,34 +16076,29 @@
       </c>
       <c r="D439" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CRISIS_DIALOGUE</t>
+          <t xml:space="preserve">HEAT_STATE_COACH_LINES</t>
         </is>
       </c>
       <c r="E439" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">enter.cool[2]</t>
-        </is>
-      </c>
-      <c r="F439" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">クール</t>
+          <t xml:space="preserve">fresh[6]</t>
         </is>
       </c>
       <c r="H439" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やるしかない。私にできることは、リングで応える、それだけだ</t>
+          <t xml:space="preserve">{name}は休み明けの体だ。一番よく入る時期に来ている</t>
         </is>
       </c>
     </row>
     <row r="440" ht="40" customHeight="1">
       <c r="A440" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CRISIS_DIALOGUE.enter.seductive[1]</t>
+          <t xml:space="preserve">HEAT_STATE_COACH_LINES.fresh[7]</t>
         </is>
       </c>
       <c r="B440" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18-経営危機・エンディング</t>
+          <t xml:space="preserve">15-その他</t>
         </is>
       </c>
       <c r="C440" t="inlineStr" s="2">
@@ -16033,34 +16108,29 @@
       </c>
       <c r="D440" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CRISIS_DIALOGUE</t>
+          <t xml:space="preserve">HEAT_STATE_COACH_LINES</t>
         </is>
       </c>
       <c r="E440" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">enter.seductive[1]</t>
-        </is>
-      </c>
-      <c r="F440" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">蠱惑</t>
+          <t xml:space="preserve">fresh[7]</t>
         </is>
       </c>
       <c r="H440" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら……興味深い局面ね。社長、楽しませてくださる?</t>
+          <t xml:space="preserve">{name}、今週は当たり週だ。使うなら、ここで使え</t>
         </is>
       </c>
     </row>
     <row r="441" ht="40" customHeight="1">
       <c r="A441" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CRISIS_DIALOGUE.enter.seductive[2]</t>
+          <t xml:space="preserve">HEAT_STATE_COACH_LINES.warm[1]</t>
         </is>
       </c>
       <c r="B441" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18-経営危機・エンディング</t>
+          <t xml:space="preserve">15-その他</t>
         </is>
       </c>
       <c r="C441" t="inlineStr" s="2">
@@ -16070,34 +16140,29 @@
       </c>
       <c r="D441" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CRISIS_DIALOGUE</t>
+          <t xml:space="preserve">HEAT_STATE_COACH_LINES</t>
         </is>
       </c>
       <c r="E441" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">enter.seductive[2]</t>
-        </is>
-      </c>
-      <c r="F441" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">蠱惑</t>
+          <t xml:space="preserve">warm[1]</t>
         </is>
       </c>
       <c r="H441" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">破滅の足音、というやつかしら。それでも、わたくしは舞台に立つわ</t>
+          <t xml:space="preserve">{name}、悪くはない。ただ、先週ほどは入っていかない</t>
         </is>
       </c>
     </row>
     <row r="442" ht="40" customHeight="1">
       <c r="A442" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CRISIS_DIALOGUE.enter.polite[1]</t>
+          <t xml:space="preserve">HEAT_STATE_COACH_LINES.warm[2]</t>
         </is>
       </c>
       <c r="B442" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18-経営危機・エンディング</t>
+          <t xml:space="preserve">15-その他</t>
         </is>
       </c>
       <c r="C442" t="inlineStr" s="2">
@@ -16107,34 +16172,29 @@
       </c>
       <c r="D442" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CRISIS_DIALOGUE</t>
+          <t xml:space="preserve">HEAT_STATE_COACH_LINES</t>
         </is>
       </c>
       <c r="E442" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">enter.polite[1]</t>
-        </is>
-      </c>
-      <c r="F442" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">丁寧</t>
+          <t xml:space="preserve">warm[2]</t>
         </is>
       </c>
       <c r="H442" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">資金が、そのような状態でしたか……。私にできることがあれば、何でもおっしゃってください</t>
+          <t xml:space="preserve">{name}の伸びが少し鈍ってきた。詰めすぎたか</t>
         </is>
       </c>
     </row>
     <row r="443" ht="40" customHeight="1">
       <c r="A443" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CRISIS_DIALOGUE.enter.polite[2]</t>
+          <t xml:space="preserve">HEAT_STATE_COACH_LINES.warm[3]</t>
         </is>
       </c>
       <c r="B443" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18-経営危機・エンディング</t>
+          <t xml:space="preserve">15-その他</t>
         </is>
       </c>
       <c r="C443" t="inlineStr" s="2">
@@ -16144,34 +16204,29 @@
       </c>
       <c r="D443" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CRISIS_DIALOGUE</t>
+          <t xml:space="preserve">HEAT_STATE_COACH_LINES</t>
         </is>
       </c>
       <c r="E443" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">enter.polite[2]</t>
-        </is>
-      </c>
-      <c r="F443" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">丁寧</t>
+          <t xml:space="preserve">warm[3]</t>
         </is>
       </c>
       <c r="H443" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">諦めずに、最後まで力を尽くしましょう</t>
+          <t xml:space="preserve">{name}、同じメニューなのに返りが薄い。そろそろ一息か</t>
         </is>
       </c>
     </row>
     <row r="444" ht="40" customHeight="1">
       <c r="A444" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CRISIS_DIALOGUE.enter.standard[1]</t>
+          <t xml:space="preserve">HEAT_STATE_COACH_LINES.warm[4]</t>
         </is>
       </c>
       <c r="B444" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18-経営危機・エンディング</t>
+          <t xml:space="preserve">15-その他</t>
         </is>
       </c>
       <c r="C444" t="inlineStr" s="2">
@@ -16181,34 +16236,29 @@
       </c>
       <c r="D444" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CRISIS_DIALOGUE</t>
+          <t xml:space="preserve">HEAT_STATE_COACH_LINES</t>
         </is>
       </c>
       <c r="E444" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">enter.standard[1]</t>
-        </is>
-      </c>
-      <c r="F444" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">標準</t>
+          <t xml:space="preserve">warm[4]</t>
         </is>
       </c>
       <c r="H444" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、諦めずに頑張りましょう。何とかなるはずです</t>
+          <t xml:space="preserve">{name}、動けてはいる。だが、切れがひとつ落ちている</t>
         </is>
       </c>
     </row>
     <row r="445" ht="40" customHeight="1">
       <c r="A445" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CRISIS_DIALOGUE.enter.standard[2]</t>
+          <t xml:space="preserve">HEAT_STATE_COACH_LINES.warm[5]</t>
         </is>
       </c>
       <c r="B445" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18-経営危機・エンディング</t>
+          <t xml:space="preserve">15-その他</t>
         </is>
       </c>
       <c r="C445" t="inlineStr" s="2">
@@ -16218,34 +16268,29 @@
       </c>
       <c r="D445" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CRISIS_DIALOGUE</t>
+          <t xml:space="preserve">HEAT_STATE_COACH_LINES</t>
         </is>
       </c>
       <c r="E445" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">enter.standard[2]</t>
-        </is>
-      </c>
-      <c r="F445" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">標準</t>
+          <t xml:space="preserve">warm[5]</t>
         </is>
       </c>
       <c r="H445" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私たちにできることを、ひとつずつやっていきましょう</t>
+          <t xml:space="preserve">{name}の体が慣れてきた。効きが落ちる頃合いだ</t>
         </is>
       </c>
     </row>
     <row r="446" ht="40" customHeight="1">
       <c r="A446" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GAMEOVER_LINES.fighter.ojousama.high[1]</t>
+          <t xml:space="preserve">HEAT_STATE_COACH_LINES.warm[6]</t>
         </is>
       </c>
       <c r="B446" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18-経営危機・エンディング</t>
+          <t xml:space="preserve">15-その他</t>
         </is>
       </c>
       <c r="C446" t="inlineStr" s="2">
@@ -16255,34 +16300,29 @@
       </c>
       <c r="D446" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GAMEOVER_LINES</t>
+          <t xml:space="preserve">HEAT_STATE_COACH_LINES</t>
         </is>
       </c>
       <c r="E446" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.ojousama.high[1]</t>
-        </is>
-      </c>
-      <c r="F446" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">お嬢様</t>
+          <t xml:space="preserve">warm[6]</t>
         </is>
       </c>
       <c r="H446" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">みなさま、本当にお世話になりましたわ。この団体で過ごした日々は、わたくしの誇りですの</t>
+          <t xml:space="preserve">{name}、今週も同じ調子で行くなら、得は薄いぞ</t>
         </is>
       </c>
     </row>
     <row r="447" ht="40" customHeight="1">
       <c r="A447" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GAMEOVER_LINES.fighter.ojousama.high[2]</t>
+          <t xml:space="preserve">HEAT_STATE_COACH_LINES.warm[7]</t>
         </is>
       </c>
       <c r="B447" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18-経営危機・エンディング</t>
+          <t xml:space="preserve">15-その他</t>
         </is>
       </c>
       <c r="C447" t="inlineStr" s="2">
@@ -16292,34 +16332,29 @@
       </c>
       <c r="D447" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GAMEOVER_LINES</t>
+          <t xml:space="preserve">HEAT_STATE_COACH_LINES</t>
         </is>
       </c>
       <c r="E447" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.ojousama.high[2]</t>
-        </is>
-      </c>
-      <c r="F447" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">お嬢様</t>
+          <t xml:space="preserve">warm[7]</t>
         </is>
       </c>
       <c r="H447" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……負けは認めますわ。でも、わたくし、ここで戦えたことを後悔いたしません</t>
+          <t xml:space="preserve">{name}にきついのを続けるか。…見極めどきだな</t>
         </is>
       </c>
     </row>
     <row r="448" ht="40" customHeight="1">
       <c r="A448" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GAMEOVER_LINES.fighter.ojousama.high[3]</t>
+          <t xml:space="preserve">HEAT_STATE_COACH_LINES.heavy[1]</t>
         </is>
       </c>
       <c r="B448" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18-経営危機・エンディング</t>
+          <t xml:space="preserve">15-その他</t>
         </is>
       </c>
       <c r="C448" t="inlineStr" s="2">
@@ -16329,34 +16364,29 @@
       </c>
       <c r="D448" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GAMEOVER_LINES</t>
+          <t xml:space="preserve">HEAT_STATE_COACH_LINES</t>
         </is>
       </c>
       <c r="E448" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.ojousama.high[3]</t>
-        </is>
-      </c>
-      <c r="F448" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">お嬢様</t>
+          <t xml:space="preserve">heavy[1]</t>
         </is>
       </c>
       <c r="H448" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お疲れさま、社長。胸を張って、お顔をお上げくださいまし</t>
+          <t xml:space="preserve">{name}、今日は体が重い。何をやらせても素通りだ</t>
         </is>
       </c>
     </row>
     <row r="449" ht="40" customHeight="1">
       <c r="A449" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GAMEOVER_LINES.fighter.ojousama.mid[1]</t>
+          <t xml:space="preserve">HEAT_STATE_COACH_LINES.heavy[2]</t>
         </is>
       </c>
       <c r="B449" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18-経営危機・エンディング</t>
+          <t xml:space="preserve">15-その他</t>
         </is>
       </c>
       <c r="C449" t="inlineStr" s="2">
@@ -16366,34 +16396,29 @@
       </c>
       <c r="D449" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GAMEOVER_LINES</t>
+          <t xml:space="preserve">HEAT_STATE_COACH_LINES</t>
         </is>
       </c>
       <c r="E449" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.ojousama.mid[1]</t>
-        </is>
-      </c>
-      <c r="F449" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">お嬢様</t>
+          <t xml:space="preserve">heavy[2]</t>
         </is>
       </c>
       <c r="H449" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあ……こんなことになりますの……</t>
+          <t xml:space="preserve">今の{name}に課しても、削るだけで何も積まれない</t>
         </is>
       </c>
     </row>
     <row r="450" ht="40" customHeight="1">
       <c r="A450" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GAMEOVER_LINES.fighter.ojousama.mid[2]</t>
+          <t xml:space="preserve">HEAT_STATE_COACH_LINES.heavy[3]</t>
         </is>
       </c>
       <c r="B450" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18-経営危機・エンディング</t>
+          <t xml:space="preserve">15-その他</t>
         </is>
       </c>
       <c r="C450" t="inlineStr" s="2">
@@ -16403,34 +16428,29 @@
       </c>
       <c r="D450" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GAMEOVER_LINES</t>
+          <t xml:space="preserve">HEAT_STATE_COACH_LINES</t>
         </is>
       </c>
       <c r="E450" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.ojousama.mid[2]</t>
-        </is>
-      </c>
-      <c r="F450" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">お嬢様</t>
+          <t xml:space="preserve">heavy[3]</t>
         </is>
       </c>
       <c r="H450" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次の場所は、わたくしが探さなくてはなりませんのね</t>
+          <t xml:space="preserve">{name}は追い込みすぎだ。一度、外してやってくれ</t>
         </is>
       </c>
     </row>
     <row r="451" ht="40" customHeight="1">
       <c r="A451" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GAMEOVER_LINES.fighter.ojousama.mid[3]</t>
+          <t xml:space="preserve">HEAT_STATE_COACH_LINES.heavy[4]</t>
         </is>
       </c>
       <c r="B451" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18-経営危機・エンディング</t>
+          <t xml:space="preserve">15-その他</t>
         </is>
       </c>
       <c r="C451" t="inlineStr" s="2">
@@ -16440,34 +16460,29 @@
       </c>
       <c r="D451" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GAMEOVER_LINES</t>
+          <t xml:space="preserve">HEAT_STATE_COACH_LINES</t>
         </is>
       </c>
       <c r="E451" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.ojousama.mid[3]</t>
-        </is>
-      </c>
-      <c r="F451" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">お嬢様</t>
+          <t xml:space="preserve">heavy[4]</t>
         </is>
       </c>
       <c r="H451" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……心の整理が、つきませんわ</t>
+          <t xml:space="preserve">{name}、汗はかいている。だが、身についてはいない</t>
         </is>
       </c>
     </row>
     <row r="452" ht="40" customHeight="1">
       <c r="A452" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GAMEOVER_LINES.fighter.ojousama.low[1]</t>
+          <t xml:space="preserve">HEAT_STATE_COACH_LINES.heavy[5]</t>
         </is>
       </c>
       <c r="B452" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18-経営危機・エンディング</t>
+          <t xml:space="preserve">15-その他</t>
         </is>
       </c>
       <c r="C452" t="inlineStr" s="2">
@@ -16477,34 +16492,29 @@
       </c>
       <c r="D452" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GAMEOVER_LINES</t>
+          <t xml:space="preserve">HEAT_STATE_COACH_LINES</t>
         </is>
       </c>
       <c r="E452" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.ojousama.low[1]</t>
-        </is>
-      </c>
-      <c r="F452" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">お嬢様</t>
+          <t xml:space="preserve">heavy[5]</t>
         </is>
       </c>
       <c r="H452" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">冗談ではありませんわ。わたくしの誇りは、どうなりますの</t>
+          <t xml:space="preserve">{name}の体はもう受け付けていない。休ませれば戻る</t>
         </is>
       </c>
     </row>
     <row r="453" ht="40" customHeight="1">
       <c r="A453" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GAMEOVER_LINES.fighter.ojousama.low[2]</t>
+          <t xml:space="preserve">HEAT_STATE_COACH_LINES.heavy[6]</t>
         </is>
       </c>
       <c r="B453" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18-経営危機・エンディング</t>
+          <t xml:space="preserve">15-その他</t>
         </is>
       </c>
       <c r="C453" t="inlineStr" s="2">
@@ -16514,34 +16524,29 @@
       </c>
       <c r="D453" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GAMEOVER_LINES</t>
+          <t xml:space="preserve">HEAT_STATE_COACH_LINES</t>
         </is>
       </c>
       <c r="E453" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.ojousama.low[2]</t>
-        </is>
-      </c>
-      <c r="F453" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">お嬢様</t>
+          <t xml:space="preserve">heavy[6]</t>
         </is>
       </c>
       <c r="H453" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最初から信用すべきではありませんでしたのね</t>
+          <t xml:space="preserve">今の{name}にやらせるのは、怪我を買うようなものだ</t>
         </is>
       </c>
     </row>
     <row r="454" ht="40" customHeight="1">
       <c r="A454" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GAMEOVER_LINES.fighter.ojousama.low[3]</t>
+          <t xml:space="preserve">HEAT_STATE_COACH_LINES.heavy[7]</t>
         </is>
       </c>
       <c r="B454" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18-経営危機・エンディング</t>
+          <t xml:space="preserve">15-その他</t>
         </is>
       </c>
       <c r="C454" t="inlineStr" s="2">
@@ -16551,29 +16556,24 @@
       </c>
       <c r="D454" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GAMEOVER_LINES</t>
+          <t xml:space="preserve">HEAT_STATE_COACH_LINES</t>
         </is>
       </c>
       <c r="E454" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.ojousama.low[3]</t>
-        </is>
-      </c>
-      <c r="F454" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">お嬢様</t>
+          <t xml:space="preserve">heavy[7]</t>
         </is>
       </c>
       <c r="H454" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……無能、と申し上げてもよろしいかしら</t>
+          <t xml:space="preserve">{name}、一週抜けばまた入るようになる。それだけの話だ</t>
         </is>
       </c>
     </row>
     <row r="455" ht="40" customHeight="1">
       <c r="A455" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GAMEOVER_LINES.fighter.delinquent.high[1]</t>
+          <t xml:space="preserve">CRISIS_DIALOGUE.enter.ojousama[1]</t>
         </is>
       </c>
       <c r="B455" t="inlineStr" s="2">
@@ -16588,29 +16588,29 @@
       </c>
       <c r="D455" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GAMEOVER_LINES</t>
+          <t xml:space="preserve">CRISIS_DIALOGUE</t>
         </is>
       </c>
       <c r="E455" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.delinquent.high[1]</t>
+          <t xml:space="preserve">enter.ojousama[1]</t>
         </is>
       </c>
       <c r="F455" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ヤンキー</t>
+          <t xml:space="preserve">お嬢様</t>
         </is>
       </c>
       <c r="H455" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ちっ、潰れちまったか。……でもまあ、悪くなかったぜ</t>
+          <t xml:space="preserve">資金繰りが、そのような状況に……? わたくしに何かできることはございまして?</t>
         </is>
       </c>
     </row>
     <row r="456" ht="40" customHeight="1">
       <c r="A456" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GAMEOVER_LINES.fighter.delinquent.high[2]</t>
+          <t xml:space="preserve">CRISIS_DIALOGUE.enter.ojousama[2]</t>
         </is>
       </c>
       <c r="B456" t="inlineStr" s="2">
@@ -16625,29 +16625,29 @@
       </c>
       <c r="D456" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GAMEOVER_LINES</t>
+          <t xml:space="preserve">CRISIS_DIALOGUE</t>
         </is>
       </c>
       <c r="E456" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.delinquent.high[2]</t>
+          <t xml:space="preserve">enter.ojousama[2]</t>
         </is>
       </c>
       <c r="F456" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ヤンキー</t>
+          <t xml:space="preserve">お嬢様</t>
         </is>
       </c>
       <c r="H456" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、頭は下げなくていい。私は私で、次のリングへ行く</t>
+          <t xml:space="preserve">動揺していると思われるのは癪ですけれど……正直、不安ですわ</t>
         </is>
       </c>
     </row>
     <row r="457" ht="40" customHeight="1">
       <c r="A457" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GAMEOVER_LINES.fighter.delinquent.high[3]</t>
+          <t xml:space="preserve">CRISIS_DIALOGUE.enter.delinquent[1]</t>
         </is>
       </c>
       <c r="B457" t="inlineStr" s="2">
@@ -16662,12 +16662,12 @@
       </c>
       <c r="D457" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GAMEOVER_LINES</t>
+          <t xml:space="preserve">CRISIS_DIALOGUE</t>
         </is>
       </c>
       <c r="E457" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.delinquent.high[3]</t>
+          <t xml:space="preserve">enter.delinquent[1]</t>
         </is>
       </c>
       <c r="F457" t="inlineStr" s="2">
@@ -16677,14 +16677,14 @@
       </c>
       <c r="H457" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">泣いてんじゃねぇよ。私らはまた、どっかで戦うんだろ</t>
+          <t xml:space="preserve">マジかよ。社長、立て直せんのか? まあ、やるしかねぇんだろうな</t>
         </is>
       </c>
     </row>
     <row r="458" ht="40" customHeight="1">
       <c r="A458" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GAMEOVER_LINES.fighter.delinquent.mid[1]</t>
+          <t xml:space="preserve">CRISIS_DIALOGUE.enter.delinquent[2]</t>
         </is>
       </c>
       <c r="B458" t="inlineStr" s="2">
@@ -16699,12 +16699,12 @@
       </c>
       <c r="D458" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GAMEOVER_LINES</t>
+          <t xml:space="preserve">CRISIS_DIALOGUE</t>
         </is>
       </c>
       <c r="E458" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.delinquent.mid[1]</t>
+          <t xml:space="preserve">enter.delinquent[2]</t>
         </is>
       </c>
       <c r="F458" t="inlineStr" s="2">
@@ -16714,14 +16714,14 @@
       </c>
       <c r="H458" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">は? マジかよ。冗談じゃねぇ</t>
+          <t xml:space="preserve">ったく、潰れんの勘弁してくれよ。私のリングを取り上げるな</t>
         </is>
       </c>
     </row>
     <row r="459" ht="40" customHeight="1">
       <c r="A459" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GAMEOVER_LINES.fighter.delinquent.mid[2]</t>
+          <t xml:space="preserve">CRISIS_DIALOGUE.enter.cool[1]</t>
         </is>
       </c>
       <c r="B459" t="inlineStr" s="2">
@@ -16736,29 +16736,29 @@
       </c>
       <c r="D459" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GAMEOVER_LINES</t>
+          <t xml:space="preserve">CRISIS_DIALOGUE</t>
         </is>
       </c>
       <c r="E459" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.delinquent.mid[2]</t>
+          <t xml:space="preserve">enter.cool[1]</t>
         </is>
       </c>
       <c r="F459" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ヤンキー</t>
+          <t xml:space="preserve">クール</t>
         </is>
       </c>
       <c r="H459" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ったく、潰れる団体に入っちまったのが運の尽きかよ</t>
+          <t xml:space="preserve">……そうか。残された時間は、限られているということだな</t>
         </is>
       </c>
     </row>
     <row r="460" ht="40" customHeight="1">
       <c r="A460" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GAMEOVER_LINES.fighter.delinquent.mid[3]</t>
+          <t xml:space="preserve">CRISIS_DIALOGUE.enter.cool[2]</t>
         </is>
       </c>
       <c r="B460" t="inlineStr" s="2">
@@ -16773,29 +16773,29 @@
       </c>
       <c r="D460" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GAMEOVER_LINES</t>
+          <t xml:space="preserve">CRISIS_DIALOGUE</t>
         </is>
       </c>
       <c r="E460" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.delinquent.mid[3]</t>
+          <t xml:space="preserve">enter.cool[2]</t>
         </is>
       </c>
       <c r="F460" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ヤンキー</t>
+          <t xml:space="preserve">クール</t>
         </is>
       </c>
       <c r="H460" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……次、探すしかねぇな</t>
+          <t xml:space="preserve">やるしかない。私にできることは、リングで応える、それだけだ</t>
         </is>
       </c>
     </row>
     <row r="461" ht="40" customHeight="1">
       <c r="A461" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GAMEOVER_LINES.fighter.delinquent.low[1]</t>
+          <t xml:space="preserve">CRISIS_DIALOGUE.enter.seductive[1]</t>
         </is>
       </c>
       <c r="B461" t="inlineStr" s="2">
@@ -16810,29 +16810,29 @@
       </c>
       <c r="D461" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GAMEOVER_LINES</t>
+          <t xml:space="preserve">CRISIS_DIALOGUE</t>
         </is>
       </c>
       <c r="E461" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.delinquent.low[1]</t>
+          <t xml:space="preserve">enter.seductive[1]</t>
         </is>
       </c>
       <c r="F461" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ヤンキー</t>
+          <t xml:space="preserve">蠱惑</t>
         </is>
       </c>
       <c r="H461" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふざけんな。私のキャリア、どうしてくれんだ</t>
+          <t xml:space="preserve">あら……興味深い局面ね。社長、楽しませてくださる?</t>
         </is>
       </c>
     </row>
     <row r="462" ht="40" customHeight="1">
       <c r="A462" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GAMEOVER_LINES.fighter.delinquent.low[2]</t>
+          <t xml:space="preserve">CRISIS_DIALOGUE.enter.seductive[2]</t>
         </is>
       </c>
       <c r="B462" t="inlineStr" s="2">
@@ -16847,29 +16847,29 @@
       </c>
       <c r="D462" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GAMEOVER_LINES</t>
+          <t xml:space="preserve">CRISIS_DIALOGUE</t>
         </is>
       </c>
       <c r="E462" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.delinquent.low[2]</t>
+          <t xml:space="preserve">enter.seductive[2]</t>
         </is>
       </c>
       <c r="F462" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ヤンキー</t>
+          <t xml:space="preserve">蠱惑</t>
         </is>
       </c>
       <c r="H462" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最初から胡散臭いとは思ってたんだ</t>
+          <t xml:space="preserve">破滅の足音、というやつかしら。それでも、わたくしは舞台に立つわ</t>
         </is>
       </c>
     </row>
     <row r="463" ht="40" customHeight="1">
       <c r="A463" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GAMEOVER_LINES.fighter.delinquent.low[3]</t>
+          <t xml:space="preserve">CRISIS_DIALOGUE.enter.polite[1]</t>
         </is>
       </c>
       <c r="B463" t="inlineStr" s="2">
@@ -16884,29 +16884,29 @@
       </c>
       <c r="D463" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GAMEOVER_LINES</t>
+          <t xml:space="preserve">CRISIS_DIALOGUE</t>
         </is>
       </c>
       <c r="E463" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.delinquent.low[3]</t>
+          <t xml:space="preserve">enter.polite[1]</t>
         </is>
       </c>
       <c r="F463" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ヤンキー</t>
+          <t xml:space="preserve">丁寧</t>
         </is>
       </c>
       <c r="H463" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">失せろ。お前の顔は二度と見たくねぇ</t>
+          <t xml:space="preserve">資金が、そのような状態でしたか……。私にできることがあれば、何でもおっしゃってください</t>
         </is>
       </c>
     </row>
     <row r="464" ht="40" customHeight="1">
       <c r="A464" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GAMEOVER_LINES.fighter.cool.high[1]</t>
+          <t xml:space="preserve">CRISIS_DIALOGUE.enter.polite[2]</t>
         </is>
       </c>
       <c r="B464" t="inlineStr" s="2">
@@ -16921,29 +16921,29 @@
       </c>
       <c r="D464" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GAMEOVER_LINES</t>
+          <t xml:space="preserve">CRISIS_DIALOGUE</t>
         </is>
       </c>
       <c r="E464" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.cool.high[1]</t>
+          <t xml:space="preserve">enter.polite[2]</t>
         </is>
       </c>
       <c r="F464" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">クール</t>
+          <t xml:space="preserve">丁寧</t>
         </is>
       </c>
       <c r="H464" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……世話になった</t>
+          <t xml:space="preserve">諦めずに、最後まで力を尽くしましょう</t>
         </is>
       </c>
     </row>
     <row r="465" ht="40" customHeight="1">
       <c r="A465" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GAMEOVER_LINES.fighter.cool.high[2]</t>
+          <t xml:space="preserve">CRISIS_DIALOGUE.enter.standard[1]</t>
         </is>
       </c>
       <c r="B465" t="inlineStr" s="2">
@@ -16958,29 +16958,29 @@
       </c>
       <c r="D465" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GAMEOVER_LINES</t>
+          <t xml:space="preserve">CRISIS_DIALOGUE</t>
         </is>
       </c>
       <c r="E465" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.cool.high[2]</t>
+          <t xml:space="preserve">enter.standard[1]</t>
         </is>
       </c>
       <c r="F465" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">クール</t>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="H465" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここで戦えてよかった。それだけは確かだ</t>
+          <t xml:space="preserve">社長、諦めずに頑張りましょう。何とかなるはずです</t>
         </is>
       </c>
     </row>
     <row r="466" ht="40" customHeight="1">
       <c r="A466" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GAMEOVER_LINES.fighter.cool.high[3]</t>
+          <t xml:space="preserve">CRISIS_DIALOGUE.enter.standard[2]</t>
         </is>
       </c>
       <c r="B466" t="inlineStr" s="2">
@@ -16995,29 +16995,29 @@
       </c>
       <c r="D466" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GAMEOVER_LINES</t>
+          <t xml:space="preserve">CRISIS_DIALOGUE</t>
         </is>
       </c>
       <c r="E466" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.cool.high[3]</t>
+          <t xml:space="preserve">enter.standard[2]</t>
         </is>
       </c>
       <c r="F466" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">クール</t>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="H466" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……次のリング、探す。それだけだ</t>
+          <t xml:space="preserve">私たちにできることを、ひとつずつやっていきましょう</t>
         </is>
       </c>
     </row>
     <row r="467" ht="40" customHeight="1">
       <c r="A467" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GAMEOVER_LINES.fighter.cool.mid[1]</t>
+          <t xml:space="preserve">GAMEOVER_LINES.fighter.ojousama.high[1]</t>
         </is>
       </c>
       <c r="B467" t="inlineStr" s="2">
@@ -17037,24 +17037,24 @@
       </c>
       <c r="E467" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.cool.mid[1]</t>
+          <t xml:space="preserve">fighter.ojousama.high[1]</t>
         </is>
       </c>
       <c r="F467" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">クール</t>
+          <t xml:space="preserve">お嬢様</t>
         </is>
       </c>
       <c r="H467" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……終わったか</t>
+          <t xml:space="preserve">みなさま、本当にお世話になりましたわ。この団体で過ごした日々は、わたくしの誇りですの</t>
         </is>
       </c>
     </row>
     <row r="468" ht="40" customHeight="1">
       <c r="A468" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GAMEOVER_LINES.fighter.cool.mid[2]</t>
+          <t xml:space="preserve">GAMEOVER_LINES.fighter.ojousama.high[2]</t>
         </is>
       </c>
       <c r="B468" t="inlineStr" s="2">
@@ -17074,24 +17074,24 @@
       </c>
       <c r="E468" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.cool.mid[2]</t>
+          <t xml:space="preserve">fighter.ojousama.high[2]</t>
         </is>
       </c>
       <c r="F468" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">クール</t>
+          <t xml:space="preserve">お嬢様</t>
         </is>
       </c>
       <c r="H468" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次を探すしかない</t>
+          <t xml:space="preserve">……負けは認めますわ。でも、わたくし、ここで戦えたことを後悔いたしません</t>
         </is>
       </c>
     </row>
     <row r="469" ht="40" customHeight="1">
       <c r="A469" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GAMEOVER_LINES.fighter.cool.low[1]</t>
+          <t xml:space="preserve">GAMEOVER_LINES.fighter.ojousama.high[3]</t>
         </is>
       </c>
       <c r="B469" t="inlineStr" s="2">
@@ -17111,24 +17111,24 @@
       </c>
       <c r="E469" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.cool.low[1]</t>
+          <t xml:space="preserve">fighter.ojousama.high[3]</t>
         </is>
       </c>
       <c r="F469" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">クール</t>
+          <t xml:space="preserve">お嬢様</t>
         </is>
       </c>
       <c r="H469" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">予想通りだ</t>
+          <t xml:space="preserve">お疲れさま、社長。胸を張って、お顔をお上げくださいまし</t>
         </is>
       </c>
     </row>
     <row r="470" ht="40" customHeight="1">
       <c r="A470" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GAMEOVER_LINES.fighter.cool.low[2]</t>
+          <t xml:space="preserve">GAMEOVER_LINES.fighter.ojousama.mid[1]</t>
         </is>
       </c>
       <c r="B470" t="inlineStr" s="2">
@@ -17148,24 +17148,24 @@
       </c>
       <c r="E470" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.cool.low[2]</t>
+          <t xml:space="preserve">fighter.ojousama.mid[1]</t>
         </is>
       </c>
       <c r="F470" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">クール</t>
+          <t xml:space="preserve">お嬢様</t>
         </is>
       </c>
       <c r="H470" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……特に言うことはない</t>
+          <t xml:space="preserve">まあ……こんなことになりますの……</t>
         </is>
       </c>
     </row>
     <row r="471" ht="40" customHeight="1">
       <c r="A471" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GAMEOVER_LINES.fighter.seductive.high[1]</t>
+          <t xml:space="preserve">GAMEOVER_LINES.fighter.ojousama.mid[2]</t>
         </is>
       </c>
       <c r="B471" t="inlineStr" s="2">
@@ -17185,24 +17185,24 @@
       </c>
       <c r="E471" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.seductive.high[1]</t>
+          <t xml:space="preserve">fighter.ojousama.mid[2]</t>
         </is>
       </c>
       <c r="F471" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">蠱惑</t>
+          <t xml:space="preserve">お嬢様</t>
         </is>
       </c>
       <c r="H471" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、終わってしまうのね。……でも、悪くなかったわ</t>
+          <t xml:space="preserve">次の場所は、わたくしが探さなくてはなりませんのね</t>
         </is>
       </c>
     </row>
     <row r="472" ht="40" customHeight="1">
       <c r="A472" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GAMEOVER_LINES.fighter.seductive.high[2]</t>
+          <t xml:space="preserve">GAMEOVER_LINES.fighter.ojousama.mid[3]</t>
         </is>
       </c>
       <c r="B472" t="inlineStr" s="2">
@@ -17222,24 +17222,24 @@
       </c>
       <c r="E472" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.seductive.high[2]</t>
+          <t xml:space="preserve">fighter.ojousama.mid[3]</t>
         </is>
       </c>
       <c r="F472" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">蠱惑</t>
+          <t xml:space="preserve">お嬢様</t>
         </is>
       </c>
       <c r="H472" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この団体で見せた表情、忘れないでくださる?</t>
+          <t xml:space="preserve">……心の整理が、つきませんわ</t>
         </is>
       </c>
     </row>
     <row r="473" ht="40" customHeight="1">
       <c r="A473" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GAMEOVER_LINES.fighter.seductive.high[3]</t>
+          <t xml:space="preserve">GAMEOVER_LINES.fighter.ojousama.low[1]</t>
         </is>
       </c>
       <c r="B473" t="inlineStr" s="2">
@@ -17259,24 +17259,24 @@
       </c>
       <c r="E473" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.seductive.high[3]</t>
+          <t xml:space="preserve">fighter.ojousama.low[1]</t>
         </is>
       </c>
       <c r="F473" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">蠱惑</t>
+          <t xml:space="preserve">お嬢様</t>
         </is>
       </c>
       <c r="H473" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">別れ際の言葉……どうしましょうかしら。でも、感謝しているの。本当よ</t>
+          <t xml:space="preserve">冗談ではありませんわ。わたくしの誇りは、どうなりますの</t>
         </is>
       </c>
     </row>
     <row r="474" ht="40" customHeight="1">
       <c r="A474" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GAMEOVER_LINES.fighter.seductive.mid[1]</t>
+          <t xml:space="preserve">GAMEOVER_LINES.fighter.ojousama.low[2]</t>
         </is>
       </c>
       <c r="B474" t="inlineStr" s="2">
@@ -17296,24 +17296,24 @@
       </c>
       <c r="E474" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.seductive.mid[1]</t>
+          <t xml:space="preserve">fighter.ojousama.low[2]</t>
         </is>
       </c>
       <c r="F474" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">蠱惑</t>
+          <t xml:space="preserve">お嬢様</t>
         </is>
       </c>
       <c r="H474" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あらあら、こんな結末も、また面白いのかしら</t>
+          <t xml:space="preserve">最初から信用すべきではありませんでしたのね</t>
         </is>
       </c>
     </row>
     <row r="475" ht="40" customHeight="1">
       <c r="A475" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GAMEOVER_LINES.fighter.seductive.mid[2]</t>
+          <t xml:space="preserve">GAMEOVER_LINES.fighter.ojousama.low[3]</t>
         </is>
       </c>
       <c r="B475" t="inlineStr" s="2">
@@ -17333,24 +17333,24 @@
       </c>
       <c r="E475" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.seductive.mid[2]</t>
+          <t xml:space="preserve">fighter.ojousama.low[3]</t>
         </is>
       </c>
       <c r="F475" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">蠱惑</t>
+          <t xml:space="preserve">お嬢様</t>
         </is>
       </c>
       <c r="H475" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次の舞台、見つけなくちゃね</t>
+          <t xml:space="preserve">……無能、と申し上げてもよろしいかしら</t>
         </is>
       </c>
     </row>
     <row r="476" ht="40" customHeight="1">
       <c r="A476" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GAMEOVER_LINES.fighter.seductive.mid[3]</t>
+          <t xml:space="preserve">GAMEOVER_LINES.fighter.delinquent.high[1]</t>
         </is>
       </c>
       <c r="B476" t="inlineStr" s="2">
@@ -17370,24 +17370,24 @@
       </c>
       <c r="E476" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.seductive.mid[3]</t>
+          <t xml:space="preserve">fighter.delinquent.high[1]</t>
         </is>
       </c>
       <c r="F476" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">蠱惑</t>
+          <t xml:space="preserve">ヤンキー</t>
         </is>
       </c>
       <c r="H476" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……あぁ、これで終わりなのね</t>
+          <t xml:space="preserve">ちっ、潰れちまったか。……でもまあ、悪くなかったぜ</t>
         </is>
       </c>
     </row>
     <row r="477" ht="40" customHeight="1">
       <c r="A477" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GAMEOVER_LINES.fighter.seductive.low[1]</t>
+          <t xml:space="preserve">GAMEOVER_LINES.fighter.delinquent.high[2]</t>
         </is>
       </c>
       <c r="B477" t="inlineStr" s="2">
@@ -17407,24 +17407,24 @@
       </c>
       <c r="E477" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.seductive.low[1]</t>
+          <t xml:space="preserve">fighter.delinquent.high[2]</t>
         </is>
       </c>
       <c r="F477" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">蠱惑</t>
+          <t xml:space="preserve">ヤンキー</t>
         </is>
       </c>
       <c r="H477" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">夢を見させてくれてありがとう、と言うべきかしら</t>
+          <t xml:space="preserve">社長、頭は下げなくていい。私は私で、次のリングへ行く</t>
         </is>
       </c>
     </row>
     <row r="478" ht="40" customHeight="1">
       <c r="A478" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GAMEOVER_LINES.fighter.seductive.low[2]</t>
+          <t xml:space="preserve">GAMEOVER_LINES.fighter.delinquent.high[3]</t>
         </is>
       </c>
       <c r="B478" t="inlineStr" s="2">
@@ -17444,24 +17444,24 @@
       </c>
       <c r="E478" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.seductive.low[2]</t>
+          <t xml:space="preserve">fighter.delinquent.high[3]</t>
         </is>
       </c>
       <c r="F478" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">蠱惑</t>
+          <t xml:space="preserve">ヤンキー</t>
         </is>
       </c>
       <c r="H478" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">がっかりさせられたわ、本当に</t>
+          <t xml:space="preserve">泣いてんじゃねぇよ。私らはまた、どっかで戦うんだろ</t>
         </is>
       </c>
     </row>
     <row r="479" ht="40" customHeight="1">
       <c r="A479" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GAMEOVER_LINES.fighter.seductive.low[3]</t>
+          <t xml:space="preserve">GAMEOVER_LINES.fighter.delinquent.mid[1]</t>
         </is>
       </c>
       <c r="B479" t="inlineStr" s="2">
@@ -17481,24 +17481,24 @@
       </c>
       <c r="E479" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.seductive.low[3]</t>
+          <t xml:space="preserve">fighter.delinquent.mid[1]</t>
         </is>
       </c>
       <c r="F479" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">蠱惑</t>
+          <t xml:space="preserve">ヤンキー</t>
         </is>
       </c>
       <c r="H479" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……つまらない結末ね</t>
+          <t xml:space="preserve">は? マジかよ。冗談じゃねぇ</t>
         </is>
       </c>
     </row>
     <row r="480" ht="40" customHeight="1">
       <c r="A480" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GAMEOVER_LINES.fighter.polite.high[1]</t>
+          <t xml:space="preserve">GAMEOVER_LINES.fighter.delinquent.mid[2]</t>
         </is>
       </c>
       <c r="B480" t="inlineStr" s="2">
@@ -17518,24 +17518,24 @@
       </c>
       <c r="E480" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.polite.high[1]</t>
+          <t xml:space="preserve">fighter.delinquent.mid[2]</t>
         </is>
       </c>
       <c r="F480" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">丁寧</t>
+          <t xml:space="preserve">ヤンキー</t>
         </is>
       </c>
       <c r="H480" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">みなさま、本当にお世話になりました。心より、感謝申し上げます</t>
+          <t xml:space="preserve">ったく、潰れる団体に入っちまったのが運の尽きかよ</t>
         </is>
       </c>
     </row>
     <row r="481" ht="40" customHeight="1">
       <c r="A481" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GAMEOVER_LINES.fighter.polite.high[2]</t>
+          <t xml:space="preserve">GAMEOVER_LINES.fighter.delinquent.mid[3]</t>
         </is>
       </c>
       <c r="B481" t="inlineStr" s="2">
@@ -17555,24 +17555,24 @@
       </c>
       <c r="E481" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.polite.high[2]</t>
+          <t xml:space="preserve">fighter.delinquent.mid[3]</t>
         </is>
       </c>
       <c r="F481" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">丁寧</t>
+          <t xml:space="preserve">ヤンキー</t>
         </is>
       </c>
       <c r="H481" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私にとって、この団体は特別な場所でございました</t>
+          <t xml:space="preserve">……次、探すしかねぇな</t>
         </is>
       </c>
     </row>
     <row r="482" ht="40" customHeight="1">
       <c r="A482" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GAMEOVER_LINES.fighter.polite.high[3]</t>
+          <t xml:space="preserve">GAMEOVER_LINES.fighter.delinquent.low[1]</t>
         </is>
       </c>
       <c r="B482" t="inlineStr" s="2">
@@ -17592,24 +17592,24 @@
       </c>
       <c r="E482" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.polite.high[3]</t>
+          <t xml:space="preserve">fighter.delinquent.low[1]</t>
         </is>
       </c>
       <c r="F482" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">丁寧</t>
+          <t xml:space="preserve">ヤンキー</t>
         </is>
       </c>
       <c r="H482" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ありがとうございました。この経験は、生涯忘れません</t>
+          <t xml:space="preserve">ふざけんな。私のキャリア、どうしてくれんだ</t>
         </is>
       </c>
     </row>
     <row r="483" ht="40" customHeight="1">
       <c r="A483" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GAMEOVER_LINES.fighter.polite.mid[1]</t>
+          <t xml:space="preserve">GAMEOVER_LINES.fighter.delinquent.low[2]</t>
         </is>
       </c>
       <c r="B483" t="inlineStr" s="2">
@@ -17629,24 +17629,24 @@
       </c>
       <c r="E483" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.polite.mid[1]</t>
+          <t xml:space="preserve">fighter.delinquent.low[2]</t>
         </is>
       </c>
       <c r="F483" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">丁寧</t>
+          <t xml:space="preserve">ヤンキー</t>
         </is>
       </c>
       <c r="H483" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……このような結末になるとは、思いもよりませんでした</t>
+          <t xml:space="preserve">最初から胡散臭いとは思ってたんだ</t>
         </is>
       </c>
     </row>
     <row r="484" ht="40" customHeight="1">
       <c r="A484" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GAMEOVER_LINES.fighter.polite.mid[2]</t>
+          <t xml:space="preserve">GAMEOVER_LINES.fighter.delinquent.low[3]</t>
         </is>
       </c>
       <c r="B484" t="inlineStr" s="2">
@@ -17666,24 +17666,24 @@
       </c>
       <c r="E484" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.polite.mid[2]</t>
+          <t xml:space="preserve">fighter.delinquent.low[3]</t>
         </is>
       </c>
       <c r="F484" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">丁寧</t>
+          <t xml:space="preserve">ヤンキー</t>
         </is>
       </c>
       <c r="H484" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次の所属先を、探すことになりますね</t>
+          <t xml:space="preserve">失せろ。お前の顔は二度と見たくねぇ</t>
         </is>
       </c>
     </row>
     <row r="485" ht="40" customHeight="1">
       <c r="A485" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GAMEOVER_LINES.fighter.polite.mid[3]</t>
+          <t xml:space="preserve">GAMEOVER_LINES.fighter.cool.high[1]</t>
         </is>
       </c>
       <c r="B485" t="inlineStr" s="2">
@@ -17703,24 +17703,24 @@
       </c>
       <c r="E485" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.polite.mid[3]</t>
+          <t xml:space="preserve">fighter.cool.high[1]</t>
         </is>
       </c>
       <c r="F485" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">丁寧</t>
+          <t xml:space="preserve">クール</t>
         </is>
       </c>
       <c r="H485" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……何と申し上げてよいか、言葉が見つかりません</t>
+          <t xml:space="preserve">……世話になった</t>
         </is>
       </c>
     </row>
     <row r="486" ht="40" customHeight="1">
       <c r="A486" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GAMEOVER_LINES.fighter.polite.low[1]</t>
+          <t xml:space="preserve">GAMEOVER_LINES.fighter.cool.high[2]</t>
         </is>
       </c>
       <c r="B486" t="inlineStr" s="2">
@@ -17740,24 +17740,24 @@
       </c>
       <c r="E486" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.polite.low[1]</t>
+          <t xml:space="preserve">fighter.cool.high[2]</t>
         </is>
       </c>
       <c r="F486" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">丁寧</t>
+          <t xml:space="preserve">クール</t>
         </is>
       </c>
       <c r="H486" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……信じてついてまいりましたのに、残念です</t>
+          <t xml:space="preserve">ここで戦えてよかった。それだけは確かだ</t>
         </is>
       </c>
     </row>
     <row r="487" ht="40" customHeight="1">
       <c r="A487" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GAMEOVER_LINES.fighter.polite.low[2]</t>
+          <t xml:space="preserve">GAMEOVER_LINES.fighter.cool.high[3]</t>
         </is>
       </c>
       <c r="B487" t="inlineStr" s="2">
@@ -17777,24 +17777,24 @@
       </c>
       <c r="E487" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.polite.low[2]</t>
+          <t xml:space="preserve">fighter.cool.high[3]</t>
         </is>
       </c>
       <c r="F487" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">丁寧</t>
+          <t xml:space="preserve">クール</t>
         </is>
       </c>
       <c r="H487" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いえ、何も申し上げることはございません</t>
+          <t xml:space="preserve">……次のリング、探す。それだけだ</t>
         </is>
       </c>
     </row>
     <row r="488" ht="40" customHeight="1">
       <c r="A488" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GAMEOVER_LINES.fighter.polite.low[3]</t>
+          <t xml:space="preserve">GAMEOVER_LINES.fighter.cool.mid[1]</t>
         </is>
       </c>
       <c r="B488" t="inlineStr" s="2">
@@ -17814,24 +17814,24 @@
       </c>
       <c r="E488" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.polite.low[3]</t>
+          <t xml:space="preserve">fighter.cool.mid[1]</t>
         </is>
       </c>
       <c r="F488" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">丁寧</t>
+          <t xml:space="preserve">クール</t>
         </is>
       </c>
       <c r="H488" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……失礼いたします</t>
+          <t xml:space="preserve">……終わったか</t>
         </is>
       </c>
     </row>
     <row r="489" ht="40" customHeight="1">
       <c r="A489" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GAMEOVER_LINES.fighter.standard.high[1]</t>
+          <t xml:space="preserve">GAMEOVER_LINES.fighter.cool.mid[2]</t>
         </is>
       </c>
       <c r="B489" t="inlineStr" s="2">
@@ -17851,24 +17851,24 @@
       </c>
       <c r="E489" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.standard.high[1]</t>
+          <t xml:space="preserve">fighter.cool.mid[2]</t>
         </is>
       </c>
       <c r="F489" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">標準</t>
+          <t xml:space="preserve">クール</t>
         </is>
       </c>
       <c r="H489" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お疲れ様でした、社長。ここで戦えたこと、忘れません</t>
+          <t xml:space="preserve">次を探すしかない</t>
         </is>
       </c>
     </row>
     <row r="490" ht="40" customHeight="1">
       <c r="A490" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GAMEOVER_LINES.fighter.standard.high[2]</t>
+          <t xml:space="preserve">GAMEOVER_LINES.fighter.cool.low[1]</t>
         </is>
       </c>
       <c r="B490" t="inlineStr" s="2">
@@ -17888,24 +17888,24 @@
       </c>
       <c r="E490" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.standard.high[2]</t>
+          <t xml:space="preserve">fighter.cool.low[1]</t>
         </is>
       </c>
       <c r="F490" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">標準</t>
+          <t xml:space="preserve">クール</t>
         </is>
       </c>
       <c r="H490" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いい経験になりました。本当にありがとうございました</t>
+          <t xml:space="preserve">予想通りだ</t>
         </is>
       </c>
     </row>
     <row r="491" ht="40" customHeight="1">
       <c r="A491" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GAMEOVER_LINES.fighter.standard.high[3]</t>
+          <t xml:space="preserve">GAMEOVER_LINES.fighter.cool.low[2]</t>
         </is>
       </c>
       <c r="B491" t="inlineStr" s="2">
@@ -17925,24 +17925,24 @@
       </c>
       <c r="E491" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.standard.high[3]</t>
+          <t xml:space="preserve">fighter.cool.low[2]</t>
         </is>
       </c>
       <c r="F491" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">標準</t>
+          <t xml:space="preserve">クール</t>
         </is>
       </c>
       <c r="H491" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">また、どこかのリングで会えますように</t>
+          <t xml:space="preserve">……特に言うことはない</t>
         </is>
       </c>
     </row>
     <row r="492" ht="40" customHeight="1">
       <c r="A492" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GAMEOVER_LINES.fighter.standard.mid[1]</t>
+          <t xml:space="preserve">GAMEOVER_LINES.fighter.seductive.high[1]</t>
         </is>
       </c>
       <c r="B492" t="inlineStr" s="2">
@@ -17962,24 +17962,24 @@
       </c>
       <c r="E492" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.standard.mid[1]</t>
+          <t xml:space="preserve">fighter.seductive.high[1]</t>
         </is>
       </c>
       <c r="F492" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">標準</t>
+          <t xml:space="preserve">蠱惑</t>
         </is>
       </c>
       <c r="H492" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">仕方ないですね。次の場所を探します</t>
+          <t xml:space="preserve">あら、終わってしまうのね。……でも、悪くなかったわ</t>
         </is>
       </c>
     </row>
     <row r="493" ht="40" customHeight="1">
       <c r="A493" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GAMEOVER_LINES.fighter.standard.mid[2]</t>
+          <t xml:space="preserve">GAMEOVER_LINES.fighter.seductive.high[2]</t>
         </is>
       </c>
       <c r="B493" t="inlineStr" s="2">
@@ -17999,24 +17999,24 @@
       </c>
       <c r="E493" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.standard.mid[2]</t>
+          <t xml:space="preserve">fighter.seductive.high[2]</t>
         </is>
       </c>
       <c r="F493" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">標準</t>
+          <t xml:space="preserve">蠱惑</t>
         </is>
       </c>
       <c r="H493" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こうなったら、新しい団体に移るしかありません</t>
+          <t xml:space="preserve">この団体で見せた表情、忘れないでくださる?</t>
         </is>
       </c>
     </row>
     <row r="494" ht="40" customHeight="1">
       <c r="A494" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GAMEOVER_LINES.fighter.standard.mid[3]</t>
+          <t xml:space="preserve">GAMEOVER_LINES.fighter.seductive.high[3]</t>
         </is>
       </c>
       <c r="B494" t="inlineStr" s="2">
@@ -18036,24 +18036,24 @@
       </c>
       <c r="E494" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.standard.mid[3]</t>
+          <t xml:space="preserve">fighter.seductive.high[3]</t>
         </is>
       </c>
       <c r="F494" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">標準</t>
+          <t xml:space="preserve">蠱惑</t>
         </is>
       </c>
       <c r="H494" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……無念です</t>
+          <t xml:space="preserve">別れ際の言葉……どうしましょうかしら。でも、感謝しているの。本当よ</t>
         </is>
       </c>
     </row>
     <row r="495" ht="40" customHeight="1">
       <c r="A495" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GAMEOVER_LINES.fighter.standard.low[1]</t>
+          <t xml:space="preserve">GAMEOVER_LINES.fighter.seductive.mid[1]</t>
         </is>
       </c>
       <c r="B495" t="inlineStr" s="2">
@@ -18073,24 +18073,24 @@
       </c>
       <c r="E495" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.standard.low[1]</t>
+          <t xml:space="preserve">fighter.seductive.mid[1]</t>
         </is>
       </c>
       <c r="F495" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">標準</t>
+          <t xml:space="preserve">蠱惑</t>
         </is>
       </c>
       <c r="H495" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">結局こうなったか</t>
+          <t xml:space="preserve">あらあら、こんな結末も、また面白いのかしら</t>
         </is>
       </c>
     </row>
     <row r="496" ht="40" customHeight="1">
       <c r="A496" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GAMEOVER_LINES.fighter.standard.low[2]</t>
+          <t xml:space="preserve">GAMEOVER_LINES.fighter.seductive.mid[2]</t>
         </is>
       </c>
       <c r="B496" t="inlineStr" s="2">
@@ -18110,24 +18110,24 @@
       </c>
       <c r="E496" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.standard.low[2]</t>
+          <t xml:space="preserve">fighter.seductive.mid[2]</t>
         </is>
       </c>
       <c r="F496" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">標準</t>
+          <t xml:space="preserve">蠱惑</t>
         </is>
       </c>
       <c r="H496" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">想定の範囲内です</t>
+          <t xml:space="preserve">次の舞台、見つけなくちゃね</t>
         </is>
       </c>
     </row>
     <row r="497" ht="40" customHeight="1">
       <c r="A497" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GAMEOVER_LINES.fighter.standard.low[3]</t>
+          <t xml:space="preserve">GAMEOVER_LINES.fighter.seductive.mid[3]</t>
         </is>
       </c>
       <c r="B497" t="inlineStr" s="2">
@@ -18147,24 +18147,24 @@
       </c>
       <c r="E497" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.standard.low[3]</t>
+          <t xml:space="preserve">fighter.seductive.mid[3]</t>
         </is>
       </c>
       <c r="F497" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">標準</t>
+          <t xml:space="preserve">蠱惑</t>
         </is>
       </c>
       <c r="H497" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……何も言うことはありません</t>
+          <t xml:space="preserve">……あぁ、これで終わりなのね</t>
         </is>
       </c>
     </row>
     <row r="498" ht="40" customHeight="1">
       <c r="A498" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GAMEOVER_LINES.coach[1]</t>
+          <t xml:space="preserve">GAMEOVER_LINES.fighter.seductive.low[1]</t>
         </is>
       </c>
       <c r="B498" t="inlineStr" s="2">
@@ -18184,19 +18184,24 @@
       </c>
       <c r="E498" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">coach[1]</t>
+          <t xml:space="preserve">fighter.seductive.low[1]</t>
+        </is>
+      </c>
+      <c r="F498" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">蠱惑</t>
         </is>
       </c>
       <c r="H498" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私の力不足だ。選手たちには、すまないとしか言えない</t>
+          <t xml:space="preserve">夢を見させてくれてありがとう、と言うべきかしら</t>
         </is>
       </c>
     </row>
     <row r="499" ht="40" customHeight="1">
       <c r="A499" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GAMEOVER_LINES.coach[2]</t>
+          <t xml:space="preserve">GAMEOVER_LINES.fighter.seductive.low[2]</t>
         </is>
       </c>
       <c r="B499" t="inlineStr" s="2">
@@ -18216,19 +18221,24 @@
       </c>
       <c r="E499" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">coach[2]</t>
+          <t xml:space="preserve">fighter.seductive.low[2]</t>
+        </is>
+      </c>
+      <c r="F499" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">蠱惑</t>
         </is>
       </c>
       <c r="H499" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ伸びる途中だった子が多い……それが、悔しくてならない</t>
+          <t xml:space="preserve">がっかりさせられたわ、本当に</t>
         </is>
       </c>
     </row>
     <row r="500" ht="40" customHeight="1">
       <c r="A500" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GAMEOVER_LINES.coach[3]</t>
+          <t xml:space="preserve">GAMEOVER_LINES.fighter.seductive.low[3]</t>
         </is>
       </c>
       <c r="B500" t="inlineStr" s="2">
@@ -18248,19 +18258,24 @@
       </c>
       <c r="E500" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">coach[3]</t>
+          <t xml:space="preserve">fighter.seductive.low[3]</t>
+        </is>
+      </c>
+      <c r="F500" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">蠱惑</t>
         </is>
       </c>
       <c r="H500" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よくここまで耐えた。胸を張りなさい、君たちは</t>
+          <t xml:space="preserve">……つまらない結末ね</t>
         </is>
       </c>
     </row>
     <row r="501" ht="40" customHeight="1">
       <c r="A501" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GAMEOVER_LINES.coach[4]</t>
+          <t xml:space="preserve">GAMEOVER_LINES.fighter.polite.high[1]</t>
         </is>
       </c>
       <c r="B501" t="inlineStr" s="2">
@@ -18280,19 +18295,24 @@
       </c>
       <c r="E501" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">coach[4]</t>
+          <t xml:space="preserve">fighter.polite.high[1]</t>
+        </is>
+      </c>
+      <c r="F501" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">丁寧</t>
         </is>
       </c>
       <c r="H501" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">指導者として、最後まで支えきれなかった。それだけが心残りだ</t>
+          <t xml:space="preserve">みなさま、本当にお世話になりました。心より、感謝申し上げます</t>
         </is>
       </c>
     </row>
     <row r="502" ht="40" customHeight="1">
       <c r="A502" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GAMEOVER_LINES.coach[5]</t>
+          <t xml:space="preserve">GAMEOVER_LINES.fighter.polite.high[2]</t>
         </is>
       </c>
       <c r="B502" t="inlineStr" s="2">
@@ -18312,19 +18332,24 @@
       </c>
       <c r="E502" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">coach[5]</t>
+          <t xml:space="preserve">fighter.polite.high[2]</t>
+        </is>
+      </c>
+      <c r="F502" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">丁寧</t>
         </is>
       </c>
       <c r="H502" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">若い選手たちの行く先だけが心配だ。誰か、引き取ってくれるといい</t>
+          <t xml:space="preserve">私にとって、この団体は特別な場所でございました</t>
         </is>
       </c>
     </row>
     <row r="503" ht="40" customHeight="1">
       <c r="A503" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GAMEOVER_LINES.coach[6]</t>
+          <t xml:space="preserve">GAMEOVER_LINES.fighter.polite.high[3]</t>
         </is>
       </c>
       <c r="B503" t="inlineStr" s="2">
@@ -18344,19 +18369,24 @@
       </c>
       <c r="E503" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">coach[6]</t>
+          <t xml:space="preserve">fighter.polite.high[3]</t>
+        </is>
+      </c>
+      <c r="F503" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">丁寧</t>
         </is>
       </c>
       <c r="H503" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">責任は私にもある。社長、頭を上げてくれ</t>
+          <t xml:space="preserve">……ありがとうございました。この経験は、生涯忘れません</t>
         </is>
       </c>
     </row>
     <row r="504" ht="40" customHeight="1">
       <c r="A504" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.coach[1]</t>
+          <t xml:space="preserve">GAMEOVER_LINES.fighter.polite.mid[1]</t>
         </is>
       </c>
       <c r="B504" t="inlineStr" s="2">
@@ -18371,24 +18401,29 @@
       </c>
       <c r="D504" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">GAMEOVER_LINES</t>
         </is>
       </c>
       <c r="E504" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">coach[1]</t>
+          <t xml:space="preserve">fighter.polite.mid[1]</t>
+        </is>
+      </c>
+      <c r="F504" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">丁寧</t>
         </is>
       </c>
       <c r="H504" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よくぞここまで……立派になった</t>
+          <t xml:space="preserve">……このような結末になるとは、思いもよりませんでした</t>
         </is>
       </c>
     </row>
     <row r="505" ht="40" customHeight="1">
       <c r="A505" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.coach[2]</t>
+          <t xml:space="preserve">GAMEOVER_LINES.fighter.polite.mid[2]</t>
         </is>
       </c>
       <c r="B505" t="inlineStr" s="2">
@@ -18403,24 +18438,29 @@
       </c>
       <c r="D505" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">GAMEOVER_LINES</t>
         </is>
       </c>
       <c r="E505" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">coach[2]</t>
+          <t xml:space="preserve">fighter.polite.mid[2]</t>
+        </is>
+      </c>
+      <c r="F505" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">丁寧</t>
         </is>
       </c>
       <c r="H505" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの選手たちを見ていると、指導者冥利に尽きる</t>
+          <t xml:space="preserve">次の所属先を、探すことになりますね</t>
         </is>
       </c>
     </row>
     <row r="506" ht="40" customHeight="1">
       <c r="A506" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.coach[3]</t>
+          <t xml:space="preserve">GAMEOVER_LINES.fighter.polite.mid[3]</t>
         </is>
       </c>
       <c r="B506" t="inlineStr" s="2">
@@ -18435,24 +18475,29 @@
       </c>
       <c r="D506" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">GAMEOVER_LINES</t>
         </is>
       </c>
       <c r="E506" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">coach[3]</t>
+          <t xml:space="preserve">fighter.polite.mid[3]</t>
+        </is>
+      </c>
+      <c r="F506" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">丁寧</t>
         </is>
       </c>
       <c r="H506" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私の教え子たちが業界の頂点に。これ以上の喜びはない</t>
+          <t xml:space="preserve">……何と申し上げてよいか、言葉が見つかりません</t>
         </is>
       </c>
     </row>
     <row r="507" ht="40" customHeight="1">
       <c r="A507" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.coach[4]</t>
+          <t xml:space="preserve">GAMEOVER_LINES.fighter.polite.low[1]</t>
         </is>
       </c>
       <c r="B507" t="inlineStr" s="2">
@@ -18467,24 +18512,29 @@
       </c>
       <c r="D507" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">GAMEOVER_LINES</t>
         </is>
       </c>
       <c r="E507" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">coach[4]</t>
+          <t xml:space="preserve">fighter.polite.low[1]</t>
+        </is>
+      </c>
+      <c r="F507" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">丁寧</t>
         </is>
       </c>
       <c r="H507" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだまだ伸びる選手ばかりだ。楽しみは尽きないよ</t>
+          <t xml:space="preserve">……信じてついてまいりましたのに、残念です</t>
         </is>
       </c>
     </row>
     <row r="508" ht="40" customHeight="1">
       <c r="A508" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.coach[5]</t>
+          <t xml:space="preserve">GAMEOVER_LINES.fighter.polite.low[2]</t>
         </is>
       </c>
       <c r="B508" t="inlineStr" s="2">
@@ -18499,24 +18549,29 @@
       </c>
       <c r="D508" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">GAMEOVER_LINES</t>
         </is>
       </c>
       <c r="E508" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">coach[5]</t>
+          <t xml:space="preserve">fighter.polite.low[2]</t>
+        </is>
+      </c>
+      <c r="F508" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">丁寧</t>
         </is>
       </c>
       <c r="H508" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここが終着点じゃない。さらに上の景色を見せてやる</t>
+          <t xml:space="preserve">いえ、何も申し上げることはございません</t>
         </is>
       </c>
     </row>
     <row r="509" ht="40" customHeight="1">
       <c r="A509" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.coach[6]</t>
+          <t xml:space="preserve">GAMEOVER_LINES.fighter.polite.low[3]</t>
         </is>
       </c>
       <c r="B509" t="inlineStr" s="2">
@@ -18531,24 +18586,29 @@
       </c>
       <c r="D509" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">GAMEOVER_LINES</t>
         </is>
       </c>
       <c r="E509" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">coach[6]</t>
+          <t xml:space="preserve">fighter.polite.low[3]</t>
+        </is>
+      </c>
+      <c r="F509" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">丁寧</t>
         </is>
       </c>
       <c r="H509" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">選手たちの努力が実を結んだ。私は見守っただけだ</t>
+          <t xml:space="preserve">……失礼いたします</t>
         </is>
       </c>
     </row>
     <row r="510" ht="40" customHeight="1">
       <c r="A510" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.coach[7]</t>
+          <t xml:space="preserve">GAMEOVER_LINES.fighter.standard.high[1]</t>
         </is>
       </c>
       <c r="B510" t="inlineStr" s="2">
@@ -18563,24 +18623,29 @@
       </c>
       <c r="D510" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">GAMEOVER_LINES</t>
         </is>
       </c>
       <c r="E510" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">coach[7]</t>
+          <t xml:space="preserve">fighter.standard.high[1]</t>
+        </is>
+      </c>
+      <c r="F510" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="H510" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">苦しい時期を乗り越えた選手たちの姿に……涙が出そうだ</t>
+          <t xml:space="preserve">お疲れ様でした、社長。ここで戦えたこと、忘れません</t>
         </is>
       </c>
     </row>
     <row r="511" ht="40" customHeight="1">
       <c r="A511" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.coach[8]</t>
+          <t xml:space="preserve">GAMEOVER_LINES.fighter.standard.high[2]</t>
         </is>
       </c>
       <c r="B511" t="inlineStr" s="2">
@@ -18595,24 +18660,29 @@
       </c>
       <c r="D511" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">GAMEOVER_LINES</t>
         </is>
       </c>
       <c r="E511" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">coach[8]</t>
+          <t xml:space="preserve">fighter.standard.high[2]</t>
+        </is>
+      </c>
+      <c r="F511" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="H511" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全員が成長した。一人の脱落者も出さなかった。それが誇りだ</t>
+          <t xml:space="preserve">いい経験になりました。本当にありがとうございました</t>
         </is>
       </c>
     </row>
     <row r="512" ht="40" customHeight="1">
       <c r="A512" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.coach[9]</t>
+          <t xml:space="preserve">GAMEOVER_LINES.fighter.standard.high[3]</t>
         </is>
       </c>
       <c r="B512" t="inlineStr" s="2">
@@ -18627,54 +18697,761 @@
       </c>
       <c r="D512" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">GAMEOVER_LINES</t>
         </is>
       </c>
       <c r="E512" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">coach[9]</t>
+          <t xml:space="preserve">fighter.standard.high[3]</t>
+        </is>
+      </c>
+      <c r="F512" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="H512" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この子たちとなら、もっと高い場所を目指せる</t>
+          <t xml:space="preserve">また、どこかのリングで会えますように</t>
         </is>
       </c>
     </row>
     <row r="513" ht="40" customHeight="1">
       <c r="A513" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">GAMEOVER_LINES.fighter.standard.mid[1]</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">18-経営危機・エンディング</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GAMEOVER_LINES</t>
+        </is>
+      </c>
+      <c r="E513" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">fighter.standard.mid[1]</t>
+        </is>
+      </c>
+      <c r="F513" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
+        </is>
+      </c>
+      <c r="H513" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">仕方ないですね。次の場所を探します</t>
+        </is>
+      </c>
+    </row>
+    <row r="514" ht="40" customHeight="1">
+      <c r="A514" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GAMEOVER_LINES.fighter.standard.mid[2]</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">18-経営危機・エンディング</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GAMEOVER_LINES</t>
+        </is>
+      </c>
+      <c r="E514" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">fighter.standard.mid[2]</t>
+        </is>
+      </c>
+      <c r="F514" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
+        </is>
+      </c>
+      <c r="H514" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">こうなったら、新しい団体に移るしかありません</t>
+        </is>
+      </c>
+    </row>
+    <row r="515" ht="40" customHeight="1">
+      <c r="A515" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GAMEOVER_LINES.fighter.standard.mid[3]</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">18-経営危機・エンディング</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GAMEOVER_LINES</t>
+        </is>
+      </c>
+      <c r="E515" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">fighter.standard.mid[3]</t>
+        </is>
+      </c>
+      <c r="F515" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
+        </is>
+      </c>
+      <c r="H515" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……無念です</t>
+        </is>
+      </c>
+    </row>
+    <row r="516" ht="40" customHeight="1">
+      <c r="A516" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GAMEOVER_LINES.fighter.standard.low[1]</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">18-経営危機・エンディング</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GAMEOVER_LINES</t>
+        </is>
+      </c>
+      <c r="E516" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">fighter.standard.low[1]</t>
+        </is>
+      </c>
+      <c r="F516" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
+        </is>
+      </c>
+      <c r="H516" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">結局こうなったか</t>
+        </is>
+      </c>
+    </row>
+    <row r="517" ht="40" customHeight="1">
+      <c r="A517" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GAMEOVER_LINES.fighter.standard.low[2]</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">18-経営危機・エンディング</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GAMEOVER_LINES</t>
+        </is>
+      </c>
+      <c r="E517" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">fighter.standard.low[2]</t>
+        </is>
+      </c>
+      <c r="F517" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
+        </is>
+      </c>
+      <c r="H517" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">想定の範囲内です</t>
+        </is>
+      </c>
+    </row>
+    <row r="518" ht="40" customHeight="1">
+      <c r="A518" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GAMEOVER_LINES.fighter.standard.low[3]</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">18-経営危機・エンディング</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GAMEOVER_LINES</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">fighter.standard.low[3]</t>
+        </is>
+      </c>
+      <c r="F518" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
+        </is>
+      </c>
+      <c r="H518" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……何も言うことはありません</t>
+        </is>
+      </c>
+    </row>
+    <row r="519" ht="40" customHeight="1">
+      <c r="A519" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GAMEOVER_LINES.coach[1]</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">18-経営危機・エンディング</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GAMEOVER_LINES</t>
+        </is>
+      </c>
+      <c r="E519" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">coach[1]</t>
+        </is>
+      </c>
+      <c r="H519" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">私の力不足だ。選手たちには、すまないとしか言えない</t>
+        </is>
+      </c>
+    </row>
+    <row r="520" ht="40" customHeight="1">
+      <c r="A520" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GAMEOVER_LINES.coach[2]</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">18-経営危機・エンディング</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GAMEOVER_LINES</t>
+        </is>
+      </c>
+      <c r="E520" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">coach[2]</t>
+        </is>
+      </c>
+      <c r="H520" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">まだ伸びる途中だった子が多い……それが、悔しくてならない</t>
+        </is>
+      </c>
+    </row>
+    <row r="521" ht="40" customHeight="1">
+      <c r="A521" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GAMEOVER_LINES.coach[3]</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">18-経営危機・エンディング</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GAMEOVER_LINES</t>
+        </is>
+      </c>
+      <c r="E521" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">coach[3]</t>
+        </is>
+      </c>
+      <c r="H521" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">よくここまで耐えた。胸を張りなさい、君たちは</t>
+        </is>
+      </c>
+    </row>
+    <row r="522" ht="40" customHeight="1">
+      <c r="A522" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GAMEOVER_LINES.coach[4]</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">18-経営危機・エンディング</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GAMEOVER_LINES</t>
+        </is>
+      </c>
+      <c r="E522" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">coach[4]</t>
+        </is>
+      </c>
+      <c r="H522" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">指導者として、最後まで支えきれなかった。それだけが心残りだ</t>
+        </is>
+      </c>
+    </row>
+    <row r="523" ht="40" customHeight="1">
+      <c r="A523" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GAMEOVER_LINES.coach[5]</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">18-経営危機・エンディング</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GAMEOVER_LINES</t>
+        </is>
+      </c>
+      <c r="E523" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">coach[5]</t>
+        </is>
+      </c>
+      <c r="H523" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">若い選手たちの行く先だけが心配だ。誰か、引き取ってくれるといい</t>
+        </is>
+      </c>
+    </row>
+    <row r="524" ht="40" customHeight="1">
+      <c r="A524" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GAMEOVER_LINES.coach[6]</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">18-経営危機・エンディング</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GAMEOVER_LINES</t>
+        </is>
+      </c>
+      <c r="E524" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">coach[6]</t>
+        </is>
+      </c>
+      <c r="H524" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">責任は私にもある。社長、頭を上げてくれ</t>
+        </is>
+      </c>
+    </row>
+    <row r="525" ht="40" customHeight="1">
+      <c r="A525" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">ENDING_LINES.coach[1]</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">18-経営危機・エンディング</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ENDING_LINES</t>
+        </is>
+      </c>
+      <c r="E525" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">coach[1]</t>
+        </is>
+      </c>
+      <c r="H525" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">よくぞここまで……立派になった</t>
+        </is>
+      </c>
+    </row>
+    <row r="526" ht="40" customHeight="1">
+      <c r="A526" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">ENDING_LINES.coach[2]</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">18-経営危機・エンディング</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ENDING_LINES</t>
+        </is>
+      </c>
+      <c r="E526" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">coach[2]</t>
+        </is>
+      </c>
+      <c r="H526" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あの選手たちを見ていると、指導者冥利に尽きる</t>
+        </is>
+      </c>
+    </row>
+    <row r="527" ht="40" customHeight="1">
+      <c r="A527" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">ENDING_LINES.coach[3]</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">18-経営危機・エンディング</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ENDING_LINES</t>
+        </is>
+      </c>
+      <c r="E527" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">coach[3]</t>
+        </is>
+      </c>
+      <c r="H527" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">私の教え子たちが業界の頂点に。これ以上の喜びはない</t>
+        </is>
+      </c>
+    </row>
+    <row r="528" ht="40" customHeight="1">
+      <c r="A528" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">ENDING_LINES.coach[4]</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">18-経営危機・エンディング</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ENDING_LINES</t>
+        </is>
+      </c>
+      <c r="E528" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">coach[4]</t>
+        </is>
+      </c>
+      <c r="H528" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">まだまだ伸びる選手ばかりだ。楽しみは尽きないよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="529" ht="40" customHeight="1">
+      <c r="A529" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">ENDING_LINES.coach[5]</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">18-経営危機・エンディング</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ENDING_LINES</t>
+        </is>
+      </c>
+      <c r="E529" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">coach[5]</t>
+        </is>
+      </c>
+      <c r="H529" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ここが終着点じゃない。さらに上の景色を見せてやる</t>
+        </is>
+      </c>
+    </row>
+    <row r="530" ht="40" customHeight="1">
+      <c r="A530" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">ENDING_LINES.coach[6]</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">18-経営危機・エンディング</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ENDING_LINES</t>
+        </is>
+      </c>
+      <c r="E530" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">coach[6]</t>
+        </is>
+      </c>
+      <c r="H530" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">選手たちの努力が実を結んだ。私は見守っただけだ</t>
+        </is>
+      </c>
+    </row>
+    <row r="531" ht="40" customHeight="1">
+      <c r="A531" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">ENDING_LINES.coach[7]</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">18-経営危機・エンディング</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ENDING_LINES</t>
+        </is>
+      </c>
+      <c r="E531" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">coach[7]</t>
+        </is>
+      </c>
+      <c r="H531" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">苦しい時期を乗り越えた選手たちの姿に……涙が出そうだ</t>
+        </is>
+      </c>
+    </row>
+    <row r="532" ht="40" customHeight="1">
+      <c r="A532" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">ENDING_LINES.coach[8]</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">18-経営危機・エンディング</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ENDING_LINES</t>
+        </is>
+      </c>
+      <c r="E532" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">coach[8]</t>
+        </is>
+      </c>
+      <c r="H532" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">全員が成長した。一人の脱落者も出さなかった。それが誇りだ</t>
+        </is>
+      </c>
+    </row>
+    <row r="533" ht="40" customHeight="1">
+      <c r="A533" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">ENDING_LINES.coach[9]</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">18-経営危機・エンディング</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ENDING_LINES</t>
+        </is>
+      </c>
+      <c r="E533" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">coach[9]</t>
+        </is>
+      </c>
+      <c r="H533" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">この子たちとなら、もっと高い場所を目指せる</t>
+        </is>
+      </c>
+    </row>
+    <row r="534" ht="40" customHeight="1">
+      <c r="A534" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">ENDING_LINES.coach[10]</t>
         </is>
       </c>
-      <c r="B513" t="inlineStr" s="2">
+      <c r="B534" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">18-経営危機・エンディング</t>
         </is>
       </c>
-      <c r="C513" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="D513" t="inlineStr" s="2">
+      <c r="C534" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">ENDING_LINES</t>
         </is>
       </c>
-      <c r="E513" t="inlineStr" s="12">
+      <c r="E534" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">coach[10]</t>
         </is>
       </c>
-      <c r="H513" t="inlineStr" s="3">
+      <c r="H534" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">指導者として、これ以上の幸せはないよ</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J513"/>
+  <autoFilter ref="A1:J534"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/その他セリフ/その他.xlsx
+++ b/セリフ編集/その他セリフ/その他.xlsx
@@ -3725,7 +3725,7 @@
       </c>
       <c r="H96" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">旗揚げからここにいるのよ、わたし。</t>
+          <t xml:space="preserve">旗揚げからここにいるのよ、私。</t>
         </is>
       </c>
     </row>
@@ -4243,7 +4243,7 @@
       </c>
       <c r="H110" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたしなりに、結果は出してきたつもりよ。</t>
+          <t xml:space="preserve">私なりに、結果は出してきたつもりよ。</t>
         </is>
       </c>
     </row>
@@ -6648,7 +6648,7 @@
       </c>
       <c r="H175" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……はい。皆には、わたしから伝えます</t>
+          <t xml:space="preserve">……はい。皆には、私から伝えます</t>
         </is>
       </c>
     </row>
